--- a/docs/gymhub_expotecnica/modelo_negocios/Analisis_ gym.xlsx
+++ b/docs/gymhub_expotecnica/modelo_negocios/Analisis_ gym.xlsx
@@ -252,7 +252,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="61">
+  <cellXfs count="60">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -350,13 +350,25 @@
     </xf>
     <xf numFmtId="0" fontId="8" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -365,24 +377,13 @@
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <tableStyles count="1" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16">
+    <tableStyle name="Invisible" pivot="0" table="0" count="0"/>
+  </tableStyles>
   <colors>
     <indexedColors>
       <rgbColor rgb="00000000"/>
@@ -466,7 +467,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>Ingresos y costos completos por mes</a:t>
+              <a:t>Ingresos y pagos efectivos por mes</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -483,6 +484,12 @@
           <tx>
             <strRef>
               <f>'Clientes e Ingresos'!$H$5</f>
+              <strCache>
+                <ptCount val="1"/>
+                <pt idx="0">
+                  <v>Ingreso Mensual MRR (₡)</v>
+                </pt>
+              </strCache>
             </strRef>
           </tx>
           <spPr>
@@ -595,6 +602,12 @@
           <tx>
             <strRef>
               <f>'Egresos e Inversión'!$F$34</f>
+              <strCache>
+                <ptCount val="1"/>
+                <pt idx="0">
+                  <v>Egresos sin desarrollo</v>
+                </pt>
+              </strCache>
             </strRef>
           </tx>
           <spPr>
@@ -661,40 +674,40 @@
                 <formatCode>#,##0.00</formatCode>
                 <ptCount val="12"/>
                 <pt idx="0">
-                  <v>785607.79</v>
+                  <v>111107.79</v>
                 </pt>
                 <pt idx="1">
-                  <v>148558.2</v>
+                  <v>83558.2</v>
                 </pt>
                 <pt idx="2">
-                  <v>151508.61</v>
+                  <v>84008.61</v>
                 </pt>
                 <pt idx="3">
-                  <v>164459.02</v>
+                  <v>94459.02</v>
                 </pt>
                 <pt idx="4">
-                  <v>167409.43</v>
+                  <v>94909.42999999999</v>
                 </pt>
                 <pt idx="5">
-                  <v>167409.43</v>
+                  <v>94909.42999999999</v>
                 </pt>
                 <pt idx="6">
-                  <v>170359.84</v>
+                  <v>95359.84</v>
                 </pt>
                 <pt idx="7">
-                  <v>175810.25</v>
+                  <v>98310.25</v>
                 </pt>
                 <pt idx="8">
-                  <v>178760.66</v>
+                  <v>98760.66</v>
                 </pt>
                 <pt idx="9">
-                  <v>178760.66</v>
+                  <v>98760.66</v>
                 </pt>
                 <pt idx="10">
-                  <v>181711.07</v>
+                  <v>99211.06999999999</v>
                 </pt>
                 <pt idx="11">
-                  <v>184661.48</v>
+                  <v>99661.48000000001</v>
                 </pt>
               </numCache>
             </numRef>
@@ -801,16 +814,19 @@
       <tx>
         <rich>
           <a:bodyPr/>
+          <a:lstStyle/>
           <a:p>
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
             <a:r>
+              <a:rPr lang="es-CR"/>
               <a:t>Saldo acumulado con financiamiento inicial</a:t>
             </a:r>
           </a:p>
         </rich>
       </tx>
+      <overlay val="1"/>
     </title>
     <plotArea>
       <layout/>
@@ -878,40 +894,40 @@
                 <formatCode>#,##0.00</formatCode>
                 <ptCount val="12"/>
                 <pt idx="0">
-                  <v>8558.199999999953</v>
+                  <v>43892.21000000001</v>
                 </pt>
                 <pt idx="1">
-                  <v>-5.820766091346741e-11</v>
+                  <v>100334.01</v>
                 </pt>
                 <pt idx="2">
-                  <v>13491.38999999996</v>
+                  <v>181325.4</v>
                 </pt>
                 <pt idx="3">
-                  <v>39032.36999999994</v>
+                  <v>276866.38</v>
                 </pt>
                 <pt idx="4">
-                  <v>86622.93999999994</v>
+                  <v>396956.95</v>
                 </pt>
                 <pt idx="5">
-                  <v>134213.51</v>
+                  <v>517047.52</v>
                 </pt>
                 <pt idx="6">
-                  <v>203853.67</v>
+                  <v>661687.6800000001</v>
                 </pt>
                 <pt idx="7">
-                  <v>293043.4199999999</v>
+                  <v>828377.4300000001</v>
                 </pt>
                 <pt idx="8">
-                  <v>404282.7599999999</v>
+                  <v>1019616.77</v>
                 </pt>
                 <pt idx="9">
-                  <v>515522.0999999999</v>
+                  <v>1210856.11</v>
                 </pt>
                 <pt idx="10">
-                  <v>648811.0299999998</v>
+                  <v>1426645.04</v>
                 </pt>
                 <pt idx="11">
-                  <v>804149.5499999998</v>
+                  <v>1666983.56</v>
                 </pt>
               </numCache>
             </numRef>
@@ -1014,8 +1030,9 @@
   <commentList>
     <comment ref="B9" authorId="0" shapeId="0">
       <text>
-        <t>Precios y alcance: Modelo de Costeo y Precio.xlsx, catálogo C5:C12; Costeo B22:E23, B28, E90, B36:E47. Los ₡90 000/₡180 000 son costos internos de instalación avanzada; ₡129 000/₡258 000 son precios calculados con margen de 30% y redondeo. Supabase dedicado obligatorio para Premium y Enterprise. El Word es la base histórica: sus reservas de ₡750 y precios/capacidades anteriores fueron reemplazados por el análisis posterior del mismo directorio.
-Variables base por gimnasio/mes: Starter ₡2 681,15; Pro Gym ₡2 950,41; Premium ₡16 123,56; Enterprise ₡24 745,48, antes de excedentes de cartera. Fuente: Costeo B129:E129. Modelo independiente: referencias de origen en notas, sin vínculos externos de Excel. Cambiar precios/alcance requiere sincronizar los supuestos en las fórmulas.</t>
+        <t>Estimación interna aprobada 17/09/2026; no cotización. Mes 1: 3 recorridos bus × 2 personas × ₡2 000 = ₡12 000; 2 en vehículo × ₡4 000 = ₡8 000; 1 combinado/taxi ₡8 000; comida 2 jornadas × 2 personas × ₡3 000 = ₡12 000. Total ₡40 000. Meses 2–12: 2 recorridos × 2 personas × ₡2 000 + ₡4 000 alimentación = ₡12 000/mes. Diez prospectos; conversión hipotética 50%, no ventas confirmadas. Tiempo: 6 o 2 recorridos × 3 h × 2 personas; no duplica soporte ni instalación.
+Escenario condicionado: Pulso aún sin registro. Beneficio exige inscripción tributaria en régimen general y registro micro/pequeña ante MEIC o MAG. 0% del impuesto determinado años 1–3; 25% años 4–5; 50% año 6. Primer año desde inscripción tributaria. No es tasa sobre ventas ni concede exención de otros tributos. Fuente: https://www.hacienda.go.cr/docs/BeneficiosPymes1.pdf
+https://www.mtss.go.cr/temas-laborales/salarios/lista_salarios_minimos_2026.pdf</t>
       </text>
     </comment>
   </commentList>
@@ -1256,32 +1273,27 @@
   <commentList>
     <comment ref="D7" authorId="0" shapeId="0">
       <text>
-        <t>Fuente: Modelo de Costeo y Precio.xlsx; Costeo!B175.
-Estimación de trabajo pendiente presupuestado; no afirma funcionalidad terminada. Reemplaza rubros de tiendas móviles ajenos al alcance web.</t>
+        <t>Trabajo propio aportado sin pago. Horas estimadas, valoradas con salario MTSS 2026 ÷30÷8. https://www.mtss.go.cr/temas-laborales/salarios/lista_salarios_minimos_2026.pdf</t>
       </text>
     </comment>
     <comment ref="D8" authorId="0" shapeId="0">
       <text>
-        <t>Fuente: Modelo de Costeo y Precio.xlsx; Costeo!B176.
-Estimación de trabajo pendiente presupuestado; no afirma funcionalidad terminada. Reemplaza rubros de tiendas móviles ajenos al alcance web.</t>
+        <t>Trabajo propio aportado sin pago. Horas estimadas, valoradas con salario MTSS 2026 ÷30÷8. https://www.mtss.go.cr/temas-laborales/salarios/lista_salarios_minimos_2026.pdf</t>
       </text>
     </comment>
     <comment ref="D9" authorId="0" shapeId="0">
       <text>
-        <t>Fuente: Modelo de Costeo y Precio.xlsx; Costeo!B177:B178.
-Estimación de trabajo pendiente presupuestado; no afirma funcionalidad terminada. Reemplaza rubros de tiendas móviles ajenos al alcance web.</t>
+        <t>Trabajo propio aportado sin pago. Horas estimadas, valoradas con salario MTSS 2026 ÷30÷8. https://www.mtss.go.cr/temas-laborales/salarios/lista_salarios_minimos_2026.pdf</t>
       </text>
     </comment>
     <comment ref="D10" authorId="0" shapeId="0">
       <text>
-        <t>Fuente: Modelo de Costeo y Precio.xlsx; Costeo!B179.
-Estimación de trabajo pendiente presupuestado; no afirma funcionalidad terminada. Reemplaza rubros de tiendas móviles ajenos al alcance web.</t>
+        <t>Trabajo propio aportado sin pago. Horas estimadas, valoradas con salario MTSS 2026 ÷30÷8. https://www.mtss.go.cr/temas-laborales/salarios/lista_salarios_minimos_2026.pdf</t>
       </text>
     </comment>
     <comment ref="D11" authorId="0" shapeId="0">
       <text>
-        <t>Fuente: Modelo de Costeo y Precio.xlsx; Costeo!B180.
-Estimación de trabajo pendiente presupuestado; no afirma funcionalidad terminada. Reemplaza rubros de tiendas móviles ajenos al alcance web.</t>
+        <t>Trabajo propio aportado sin pago. Horas estimadas, valoradas con salario MTSS 2026 ÷30÷8. https://www.mtss.go.cr/temas-laborales/salarios/lista_salarios_minimos_2026.pdf</t>
       </text>
     </comment>
     <comment ref="D17" authorId="0" shapeId="0">
@@ -1292,8 +1304,7 @@
     </comment>
     <comment ref="D18" authorId="0" shapeId="0">
       <text>
-        <t>Fuente: Modelo de Costeo y Precio.xlsx; Costeo!E103.
-Fijo común independiente del número de clientes; los excedentes se calculan aparte.</t>
+        <t>Estimación interna aprobada 17/09/2026; no cotización. Mes 1: 3 recorridos bus × 2 personas × ₡2 000 = ₡12 000; 2 en vehículo × ₡4 000 = ₡8 000; 1 combinado/taxi ₡8 000; comida 2 jornadas × 2 personas × ₡3 000 = ₡12 000. Total ₡40 000. Meses 2–12: 2 recorridos × 2 personas × ₡2 000 + ₡4 000 alimentación = ₡12 000/mes. Diez prospectos; conversión hipotética 50%, no ventas confirmadas. Tiempo: 6 o 2 recorridos × 3 h × 2 personas; no duplica soporte ni instalación.</t>
       </text>
     </comment>
     <comment ref="D19" authorId="0" shapeId="0">
@@ -1334,75 +1345,62 @@
     </comment>
     <comment ref="E35" authorId="0" shapeId="0">
       <text>
-        <t>Fuente: Modelo de Costeo y Precio.xlsx; Costeo!B129:C129; B22; B138:C149.
-Incluye servicio variable por mezcla, instalación básica de cada alta (₡40 000 absorbidos) y excedentes/escalamiento calculados con las cuotas del modelo. La reserva genérica de ₡750 no se utiliza. Alcance de esta hoja: 1 Starter y resto Pro Gym, hasta 10 000 miembros.
-Tarifas y cuotas copiadas del modelo vigente: Supabase 100 GB storage, 250 GB egress, 8 GB disco; adicionales 0,0213/0,09/0,125 USD respectivamente. Compute compartido por miembros y CDN Vercel por solicitudes según Costeo B138:C138. Estos umbrales son supuestos de dimensionamiento y no pruebas de carga.</t>
+        <t>Servicio por mezcla + altas de 8 h a referencia MTSS + nube de cartera. Trabajo propio sin pago; tarifas de nube conservadas del modelo. Estimación interna aprobada 17/09/2026; no cotización. Mes 1: 3 recorridos bus × 2 personas × ₡2 000 = ₡12 000; 2 en vehículo × ₡4 000 = ₡8 000; 1 combinado/taxi ₡8 000; comida 2 jornadas × 2 personas × ₡3 000 = ₡12 000. Total ₡40 000. Meses 2–12: 2 recorridos × 2 personas × ₡2 000 + ₡4 000 alimentación = ₡12 000/mes. Diez prospectos; conversión hipotética 50%, no ventas confirmadas. Tiempo: 6 o 2 recorridos × 3 h × 2 personas; no duplica soporte ni instalación.</t>
       </text>
     </comment>
     <comment ref="E36" authorId="0" shapeId="0">
       <text>
-        <t>Fuente: Modelo de Costeo y Precio.xlsx; Costeo!B129:C129; B22; B138:C149.
-Incluye servicio variable por mezcla, instalación básica de cada alta (₡40 000 absorbidos) y excedentes/escalamiento calculados con las cuotas del modelo. La reserva genérica de ₡750 no se utiliza. Alcance de esta hoja: 1 Starter y resto Pro Gym, hasta 10 000 miembros.</t>
+        <t>Servicio por mezcla + altas de 8 h a referencia MTSS + nube de cartera. Trabajo propio sin pago; tarifas de nube conservadas del modelo. Estimación interna aprobada 17/09/2026; no cotización. Mes 1: 3 recorridos bus × 2 personas × ₡2 000 = ₡12 000; 2 en vehículo × ₡4 000 = ₡8 000; 1 combinado/taxi ₡8 000; comida 2 jornadas × 2 personas × ₡3 000 = ₡12 000. Total ₡40 000. Meses 2–12: 2 recorridos × 2 personas × ₡2 000 + ₡4 000 alimentación = ₡12 000/mes. Diez prospectos; conversión hipotética 50%, no ventas confirmadas. Tiempo: 6 o 2 recorridos × 3 h × 2 personas; no duplica soporte ni instalación.</t>
       </text>
     </comment>
     <comment ref="E37" authorId="0" shapeId="0">
       <text>
-        <t>Fuente: Modelo de Costeo y Precio.xlsx; Costeo!B129:C129; B22; B138:C149.
-Incluye servicio variable por mezcla, instalación básica de cada alta (₡40 000 absorbidos) y excedentes/escalamiento calculados con las cuotas del modelo. La reserva genérica de ₡750 no se utiliza. Alcance de esta hoja: 1 Starter y resto Pro Gym, hasta 10 000 miembros.</t>
+        <t>Servicio por mezcla + altas de 8 h a referencia MTSS + nube de cartera. Trabajo propio sin pago; tarifas de nube conservadas del modelo. Estimación interna aprobada 17/09/2026; no cotización. Mes 1: 3 recorridos bus × 2 personas × ₡2 000 = ₡12 000; 2 en vehículo × ₡4 000 = ₡8 000; 1 combinado/taxi ₡8 000; comida 2 jornadas × 2 personas × ₡3 000 = ₡12 000. Total ₡40 000. Meses 2–12: 2 recorridos × 2 personas × ₡2 000 + ₡4 000 alimentación = ₡12 000/mes. Diez prospectos; conversión hipotética 50%, no ventas confirmadas. Tiempo: 6 o 2 recorridos × 3 h × 2 personas; no duplica soporte ni instalación.</t>
       </text>
     </comment>
     <comment ref="E38" authorId="0" shapeId="0">
       <text>
-        <t>Fuente: Modelo de Costeo y Precio.xlsx; Costeo!B129:C129; B22; B138:C149.
-Incluye servicio variable por mezcla, instalación básica de cada alta (₡40 000 absorbidos) y excedentes/escalamiento calculados con las cuotas del modelo. La reserva genérica de ₡750 no se utiliza. Alcance de esta hoja: 1 Starter y resto Pro Gym, hasta 10 000 miembros.</t>
+        <t>Servicio por mezcla + altas de 8 h a referencia MTSS + nube de cartera. Trabajo propio sin pago; tarifas de nube conservadas del modelo. Estimación interna aprobada 17/09/2026; no cotización. Mes 1: 3 recorridos bus × 2 personas × ₡2 000 = ₡12 000; 2 en vehículo × ₡4 000 = ₡8 000; 1 combinado/taxi ₡8 000; comida 2 jornadas × 2 personas × ₡3 000 = ₡12 000. Total ₡40 000. Meses 2–12: 2 recorridos × 2 personas × ₡2 000 + ₡4 000 alimentación = ₡12 000/mes. Diez prospectos; conversión hipotética 50%, no ventas confirmadas. Tiempo: 6 o 2 recorridos × 3 h × 2 personas; no duplica soporte ni instalación.</t>
       </text>
     </comment>
     <comment ref="E39" authorId="0" shapeId="0">
       <text>
-        <t>Fuente: Modelo de Costeo y Precio.xlsx; Costeo!B129:C129; B22; B138:C149.
-Incluye servicio variable por mezcla, instalación básica de cada alta (₡40 000 absorbidos) y excedentes/escalamiento calculados con las cuotas del modelo. La reserva genérica de ₡750 no se utiliza. Alcance de esta hoja: 1 Starter y resto Pro Gym, hasta 10 000 miembros.</t>
+        <t>Servicio por mezcla + altas de 8 h a referencia MTSS + nube de cartera. Trabajo propio sin pago; tarifas de nube conservadas del modelo. Estimación interna aprobada 17/09/2026; no cotización. Mes 1: 3 recorridos bus × 2 personas × ₡2 000 = ₡12 000; 2 en vehículo × ₡4 000 = ₡8 000; 1 combinado/taxi ₡8 000; comida 2 jornadas × 2 personas × ₡3 000 = ₡12 000. Total ₡40 000. Meses 2–12: 2 recorridos × 2 personas × ₡2 000 + ₡4 000 alimentación = ₡12 000/mes. Diez prospectos; conversión hipotética 50%, no ventas confirmadas. Tiempo: 6 o 2 recorridos × 3 h × 2 personas; no duplica soporte ni instalación.</t>
       </text>
     </comment>
     <comment ref="E40" authorId="0" shapeId="0">
       <text>
-        <t>Fuente: Modelo de Costeo y Precio.xlsx; Costeo!B129:C129; B22; B138:C149.
-Incluye servicio variable por mezcla, instalación básica de cada alta (₡40 000 absorbidos) y excedentes/escalamiento calculados con las cuotas del modelo. La reserva genérica de ₡750 no se utiliza. Alcance de esta hoja: 1 Starter y resto Pro Gym, hasta 10 000 miembros.</t>
+        <t>Servicio por mezcla + altas de 8 h a referencia MTSS + nube de cartera. Trabajo propio sin pago; tarifas de nube conservadas del modelo. Estimación interna aprobada 17/09/2026; no cotización. Mes 1: 3 recorridos bus × 2 personas × ₡2 000 = ₡12 000; 2 en vehículo × ₡4 000 = ₡8 000; 1 combinado/taxi ₡8 000; comida 2 jornadas × 2 personas × ₡3 000 = ₡12 000. Total ₡40 000. Meses 2–12: 2 recorridos × 2 personas × ₡2 000 + ₡4 000 alimentación = ₡12 000/mes. Diez prospectos; conversión hipotética 50%, no ventas confirmadas. Tiempo: 6 o 2 recorridos × 3 h × 2 personas; no duplica soporte ni instalación.</t>
       </text>
     </comment>
     <comment ref="E41" authorId="0" shapeId="0">
       <text>
-        <t>Fuente: Modelo de Costeo y Precio.xlsx; Costeo!B129:C129; B22; B138:C149.
-Incluye servicio variable por mezcla, instalación básica de cada alta (₡40 000 absorbidos) y excedentes/escalamiento calculados con las cuotas del modelo. La reserva genérica de ₡750 no se utiliza. Alcance de esta hoja: 1 Starter y resto Pro Gym, hasta 10 000 miembros.</t>
+        <t>Servicio por mezcla + altas de 8 h a referencia MTSS + nube de cartera. Trabajo propio sin pago; tarifas de nube conservadas del modelo. Estimación interna aprobada 17/09/2026; no cotización. Mes 1: 3 recorridos bus × 2 personas × ₡2 000 = ₡12 000; 2 en vehículo × ₡4 000 = ₡8 000; 1 combinado/taxi ₡8 000; comida 2 jornadas × 2 personas × ₡3 000 = ₡12 000. Total ₡40 000. Meses 2–12: 2 recorridos × 2 personas × ₡2 000 + ₡4 000 alimentación = ₡12 000/mes. Diez prospectos; conversión hipotética 50%, no ventas confirmadas. Tiempo: 6 o 2 recorridos × 3 h × 2 personas; no duplica soporte ni instalación.</t>
       </text>
     </comment>
     <comment ref="E42" authorId="0" shapeId="0">
       <text>
-        <t>Fuente: Modelo de Costeo y Precio.xlsx; Costeo!B129:C129; B22; B138:C149.
-Incluye servicio variable por mezcla, instalación básica de cada alta (₡40 000 absorbidos) y excedentes/escalamiento calculados con las cuotas del modelo. La reserva genérica de ₡750 no se utiliza. Alcance de esta hoja: 1 Starter y resto Pro Gym, hasta 10 000 miembros.</t>
+        <t>Servicio por mezcla + altas de 8 h a referencia MTSS + nube de cartera. Trabajo propio sin pago; tarifas de nube conservadas del modelo. Estimación interna aprobada 17/09/2026; no cotización. Mes 1: 3 recorridos bus × 2 personas × ₡2 000 = ₡12 000; 2 en vehículo × ₡4 000 = ₡8 000; 1 combinado/taxi ₡8 000; comida 2 jornadas × 2 personas × ₡3 000 = ₡12 000. Total ₡40 000. Meses 2–12: 2 recorridos × 2 personas × ₡2 000 + ₡4 000 alimentación = ₡12 000/mes. Diez prospectos; conversión hipotética 50%, no ventas confirmadas. Tiempo: 6 o 2 recorridos × 3 h × 2 personas; no duplica soporte ni instalación.</t>
       </text>
     </comment>
     <comment ref="E43" authorId="0" shapeId="0">
       <text>
-        <t>Fuente: Modelo de Costeo y Precio.xlsx; Costeo!B129:C129; B22; B138:C149.
-Incluye servicio variable por mezcla, instalación básica de cada alta (₡40 000 absorbidos) y excedentes/escalamiento calculados con las cuotas del modelo. La reserva genérica de ₡750 no se utiliza. Alcance de esta hoja: 1 Starter y resto Pro Gym, hasta 10 000 miembros.</t>
+        <t>Servicio por mezcla + altas de 8 h a referencia MTSS + nube de cartera. Trabajo propio sin pago; tarifas de nube conservadas del modelo. Estimación interna aprobada 17/09/2026; no cotización. Mes 1: 3 recorridos bus × 2 personas × ₡2 000 = ₡12 000; 2 en vehículo × ₡4 000 = ₡8 000; 1 combinado/taxi ₡8 000; comida 2 jornadas × 2 personas × ₡3 000 = ₡12 000. Total ₡40 000. Meses 2–12: 2 recorridos × 2 personas × ₡2 000 + ₡4 000 alimentación = ₡12 000/mes. Diez prospectos; conversión hipotética 50%, no ventas confirmadas. Tiempo: 6 o 2 recorridos × 3 h × 2 personas; no duplica soporte ni instalación.</t>
       </text>
     </comment>
     <comment ref="E44" authorId="0" shapeId="0">
       <text>
-        <t>Fuente: Modelo de Costeo y Precio.xlsx; Costeo!B129:C129; B22; B138:C149.
-Incluye servicio variable por mezcla, instalación básica de cada alta (₡40 000 absorbidos) y excedentes/escalamiento calculados con las cuotas del modelo. La reserva genérica de ₡750 no se utiliza. Alcance de esta hoja: 1 Starter y resto Pro Gym, hasta 10 000 miembros.</t>
+        <t>Servicio por mezcla + altas de 8 h a referencia MTSS + nube de cartera. Trabajo propio sin pago; tarifas de nube conservadas del modelo. Estimación interna aprobada 17/09/2026; no cotización. Mes 1: 3 recorridos bus × 2 personas × ₡2 000 = ₡12 000; 2 en vehículo × ₡4 000 = ₡8 000; 1 combinado/taxi ₡8 000; comida 2 jornadas × 2 personas × ₡3 000 = ₡12 000. Total ₡40 000. Meses 2–12: 2 recorridos × 2 personas × ₡2 000 + ₡4 000 alimentación = ₡12 000/mes. Diez prospectos; conversión hipotética 50%, no ventas confirmadas. Tiempo: 6 o 2 recorridos × 3 h × 2 personas; no duplica soporte ni instalación.</t>
       </text>
     </comment>
     <comment ref="E45" authorId="0" shapeId="0">
       <text>
-        <t>Fuente: Modelo de Costeo y Precio.xlsx; Costeo!B129:C129; B22; B138:C149.
-Incluye servicio variable por mezcla, instalación básica de cada alta (₡40 000 absorbidos) y excedentes/escalamiento calculados con las cuotas del modelo. La reserva genérica de ₡750 no se utiliza. Alcance de esta hoja: 1 Starter y resto Pro Gym, hasta 10 000 miembros.</t>
+        <t>Servicio por mezcla + altas de 8 h a referencia MTSS + nube de cartera. Trabajo propio sin pago; tarifas de nube conservadas del modelo. Estimación interna aprobada 17/09/2026; no cotización. Mes 1: 3 recorridos bus × 2 personas × ₡2 000 = ₡12 000; 2 en vehículo × ₡4 000 = ₡8 000; 1 combinado/taxi ₡8 000; comida 2 jornadas × 2 personas × ₡3 000 = ₡12 000. Total ₡40 000. Meses 2–12: 2 recorridos × 2 personas × ₡2 000 + ₡4 000 alimentación = ₡12 000/mes. Diez prospectos; conversión hipotética 50%, no ventas confirmadas. Tiempo: 6 o 2 recorridos × 3 h × 2 personas; no duplica soporte ni instalación.</t>
       </text>
     </comment>
     <comment ref="E46" authorId="0" shapeId="0">
       <text>
-        <t>Fuente: Modelo de Costeo y Precio.xlsx; Costeo!B129:C129; B22; B138:C149.
-Incluye servicio variable por mezcla, instalación básica de cada alta (₡40 000 absorbidos) y excedentes/escalamiento calculados con las cuotas del modelo. La reserva genérica de ₡750 no se utiliza. Alcance de esta hoja: 1 Starter y resto Pro Gym, hasta 10 000 miembros.</t>
+        <t>Servicio por mezcla + altas de 8 h a referencia MTSS + nube de cartera. Trabajo propio sin pago; tarifas de nube conservadas del modelo. Estimación interna aprobada 17/09/2026; no cotización. Mes 1: 3 recorridos bus × 2 personas × ₡2 000 = ₡12 000; 2 en vehículo × ₡4 000 = ₡8 000; 1 combinado/taxi ₡8 000; comida 2 jornadas × 2 personas × ₡3 000 = ₡12 000. Total ₡40 000. Meses 2–12: 2 recorridos × 2 personas × ₡2 000 + ₡4 000 alimentación = ₡12 000/mes. Diez prospectos; conversión hipotética 50%, no ventas confirmadas. Tiempo: 6 o 2 recorridos × 3 h × 2 personas; no duplica soporte ni instalación.</t>
       </text>
     </comment>
   </commentList>
@@ -1433,12 +1431,22 @@
   <commentList>
     <comment ref="C9" authorId="0" shapeId="0">
       <text>
-        <t>Financiamiento económico máximo: déficit acumulado de ingresos menos todos los costos, antes de aporte. Supone pagar el trabajo propio. No equivale a una aportación ya confirmada.</t>
+        <t>Liquidez mínima = mayor entre ₡40 000 para viáticos anteriores a primeras ventas y el déficit mensual de efectivo. No duplica gasto: el aporte financia los viáticos ya incluidos en egresos. Trabajo propio sin pago. Otros cobros y pagos se suponen dentro del mismo mes.</t>
+      </text>
+    </comment>
+    <comment ref="C29" authorId="0" shapeId="0">
+      <text>
+        <t>Escenario condicionado: Pulso aún sin registro. Beneficio exige inscripción tributaria en régimen general y registro micro/pequeña ante MEIC o MAG. 0% del impuesto determinado años 1–3; 25% años 4–5; 50% año 6. Primer año desde inscripción tributaria. No es tasa sobre ventas ni concede exención de otros tributos. Fuente: https://www.hacienda.go.cr/docs/BeneficiosPymes1.pdf</t>
       </text>
     </comment>
     <comment ref="C38" authorId="0" shapeId="0">
       <text>
         <t>El modelo reconoce todo el desarrollo como costo del año para mantener consistencia con Modelo de Costeo y Precio.xlsx. No se registra simultáneamente un activo ni amortización de ese gasto.</t>
+      </text>
+    </comment>
+    <comment ref="F38" authorId="0" shapeId="0">
+      <text>
+        <t>Balance gerencial: aporte económico del trabajo propio (no capital social legal ni deuda) más aporte de efectivo. Todo desarrollo es gasto del año; no activo duplicado.</t>
       </text>
     </comment>
   </commentList>
@@ -1786,19 +1794,19 @@
   <dimension ref="B2:M15"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
   <cols>
-    <col width="3" customWidth="1" min="1" max="1"/>
-    <col width="24" customWidth="1" min="2" max="2"/>
-    <col width="29" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="5"/>
-    <col width="26" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="8"/>
-    <col width="23" customWidth="1" min="9" max="9"/>
-    <col width="12" customWidth="1" min="10" max="11"/>
-    <col width="28" customWidth="1" min="12" max="12"/>
-    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="3" customWidth="1" style="51" min="1" max="1"/>
+    <col width="24" customWidth="1" style="51" min="2" max="2"/>
+    <col width="29" customWidth="1" style="51" min="3" max="3"/>
+    <col width="12" customWidth="1" style="51" min="4" max="5"/>
+    <col width="26" customWidth="1" style="51" min="6" max="6"/>
+    <col width="12" customWidth="1" style="51" min="7" max="8"/>
+    <col width="23" customWidth="1" style="51" min="9" max="9"/>
+    <col width="12" customWidth="1" style="51" min="10" max="11"/>
+    <col width="28" customWidth="1" style="51" min="12" max="12"/>
+    <col width="12" customWidth="1" style="51" min="13" max="13"/>
   </cols>
   <sheetData>
-    <row r="2" ht="21" customHeight="1">
+    <row r="2" ht="21" customHeight="1" s="51">
       <c r="B2" s="1" t="inlineStr">
         <is>
           <t>PULSO: ANÁLISIS ECONÓMICO DEL SERVICIO SaaS</t>
@@ -1808,59 +1816,59 @@
     <row r="3">
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Escenario de 12 meses · Starter + Pro Gym · cifras CRC, antes de impuestos</t>
+          <t>Cartera Starter + Pro Gym · costo económico y efectivo separados · beneficio MYPE condicionado</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="C4" s="43" t="inlineStr">
+      <c r="C4" s="45" t="inlineStr">
         <is>
           <t>GIMNASIOS AL CIERRE</t>
         </is>
       </c>
-      <c r="D4" s="53" t="n"/>
-      <c r="F4" s="43" t="inlineStr">
+      <c r="D4" s="46" t="n"/>
+      <c r="F4" s="45" t="inlineStr">
         <is>
           <t>INGRESOS TOTALES AÑO 1</t>
         </is>
       </c>
-      <c r="G4" s="53" t="n"/>
-      <c r="I4" s="43" t="inlineStr">
+      <c r="G4" s="46" t="n"/>
+      <c r="I4" s="45" t="inlineStr">
         <is>
           <t>EQUILIBRIO OPERATIVO</t>
         </is>
       </c>
-      <c r="J4" s="53" t="n"/>
-      <c r="L4" s="43" t="inlineStr">
-        <is>
-          <t>FINANCIAMIENTO REQUERIDO</t>
-        </is>
-      </c>
-      <c r="M4" s="53" t="n"/>
+      <c r="J4" s="46" t="n"/>
+      <c r="L4" s="45" t="inlineStr">
+        <is>
+          <t>LIQUIDEZ INICIAL MÍNIMA</t>
+        </is>
+      </c>
+      <c r="M4" s="46" t="n"/>
     </row>
     <row r="5">
-      <c r="C5" s="47">
+      <c r="C5" s="57">
         <f>'Clientes e Ingresos'!F17</f>
         <v>14.0</v>
       </c>
-      <c r="D5" s="53" t="n"/>
-      <c r="F5" s="46">
+      <c r="D5" s="46" t="n"/>
+      <c r="F5" s="56">
         <f>'Clientes e Ingresos'!H18</f>
         <v>2780000.0</v>
       </c>
-      <c r="G5" s="53" t="n"/>
-      <c r="I5" s="47">
+      <c r="G5" s="46" t="n"/>
+      <c r="I5" s="57">
         <f>'Punto de Equilibrio'!D13</f>
-        <v>5</v>
-      </c>
-      <c r="J5" s="53" t="n"/>
-      <c r="L5" s="46">
+        <v>6</v>
+      </c>
+      <c r="J5" s="46" t="n"/>
+      <c r="L5" s="56">
         <f>'Estados Financieros'!C9</f>
-        <v>679165.99</v>
-      </c>
-      <c r="M5" s="53" t="n"/>
-    </row>
-    <row r="8" ht="17.4" customHeight="1">
+        <v>40000</v>
+      </c>
+      <c r="M5" s="46" t="n"/>
+    </row>
+    <row r="8" ht="17.4" customHeight="1" s="51">
       <c r="B8" s="3" t="inlineStr">
         <is>
           <t>RESUMEN DEL PROYECTO</t>
@@ -1868,60 +1876,60 @@
       </c>
     </row>
     <row r="9">
-      <c r="B9" s="45" t="str">
-        <f>"Pulso es un servicio web para gestionar gimnasios. Escenario comercial proyectado, no ventas confirmadas."&amp;CHAR(10)&amp;CHAR(10)&amp;"• Starter ₡15 000; Pro Gym ₡25 000; Premium dedicado ₡45 000; Enterprise desde ₡70 000."&amp;CHAR(10)&amp;"• Cartera: 1 Starter y el resto Pro; "&amp;'Clientes e Ingresos'!F17&amp;" activos al cierre. Instalación básica: ₡40 000 por alta, absorbidos por Pulso."&amp;CHAR(10)&amp;"• Fijo común: ₡"&amp;TEXT('Egresos e Inversión'!D22,"#,##0")&amp;"/mes. Desarrollo inicial: ₡"&amp;TEXT('Egresos e Inversión'!D12,"#,##0")&amp;"."&amp;CHAR(10)&amp;"• Resultado anual antes de impuestos: ₡"&amp;TEXT('Estados Financieros'!C30,"#,##0.00")&amp;". El equilibrio operativo no equivale a recuperar la inversión."&amp;CHAR(10)&amp;"• Premium/Enterprise sin ventas en esta cartera; instalación cobrada ₡129 000/₡258 000. Capacidades avanzadas presupuestadas requieren implementación y pruebas."</f>
-        <v>Pulso es un servicio web para gestionar gimnasios. Escenario comercial proyectado, no ventas confirmadas.
-• Starter ₡15 000; Pro Gym ₡25 000; Premium dedicado ₡45 000; Enterprise desde ₡70 000.
-• Cartera: 1 Starter y el resto Pro; 14 activos al cierre. Instalación básica: ₡40 000 por alta, absorbidos por Pulso.
-• Fijo común: ₡91,125/mes. Desarrollo inicial: ₡480,000.
-• Resultado anual antes de impuestos: ₡124,983.56. El equilibrio operativo no equivale a recuperar la inversión.
-• Premium/Enterprise sin ventas en esta cartera; instalación cobrada ₡129 000/₡258 000. Capacidades avanzadas presupuestadas requieren implementación y pruebas.</v>
-      </c>
-      <c r="C9" s="54" t="n"/>
-      <c r="D9" s="54" t="n"/>
-      <c r="E9" s="54" t="n"/>
-      <c r="F9" s="54" t="n"/>
-      <c r="G9" s="54" t="n"/>
-      <c r="H9" s="54" t="n"/>
-      <c r="I9" s="54" t="n"/>
-      <c r="J9" s="54" t="n"/>
-      <c r="K9" s="54" t="n"/>
-      <c r="L9" s="54" t="n"/>
-      <c r="M9" s="55" t="n"/>
+      <c r="B9" s="47" t="str">
+        <f>"Pulso: escenario de 1 Starter y el resto Pro Gym; "&amp;'Clientes e Ingresos'!F17&amp;" activos al cierre. No son ventas confirmadas."&amp;CHAR(10)&amp;"• Viáticos: ₡40 000 mes 1; ₡12 000/mes después. Diez prospectos, meta cinco altas iniciales."&amp;CHAR(10)&amp;"• Hora técnica: salario MTSS ₡496 838,17 ÷30÷8. Trabajo propio aportado sin pago."&amp;CHAR(10)&amp;"• Desarrollo: ₡"&amp;TEXT('Egresos e Inversión'!D12,"#,##0.00")&amp;" de costo económico; no desembolso inicial."&amp;CHAR(10)&amp;"• Resultado económico anual: ₡"&amp;TEXT('Estados Financieros'!C30,"#,##0.00")&amp;". Renta 0 condicionada a formalización MYPE."&amp;CHAR(10)&amp;"• Precios de venta conservados. Equilibrio mensual distinto de recuperar el trabajo invertido."</f>
+        <v>Pulso: escenario de 1 Starter y el resto Pro Gym; 14 activos al cierre. No son ventas confirmadas.
+• Viáticos: ₡40 000 mes 1; ₡12 000/mes después. Diez prospectos, meta cinco altas iniciales.
+• Hora técnica: salario MTSS ₡496 838,17 ÷30÷8. Trabajo propio aportado sin pago.
+• Desarrollo: ₡198,735.27 de costo económico; no desembolso inicial.
+• Resultado económico anual: ₡596,044.36. Renta 0 condicionada a formalización MYPE.
+• Precios de venta conservados. Equilibrio mensual distinto de recuperar el trabajo invertido.</v>
+      </c>
+      <c r="C9" s="48" t="n"/>
+      <c r="D9" s="48" t="n"/>
+      <c r="E9" s="48" t="n"/>
+      <c r="F9" s="48" t="n"/>
+      <c r="G9" s="48" t="n"/>
+      <c r="H9" s="48" t="n"/>
+      <c r="I9" s="48" t="n"/>
+      <c r="J9" s="48" t="n"/>
+      <c r="K9" s="48" t="n"/>
+      <c r="L9" s="48" t="n"/>
+      <c r="M9" s="49" t="n"/>
     </row>
     <row r="10">
-      <c r="B10" s="56" t="n"/>
-      <c r="M10" s="57" t="n"/>
+      <c r="B10" s="50" t="n"/>
+      <c r="M10" s="52" t="n"/>
     </row>
     <row r="11">
-      <c r="B11" s="56" t="n"/>
-      <c r="M11" s="57" t="n"/>
+      <c r="B11" s="50" t="n"/>
+      <c r="M11" s="52" t="n"/>
     </row>
     <row r="12">
-      <c r="B12" s="56" t="n"/>
-      <c r="M12" s="57" t="n"/>
+      <c r="B12" s="50" t="n"/>
+      <c r="M12" s="52" t="n"/>
     </row>
     <row r="13">
-      <c r="B13" s="56" t="n"/>
-      <c r="M13" s="57" t="n"/>
+      <c r="B13" s="50" t="n"/>
+      <c r="M13" s="52" t="n"/>
     </row>
     <row r="14">
-      <c r="B14" s="56" t="n"/>
-      <c r="M14" s="57" t="n"/>
+      <c r="B14" s="50" t="n"/>
+      <c r="M14" s="52" t="n"/>
     </row>
     <row r="15">
-      <c r="B15" s="58" t="n"/>
-      <c r="C15" s="59" t="n"/>
-      <c r="D15" s="59" t="n"/>
-      <c r="E15" s="59" t="n"/>
-      <c r="F15" s="59" t="n"/>
-      <c r="G15" s="59" t="n"/>
-      <c r="H15" s="59" t="n"/>
-      <c r="I15" s="59" t="n"/>
-      <c r="J15" s="59" t="n"/>
-      <c r="K15" s="59" t="n"/>
-      <c r="L15" s="59" t="n"/>
-      <c r="M15" s="60" t="n"/>
+      <c r="B15" s="53" t="n"/>
+      <c r="C15" s="54" t="n"/>
+      <c r="D15" s="54" t="n"/>
+      <c r="E15" s="54" t="n"/>
+      <c r="F15" s="54" t="n"/>
+      <c r="G15" s="54" t="n"/>
+      <c r="H15" s="54" t="n"/>
+      <c r="I15" s="54" t="n"/>
+      <c r="J15" s="54" t="n"/>
+      <c r="K15" s="54" t="n"/>
+      <c r="L15" s="54" t="n"/>
+      <c r="M15" s="55" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="9">
@@ -1950,15 +1958,15 @@
   <dimension ref="B2:I18"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
-    <col width="22" customWidth="1" min="8" max="9"/>
+    <col width="12" customWidth="1" style="51" min="1" max="2"/>
+    <col width="20" customWidth="1" style="51" min="3" max="3"/>
+    <col width="18" customWidth="1" style="51" min="4" max="4"/>
+    <col width="22" customWidth="1" style="51" min="5" max="6"/>
+    <col width="18" customWidth="1" style="51" min="7" max="7"/>
+    <col width="22" customWidth="1" style="51" min="8" max="9"/>
   </cols>
   <sheetData>
-    <row r="2" ht="21" customHeight="1">
+    <row r="2" ht="21" customHeight="1" s="51">
       <c r="B2" s="1" t="inlineStr">
         <is>
           <t>PROYECCIÓN DE CLIENTES E INGRESOS (MRR)</t>
@@ -1972,7 +1980,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="28.8" customHeight="1">
+    <row r="5" ht="28.8" customHeight="1" s="51">
       <c r="B5" s="4" t="inlineStr">
         <is>
           <t>Mes</t>
@@ -2459,13 +2467,13 @@
   <dimension ref="B2:F47"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="32" customWidth="1" min="2" max="2"/>
-    <col width="60" customWidth="1" min="3" max="3"/>
-    <col width="24" customWidth="1" min="4" max="6"/>
+    <col width="12" customWidth="1" style="51" min="1" max="1"/>
+    <col width="32" customWidth="1" style="51" min="2" max="2"/>
+    <col width="60" customWidth="1" style="51" min="3" max="3"/>
+    <col width="24" customWidth="1" style="51" min="4" max="6"/>
   </cols>
   <sheetData>
-    <row r="2" ht="21" customHeight="1">
+    <row r="2" ht="21" customHeight="1" s="51">
       <c r="B2" s="1" t="inlineStr">
         <is>
           <t>PRESUPUESTO DE EGRESOS E INVERSIÓN INICIAL</t>
@@ -2475,11 +2483,11 @@
     <row r="3">
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Costo económico: trabajo técnico valorado a ₡5 000/h. Flujo supone pagarlo íntegro; fuente: modelo de costeo.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="17.4" customHeight="1">
+          <t>Costos económicos: trabajo propio valorado con MTSS 2026; aportado sin pago. Viáticos iniciales y recurrentes diferenciados.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="17.4" customHeight="1" s="51">
       <c r="B5" s="3" t="inlineStr">
         <is>
           <t>1. DESARROLLO INICIAL (UNA SOLA VEZ)</t>
@@ -2504,83 +2512,83 @@
       </c>
     </row>
     <row r="7">
-      <c r="B7" s="49" t="inlineStr">
+      <c r="B7" s="59" t="inlineStr">
         <is>
           <t>Aislamiento de gimnasios</t>
         </is>
       </c>
-      <c r="C7" s="49" t="inlineStr">
+      <c r="C7" s="59" t="inlineStr">
         <is>
           <t>Permisos y separación multiempresa: 24 h</t>
         </is>
       </c>
       <c r="D7" s="7">
-        <f>24*5000</f>
-        <v>120000.0</v>
+        <f>24*(496838.17/30/8)</f>
+        <v>49683.817</v>
       </c>
     </row>
     <row r="8">
-      <c r="B8" s="49" t="inlineStr">
+      <c r="B8" s="59" t="inlineStr">
         <is>
           <t>Autenticación dedicada</t>
         </is>
       </c>
-      <c r="C8" s="49" t="inlineStr">
+      <c r="C8" s="59" t="inlineStr">
         <is>
           <t>Ruteo de usuarios a bases dedicadas: 24 h</t>
         </is>
       </c>
       <c r="D8" s="7">
-        <f>24*5000</f>
-        <v>120000.0</v>
+        <f>24*(496838.17/30/8)</f>
+        <v>49683.817</v>
       </c>
     </row>
     <row r="9">
-      <c r="B9" s="49" t="inlineStr">
+      <c r="B9" s="59" t="inlineStr">
         <is>
           <t>Personalización y cupos</t>
         </is>
       </c>
-      <c r="C9" s="49" t="inlineStr">
+      <c r="C9" s="59" t="inlineStr">
         <is>
           <t>Marca/subdominios 12 h + límites de archivos e IA 8 h</t>
         </is>
       </c>
       <c r="D9" s="7">
-        <f>20*5000</f>
-        <v>100000.0</v>
+        <f>20*(496838.17/30/8)</f>
+        <v>41403.18083333333</v>
       </c>
     </row>
     <row r="10">
-      <c r="B10" s="49" t="inlineStr">
+      <c r="B10" s="59" t="inlineStr">
         <is>
           <t>Mensajería y tareas</t>
         </is>
       </c>
-      <c r="C10" s="49" t="inlineStr">
+      <c r="C10" s="59" t="inlineStr">
         <is>
           <t>SES, Redis y worker: 12 h</t>
         </is>
       </c>
       <c r="D10" s="7">
-        <f>12*5000</f>
-        <v>60000.0</v>
+        <f>12*(496838.17/30/8)</f>
+        <v>24841.9085</v>
       </c>
     </row>
     <row r="11">
-      <c r="B11" s="49" t="inlineStr">
+      <c r="B11" s="59" t="inlineStr">
         <is>
           <t>Pruebas y entrega</t>
         </is>
       </c>
-      <c r="C11" s="49" t="inlineStr">
+      <c r="C11" s="59" t="inlineStr">
         <is>
           <t>Aislamiento, carga y documentación: 16 h</t>
         </is>
       </c>
       <c r="D11" s="7">
-        <f>16*5000</f>
-        <v>80000.0</v>
+        <f>16*(496838.17/30/8)</f>
+        <v>33122.54466666667</v>
       </c>
     </row>
     <row r="12">
@@ -2592,10 +2600,10 @@
       <c r="C12" s="19" t="n"/>
       <c r="D12" s="15">
         <f>SUM(D7:D11)</f>
-        <v>480000.0</v>
-      </c>
-    </row>
-    <row r="15" ht="17.4" customHeight="1">
+        <v>198735.26799999998</v>
+      </c>
+    </row>
+    <row r="15" ht="17.4" customHeight="1" s="51">
       <c r="B15" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">2. GASTOS OPERATIVOS FIJOS MENSUALES </t>
@@ -2620,12 +2628,12 @@
       </c>
     </row>
     <row r="17">
-      <c r="B17" s="49" t="inlineStr">
+      <c r="B17" s="59" t="inlineStr">
         <is>
           <t>Infraestructura y dominio</t>
         </is>
       </c>
-      <c r="C17" s="49" t="inlineStr">
+      <c r="C17" s="59" t="inlineStr">
         <is>
           <t>Vercel + Supabase + API + dominio + Redis + worker + workspace</t>
         </is>
@@ -2636,28 +2644,28 @@
       </c>
     </row>
     <row r="18">
-      <c r="B18" s="49" t="inlineStr">
+      <c r="B18" s="59" t="inlineStr">
         <is>
           <t>Transporte y viáticos</t>
         </is>
       </c>
-      <c r="C18" s="49" t="inlineStr">
-        <is>
-          <t>Visitas comerciales presupuestadas</t>
+      <c r="C18" s="59" t="inlineStr">
+        <is>
+          <t>Mes 1 ₡40 000; después ₡12 000/mes</t>
         </is>
       </c>
       <c r="D18" s="7">
-        <f>2000</f>
-        <v>2000</v>
+        <f>2*2*2000+4000</f>
+        <v>12000.0</v>
       </c>
     </row>
     <row r="19">
-      <c r="B19" s="49" t="inlineStr">
+      <c r="B19" s="59" t="inlineStr">
         <is>
           <t>Publicidad digital</t>
         </is>
       </c>
-      <c r="C19" s="49" t="inlineStr">
+      <c r="C19" s="59" t="inlineStr">
         <is>
           <t>Anuncios para validación comercial</t>
         </is>
@@ -2668,12 +2676,12 @@
       </c>
     </row>
     <row r="20">
-      <c r="B20" s="49" t="inlineStr">
+      <c r="B20" s="59" t="inlineStr">
         <is>
           <t>Correo y diseño</t>
         </is>
       </c>
-      <c r="C20" s="49" t="inlineStr">
+      <c r="C20" s="59" t="inlineStr">
         <is>
           <t>Workspace: US$7; diseño: US$5; cambio ₡500/USD</t>
         </is>
@@ -2684,23 +2692,23 @@
       </c>
     </row>
     <row r="21">
-      <c r="B21" s="50" t="inlineStr">
-        <is>
-          <t>Mantenimiento técnico</t>
-        </is>
-      </c>
-      <c r="C21" s="50" t="inlineStr">
-        <is>
-          <t>4 horas mensuales a ₡5 000/h</t>
-        </is>
-      </c>
-      <c r="D21" s="51">
-        <f>4*5000</f>
-        <v>20000.0</v>
+      <c r="B21" s="29" t="inlineStr">
+        <is>
+          <t>Mantenimiento y captación</t>
+        </is>
+      </c>
+      <c r="C21" s="29" t="inlineStr">
+        <is>
+          <t>4 h mantenimiento + 12 h comerciales/mes</t>
+        </is>
+      </c>
+      <c r="D21" s="43">
+        <f>(4+2*3*2)*(496838.17/30/8)</f>
+        <v>33122.54466666667</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Incluye trabajo propio valorado; no se excluyen honorarios para aparentar rentabilidad.</t>
+          <t>Mes 1: 36 h comerciales; meses 2–12: 12 h. Aporte del equipo sin pago, no deuda.</t>
         </is>
       </c>
     </row>
@@ -2713,10 +2721,10 @@
       <c r="C22" s="19" t="n"/>
       <c r="D22" s="15">
         <f>SUM(D17:D21)</f>
-        <v>91125.0</v>
-      </c>
-    </row>
-    <row r="25" ht="17.4" customHeight="1">
+        <v>114247.54466666667</v>
+      </c>
+    </row>
+    <row r="25" ht="17.4" customHeight="1" s="51">
       <c r="B25" s="3" t="inlineStr">
         <is>
           <t>3. VARIABLE UNITARIO: MEZCLA INICIAL</t>
@@ -2741,28 +2749,28 @@
       </c>
     </row>
     <row r="27">
-      <c r="B27" s="49" t="inlineStr">
+      <c r="B27" s="59" t="inlineStr">
         <is>
           <t>Soporte mensual</t>
         </is>
       </c>
-      <c r="C27" s="49" t="inlineStr">
-        <is>
-          <t>0,5 h por gimnasio × ₡5 000/h</t>
+      <c r="C27" s="59" t="inlineStr">
+        <is>
+          <t>0,5 h × referencia MTSS por hora</t>
         </is>
       </c>
       <c r="D27" s="7">
-        <f>0.5*5000</f>
-        <v>2500.0</v>
+        <f>0.5*(496838.17/30/8)</f>
+        <v>1035.0795208333334</v>
       </c>
     </row>
     <row r="28">
-      <c r="B28" s="49" t="inlineStr">
+      <c r="B28" s="59" t="inlineStr">
         <is>
           <t>Correo e IA</t>
         </is>
       </c>
-      <c r="C28" s="49" t="inlineStr">
+      <c r="C28" s="59" t="inlineStr">
         <is>
           <t>SES + GPT-4.1 mini; ponderado por miembros de la mezcla</t>
         </is>
@@ -2773,12 +2781,12 @@
       </c>
     </row>
     <row r="29">
-      <c r="B29" s="49" t="inlineStr">
+      <c r="B29" s="59" t="inlineStr">
         <is>
           <t>Comisiones</t>
         </is>
       </c>
-      <c r="C29" s="49" t="inlineStr">
+      <c r="C29" s="59" t="inlineStr">
         <is>
           <t>Transferencia sin pasarela contratada</t>
         </is>
@@ -2797,7 +2805,7 @@
       <c r="C30" s="19" t="n"/>
       <c r="D30" s="15">
         <f>SUM(D27:D29)</f>
-        <v>2896.558</v>
+        <v>1431.6375208333334</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
@@ -2805,7 +2813,7 @@
         </is>
       </c>
     </row>
-    <row r="33" ht="17.4" customHeight="1">
+    <row r="33" ht="17.4" customHeight="1" s="51">
       <c r="B33" s="3" t="inlineStr">
         <is>
           <t>4. PROYECCIÓN MENSUAL DE EGRESOS (AÑO 1)</t>
@@ -2850,16 +2858,16 @@
         <v>5.0</v>
       </c>
       <c r="D35" s="7">
-        <f>$D$22</f>
-        <v>91125.0</v>
+        <f>$D$22+(3*2*2000+2*4000+8000+2*2*3000-$D$18)+(6*3*2-2*3*2)*(496838.17/30/8)</f>
+        <v>191931.36166666666</v>
       </c>
       <c r="E35" s="7">
-        <f>ROUND(C35*$D$27+(ROUND((((80*2+20)*0.16/1000+(80*2+20)*32/1000000*0.12)*500),2)+80*2*(4000*0.4+300*1.6)/1000000*500+MAX(0,C35-1)*(ROUND((((200*2+20)*0.16/1000+(200*2+20)*32/1000000*0.12)*500),2)+200*2*(4000*0.4+300*1.6)/1000000*500))+C35*$D$29+'Clientes e Ingresos'!D6*(8*5000)+(ROUND((MAX(0,((1)*1+(MAX(0,C35-1))*3+(0)*8+(0)*16)-100)*0.0213+MAX(0,((1)*1.056+(MAX(0,C35-1))*2.6399999999999997+(0)*6.6+(0)*13.2)-250)*0.09+(MAX(0,ROUNDUP((((1)*0.06+(MAX(0,C35-1))*0.15)+((0)*0.375+(0)*0.75)*0.05)*2,0)-8)+((1)*0+(MAX(0,C35-1))*0+(0)*0+(0)*0))*0.125+IF(((1)*80+(MAX(0,C35-1))*200)&lt;=2000,10,IF(((1)*80+(MAX(0,C35-1))*200)&lt;=5000,15,IF(((1)*80+(MAX(0,C35-1))*200)&lt;=10000,60,110)))-10)*500,2)+ROUND((MAX(0,((1)*0.166864+(MAX(0,C35-1))*0.41716+(0)*1.0429000000000002+(0)*2.0858000000000003)+20*2*2*0.0035+30*(1/3600*0.128+5/3600*0.0106)-20)+IF(AND(((1)*55680.0+(MAX(0,C35-1))*139200.0+(0)*348000.0+(0)*696000.0)&lt;=1000000,((1)*1.536+(MAX(0,C35-1))*3.84+(0)*9.6+(0)*19.2)&lt;=1000),0,IF(((1)*55680.0+(MAX(0,C35-1))*139200.0+(0)*348000.0+(0)*696000.0)&lt;=10000000,20,IF(((1)*55680.0+(MAX(0,C35-1))*139200.0+(0)*348000.0+(0)*696000.0)&lt;=50000000,100,300)))+MAX(0,ROUNDUP(((1)*80+(MAX(0,C35-1))*200+(0)*500+(0)*1000)/5000,0)-1)*25+IF(((1)*80+(MAX(0,C35-1))*200+(0)*500+(0)*1000)&gt;5000,32-10,0))*500,2)),2)</f>
-        <v>214482.79</v>
+        <f>C35*$D$27+(ROUND((((80*2+20)*0.16/1000+(80*2+20)*32/1000000*0.12)*500),2)+80*2*(4000*0.4+300*1.6)/1000000*500+MAX(0,C35-1)*(ROUND((((200*2+20)*0.16/1000+(200*2+20)*32/1000000*0.12)*500),2)+200*2*(4000*0.4+300*1.6)/1000000*500))+C35*$D$29+'Clientes e Ingresos'!D6*(8*(496838.17/30/8))+(ROUND((MAX(0,((1)*1+(MAX(0,C35-1))*3+(0)*8+(0)*16)-100)*0.0213+MAX(0,((1)*1.056+(MAX(0,C35-1))*2.63999999999999+(0)*6.6+(0)*13.2)-250)*0.09+(MAX(0,ROUNDUP((((1)*0.06+(MAX(0,C35-1))*0.15)+((0)*0.375+(0)*0.75)*0.05)*2,0)-8)+((1)*0+(MAX(0,C35-1))*0+(0)*0+(0)*0))*0.125+IF(((1)*80+(MAX(0,C35-1))*200)&lt;=2000,10,IF(((1)*80+(MAX(0,C35-1))*200)&lt;=5000,15,IF(((1)*80+(MAX(0,C35-1))*200)&lt;=10000,60,110)))-10)*500,2)+ROUND((MAX(0,((1)*0.166864+(MAX(0,C35-1))*0.41716+(0)*1.0429+(0)*2.0858)+20*2*2*0.0035+30*(1/3600*0.128+5/3600*0.0106)-20)+IF(AND(((1)*55680+(MAX(0,C35-1))*139200+(0)*348000+(0)*696000)&lt;=1000000,((1)*1.536+(MAX(0,C35-1))*3.84+(0)*9.6+(0)*19.2)&lt;=1000),0,IF(((1)*55680+(MAX(0,C35-1))*139200+(0)*348000+(0)*696000)&lt;=10000000,20,IF(((1)*55680+(MAX(0,C35-1))*139200+(0)*348000+(0)*696000)&lt;=50000000,100,300)))+MAX(0,ROUNDUP(((1)*80+(MAX(0,C35-1))*200+(0)*500+(0)*1000)/5000,0)-1)*25+IF(((1)*80+(MAX(0,C35-1))*200+(0)*500+(0)*1000)&gt;5000,32-10,0))*500,2))</f>
+        <v>89964.54927083333</v>
       </c>
       <c r="F35" s="7">
         <f>D35+E35</f>
-        <v>305607.79000000004</v>
+        <v>281895.9109375</v>
       </c>
     </row>
     <row r="36">
@@ -2874,15 +2882,15 @@
       </c>
       <c r="D36" s="10">
         <f>$D$22</f>
-        <v>91125.0</v>
+        <v>114247.54466666667</v>
       </c>
       <c r="E36" s="10">
-        <f>ROUND(C36*$D$27+(ROUND((((80*2+20)*0.16/1000+(80*2+20)*32/1000000*0.12)*500),2)+80*2*(4000*0.4+300*1.6)/1000000*500+MAX(0,C36-1)*(ROUND((((200*2+20)*0.16/1000+(200*2+20)*32/1000000*0.12)*500),2)+200*2*(4000*0.4+300*1.6)/1000000*500))+C36*$D$29+'Clientes e Ingresos'!D7*(8*5000)+(ROUND((MAX(0,((1)*1+(MAX(0,C36-1))*3+(0)*8+(0)*16)-100)*0.0213+MAX(0,((1)*1.056+(MAX(0,C36-1))*2.6399999999999997+(0)*6.6+(0)*13.2)-250)*0.09+(MAX(0,ROUNDUP((((1)*0.06+(MAX(0,C36-1))*0.15)+((0)*0.375+(0)*0.75)*0.05)*2,0)-8)+((1)*0+(MAX(0,C36-1))*0+(0)*0+(0)*0))*0.125+IF(((1)*80+(MAX(0,C36-1))*200)&lt;=2000,10,IF(((1)*80+(MAX(0,C36-1))*200)&lt;=5000,15,IF(((1)*80+(MAX(0,C36-1))*200)&lt;=10000,60,110)))-10)*500,2)+ROUND((MAX(0,((1)*0.166864+(MAX(0,C36-1))*0.41716+(0)*1.0429000000000002+(0)*2.0858000000000003)+20*2*2*0.0035+30*(1/3600*0.128+5/3600*0.0106)-20)+IF(AND(((1)*55680.0+(MAX(0,C36-1))*139200.0+(0)*348000.0+(0)*696000.0)&lt;=1000000,((1)*1.536+(MAX(0,C36-1))*3.84+(0)*9.6+(0)*19.2)&lt;=1000),0,IF(((1)*55680.0+(MAX(0,C36-1))*139200.0+(0)*348000.0+(0)*696000.0)&lt;=10000000,20,IF(((1)*55680.0+(MAX(0,C36-1))*139200.0+(0)*348000.0+(0)*696000.0)&lt;=50000000,100,300)))+MAX(0,ROUNDUP(((1)*80+(MAX(0,C36-1))*200+(0)*500+(0)*1000)/5000,0)-1)*25+IF(((1)*80+(MAX(0,C36-1))*200+(0)*500+(0)*1000)&gt;5000,32-10,0))*500,2)),2)</f>
-        <v>57433.2</v>
+        <f>C36*$D$27+(ROUND((((80*2+20)*0.16/1000+(80*2+20)*32/1000000*0.12)*500),2)+80*2*(4000*0.4+300*1.6)/1000000*500+MAX(0,C36-1)*(ROUND((((200*2+20)*0.16/1000+(200*2+20)*32/1000000*0.12)*500),2)+200*2*(4000*0.4+300*1.6)/1000000*500))+C36*$D$29+'Clientes e Ingresos'!D7*(8*(496838.17/30/8))+(ROUND((MAX(0,((1)*1+(MAX(0,C36-1))*3+(0)*8+(0)*16)-100)*0.0213+MAX(0,((1)*1.056+(MAX(0,C36-1))*2.63999999999999+(0)*6.6+(0)*13.2)-250)*0.09+(MAX(0,ROUNDUP((((1)*0.06+(MAX(0,C36-1))*0.15)+((0)*0.375+(0)*0.75)*0.05)*2,0)-8)+((1)*0+(MAX(0,C36-1))*0+(0)*0+(0)*0))*0.125+IF(((1)*80+(MAX(0,C36-1))*200)&lt;=2000,10,IF(((1)*80+(MAX(0,C36-1))*200)&lt;=5000,15,IF(((1)*80+(MAX(0,C36-1))*200)&lt;=10000,60,110)))-10)*500,2)+ROUND((MAX(0,((1)*0.166864+(MAX(0,C36-1))*0.41716+(0)*1.0429+(0)*2.0858)+20*2*2*0.0035+30*(1/3600*0.128+5/3600*0.0106)-20)+IF(AND(((1)*55680+(MAX(0,C36-1))*139200+(0)*348000+(0)*696000)&lt;=1000000,((1)*1.536+(MAX(0,C36-1))*3.84+(0)*9.6+(0)*19.2)&lt;=1000),0,IF(((1)*55680+(MAX(0,C36-1))*139200+(0)*348000+(0)*696000)&lt;=10000000,20,IF(((1)*55680+(MAX(0,C36-1))*139200+(0)*348000+(0)*696000)&lt;=50000000,100,300)))+MAX(0,ROUNDUP(((1)*80+(MAX(0,C36-1))*200+(0)*500+(0)*1000)/5000,0)-1)*25+IF(((1)*80+(MAX(0,C36-1))*200+(0)*500+(0)*1000)&gt;5000,32-10,0))*500,2))</f>
+        <v>25204.949458333336</v>
       </c>
       <c r="F36" s="10">
         <f>D36+E36</f>
-        <v>148558.2</v>
+        <v>139452.494125</v>
       </c>
     </row>
     <row r="37">
@@ -2897,15 +2905,15 @@
       </c>
       <c r="D37" s="7">
         <f>$D$22</f>
-        <v>91125.0</v>
+        <v>114247.54466666667</v>
       </c>
       <c r="E37" s="7">
-        <f>ROUND(C37*$D$27+(ROUND((((80*2+20)*0.16/1000+(80*2+20)*32/1000000*0.12)*500),2)+80*2*(4000*0.4+300*1.6)/1000000*500+MAX(0,C37-1)*(ROUND((((200*2+20)*0.16/1000+(200*2+20)*32/1000000*0.12)*500),2)+200*2*(4000*0.4+300*1.6)/1000000*500))+C37*$D$29+'Clientes e Ingresos'!D8*(8*5000)+(ROUND((MAX(0,((1)*1+(MAX(0,C37-1))*3+(0)*8+(0)*16)-100)*0.0213+MAX(0,((1)*1.056+(MAX(0,C37-1))*2.6399999999999997+(0)*6.6+(0)*13.2)-250)*0.09+(MAX(0,ROUNDUP((((1)*0.06+(MAX(0,C37-1))*0.15)+((0)*0.375+(0)*0.75)*0.05)*2,0)-8)+((1)*0+(MAX(0,C37-1))*0+(0)*0+(0)*0))*0.125+IF(((1)*80+(MAX(0,C37-1))*200)&lt;=2000,10,IF(((1)*80+(MAX(0,C37-1))*200)&lt;=5000,15,IF(((1)*80+(MAX(0,C37-1))*200)&lt;=10000,60,110)))-10)*500,2)+ROUND((MAX(0,((1)*0.166864+(MAX(0,C37-1))*0.41716+(0)*1.0429000000000002+(0)*2.0858000000000003)+20*2*2*0.0035+30*(1/3600*0.128+5/3600*0.0106)-20)+IF(AND(((1)*55680.0+(MAX(0,C37-1))*139200.0+(0)*348000.0+(0)*696000.0)&lt;=1000000,((1)*1.536+(MAX(0,C37-1))*3.84+(0)*9.6+(0)*19.2)&lt;=1000),0,IF(((1)*55680.0+(MAX(0,C37-1))*139200.0+(0)*348000.0+(0)*696000.0)&lt;=10000000,20,IF(((1)*55680.0+(MAX(0,C37-1))*139200.0+(0)*348000.0+(0)*696000.0)&lt;=50000000,100,300)))+MAX(0,ROUNDUP(((1)*80+(MAX(0,C37-1))*200+(0)*500+(0)*1000)/5000,0)-1)*25+IF(((1)*80+(MAX(0,C37-1))*200+(0)*500+(0)*1000)&gt;5000,32-10,0))*500,2)),2)</f>
-        <v>60383.61</v>
+        <f>C37*$D$27+(ROUND((((80*2+20)*0.16/1000+(80*2+20)*32/1000000*0.12)*500),2)+80*2*(4000*0.4+300*1.6)/1000000*500+MAX(0,C37-1)*(ROUND((((200*2+20)*0.16/1000+(200*2+20)*32/1000000*0.12)*500),2)+200*2*(4000*0.4+300*1.6)/1000000*500))+C37*$D$29+'Clientes e Ingresos'!D8*(8*(496838.17/30/8))+(ROUND((MAX(0,((1)*1+(MAX(0,C37-1))*3+(0)*8+(0)*16)-100)*0.0213+MAX(0,((1)*1.056+(MAX(0,C37-1))*2.63999999999999+(0)*6.6+(0)*13.2)-250)*0.09+(MAX(0,ROUNDUP((((1)*0.06+(MAX(0,C37-1))*0.15)+((0)*0.375+(0)*0.75)*0.05)*2,0)-8)+((1)*0+(MAX(0,C37-1))*0+(0)*0+(0)*0))*0.125+IF(((1)*80+(MAX(0,C37-1))*200)&lt;=2000,10,IF(((1)*80+(MAX(0,C37-1))*200)&lt;=5000,15,IF(((1)*80+(MAX(0,C37-1))*200)&lt;=10000,60,110)))-10)*500,2)+ROUND((MAX(0,((1)*0.166864+(MAX(0,C37-1))*0.41716+(0)*1.0429+(0)*2.0858)+20*2*2*0.0035+30*(1/3600*0.128+5/3600*0.0106)-20)+IF(AND(((1)*55680+(MAX(0,C37-1))*139200+(0)*348000+(0)*696000)&lt;=1000000,((1)*1.536+(MAX(0,C37-1))*3.84+(0)*9.6+(0)*19.2)&lt;=1000),0,IF(((1)*55680+(MAX(0,C37-1))*139200+(0)*348000+(0)*696000)&lt;=10000000,20,IF(((1)*55680+(MAX(0,C37-1))*139200+(0)*348000+(0)*696000)&lt;=50000000,100,300)))+MAX(0,ROUNDUP(((1)*80+(MAX(0,C37-1))*200+(0)*500+(0)*1000)/5000,0)-1)*25+IF(((1)*80+(MAX(0,C37-1))*200+(0)*500+(0)*1000)&gt;5000,32-10,0))*500,2))</f>
+        <v>26690.43897916667</v>
       </c>
       <c r="F37" s="7">
         <f>D37+E37</f>
-        <v>151508.61</v>
+        <v>140937.98364583333</v>
       </c>
     </row>
     <row r="38">
@@ -2920,15 +2928,15 @@
       </c>
       <c r="D38" s="10">
         <f>$D$22</f>
-        <v>91125.0</v>
+        <v>114247.54466666667</v>
       </c>
       <c r="E38" s="10">
-        <f>ROUND(C38*$D$27+(ROUND((((80*2+20)*0.16/1000+(80*2+20)*32/1000000*0.12)*500),2)+80*2*(4000*0.4+300*1.6)/1000000*500+MAX(0,C38-1)*(ROUND((((200*2+20)*0.16/1000+(200*2+20)*32/1000000*0.12)*500),2)+200*2*(4000*0.4+300*1.6)/1000000*500))+C38*$D$29+'Clientes e Ingresos'!D9*(8*5000)+(ROUND((MAX(0,((1)*1+(MAX(0,C38-1))*3+(0)*8+(0)*16)-100)*0.0213+MAX(0,((1)*1.056+(MAX(0,C38-1))*2.6399999999999997+(0)*6.6+(0)*13.2)-250)*0.09+(MAX(0,ROUNDUP((((1)*0.06+(MAX(0,C38-1))*0.15)+((0)*0.375+(0)*0.75)*0.05)*2,0)-8)+((1)*0+(MAX(0,C38-1))*0+(0)*0+(0)*0))*0.125+IF(((1)*80+(MAX(0,C38-1))*200)&lt;=2000,10,IF(((1)*80+(MAX(0,C38-1))*200)&lt;=5000,15,IF(((1)*80+(MAX(0,C38-1))*200)&lt;=10000,60,110)))-10)*500,2)+ROUND((MAX(0,((1)*0.166864+(MAX(0,C38-1))*0.41716+(0)*1.0429000000000002+(0)*2.0858000000000003)+20*2*2*0.0035+30*(1/3600*0.128+5/3600*0.0106)-20)+IF(AND(((1)*55680.0+(MAX(0,C38-1))*139200.0+(0)*348000.0+(0)*696000.0)&lt;=1000000,((1)*1.536+(MAX(0,C38-1))*3.84+(0)*9.6+(0)*19.2)&lt;=1000),0,IF(((1)*55680.0+(MAX(0,C38-1))*139200.0+(0)*348000.0+(0)*696000.0)&lt;=10000000,20,IF(((1)*55680.0+(MAX(0,C38-1))*139200.0+(0)*348000.0+(0)*696000.0)&lt;=50000000,100,300)))+MAX(0,ROUNDUP(((1)*80+(MAX(0,C38-1))*200+(0)*500+(0)*1000)/5000,0)-1)*25+IF(((1)*80+(MAX(0,C38-1))*200+(0)*500+(0)*1000)&gt;5000,32-10,0))*500,2)),2)</f>
-        <v>73334.02</v>
+        <f>C38*$D$27+(ROUND((((80*2+20)*0.16/1000+(80*2+20)*32/1000000*0.12)*500),2)+80*2*(4000*0.4+300*1.6)/1000000*500+MAX(0,C38-1)*(ROUND((((200*2+20)*0.16/1000+(200*2+20)*32/1000000*0.12)*500),2)+200*2*(4000*0.4+300*1.6)/1000000*500))+C38*$D$29+'Clientes e Ingresos'!D9*(8*(496838.17/30/8))+(ROUND((MAX(0,((1)*1+(MAX(0,C38-1))*3+(0)*8+(0)*16)-100)*0.0213+MAX(0,((1)*1.056+(MAX(0,C38-1))*2.63999999999999+(0)*6.6+(0)*13.2)-250)*0.09+(MAX(0,ROUNDUP((((1)*0.06+(MAX(0,C38-1))*0.15)+((0)*0.375+(0)*0.75)*0.05)*2,0)-8)+((1)*0+(MAX(0,C38-1))*0+(0)*0+(0)*0))*0.125+IF(((1)*80+(MAX(0,C38-1))*200)&lt;=2000,10,IF(((1)*80+(MAX(0,C38-1))*200)&lt;=5000,15,IF(((1)*80+(MAX(0,C38-1))*200)&lt;=10000,60,110)))-10)*500,2)+ROUND((MAX(0,((1)*0.166864+(MAX(0,C38-1))*0.41716+(0)*1.0429+(0)*2.0858)+20*2*2*0.0035+30*(1/3600*0.128+5/3600*0.0106)-20)+IF(AND(((1)*55680+(MAX(0,C38-1))*139200+(0)*348000+(0)*696000)&lt;=1000000,((1)*1.536+(MAX(0,C38-1))*3.84+(0)*9.6+(0)*19.2)&lt;=1000),0,IF(((1)*55680+(MAX(0,C38-1))*139200+(0)*348000+(0)*696000)&lt;=10000000,20,IF(((1)*55680+(MAX(0,C38-1))*139200+(0)*348000+(0)*696000)&lt;=50000000,100,300)))+MAX(0,ROUNDUP(((1)*80+(MAX(0,C38-1))*200+(0)*500+(0)*1000)/5000,0)-1)*25+IF(((1)*80+(MAX(0,C38-1))*200+(0)*500+(0)*1000)&gt;5000,32-10,0))*500,2))</f>
+        <v>38175.9285</v>
       </c>
       <c r="F38" s="10">
         <f>D38+E38</f>
-        <v>164459.02000000002</v>
+        <v>152423.47316666666</v>
       </c>
     </row>
     <row r="39">
@@ -2943,15 +2951,15 @@
       </c>
       <c r="D39" s="7">
         <f>$D$22</f>
-        <v>91125.0</v>
+        <v>114247.54466666667</v>
       </c>
       <c r="E39" s="7">
-        <f>ROUND(C39*$D$27+(ROUND((((80*2+20)*0.16/1000+(80*2+20)*32/1000000*0.12)*500),2)+80*2*(4000*0.4+300*1.6)/1000000*500+MAX(0,C39-1)*(ROUND((((200*2+20)*0.16/1000+(200*2+20)*32/1000000*0.12)*500),2)+200*2*(4000*0.4+300*1.6)/1000000*500))+C39*$D$29+'Clientes e Ingresos'!D10*(8*5000)+(ROUND((MAX(0,((1)*1+(MAX(0,C39-1))*3+(0)*8+(0)*16)-100)*0.0213+MAX(0,((1)*1.056+(MAX(0,C39-1))*2.6399999999999997+(0)*6.6+(0)*13.2)-250)*0.09+(MAX(0,ROUNDUP((((1)*0.06+(MAX(0,C39-1))*0.15)+((0)*0.375+(0)*0.75)*0.05)*2,0)-8)+((1)*0+(MAX(0,C39-1))*0+(0)*0+(0)*0))*0.125+IF(((1)*80+(MAX(0,C39-1))*200)&lt;=2000,10,IF(((1)*80+(MAX(0,C39-1))*200)&lt;=5000,15,IF(((1)*80+(MAX(0,C39-1))*200)&lt;=10000,60,110)))-10)*500,2)+ROUND((MAX(0,((1)*0.166864+(MAX(0,C39-1))*0.41716+(0)*1.0429000000000002+(0)*2.0858000000000003)+20*2*2*0.0035+30*(1/3600*0.128+5/3600*0.0106)-20)+IF(AND(((1)*55680.0+(MAX(0,C39-1))*139200.0+(0)*348000.0+(0)*696000.0)&lt;=1000000,((1)*1.536+(MAX(0,C39-1))*3.84+(0)*9.6+(0)*19.2)&lt;=1000),0,IF(((1)*55680.0+(MAX(0,C39-1))*139200.0+(0)*348000.0+(0)*696000.0)&lt;=10000000,20,IF(((1)*55680.0+(MAX(0,C39-1))*139200.0+(0)*348000.0+(0)*696000.0)&lt;=50000000,100,300)))+MAX(0,ROUNDUP(((1)*80+(MAX(0,C39-1))*200+(0)*500+(0)*1000)/5000,0)-1)*25+IF(((1)*80+(MAX(0,C39-1))*200+(0)*500+(0)*1000)&gt;5000,32-10,0))*500,2)),2)</f>
-        <v>76284.43</v>
+        <f>C39*$D$27+(ROUND((((80*2+20)*0.16/1000+(80*2+20)*32/1000000*0.12)*500),2)+80*2*(4000*0.4+300*1.6)/1000000*500+MAX(0,C39-1)*(ROUND((((200*2+20)*0.16/1000+(200*2+20)*32/1000000*0.12)*500),2)+200*2*(4000*0.4+300*1.6)/1000000*500))+C39*$D$29+'Clientes e Ingresos'!D10*(8*(496838.17/30/8))+(ROUND((MAX(0,((1)*1+(MAX(0,C39-1))*3+(0)*8+(0)*16)-100)*0.0213+MAX(0,((1)*1.056+(MAX(0,C39-1))*2.63999999999999+(0)*6.6+(0)*13.2)-250)*0.09+(MAX(0,ROUNDUP((((1)*0.06+(MAX(0,C39-1))*0.15)+((0)*0.375+(0)*0.75)*0.05)*2,0)-8)+((1)*0+(MAX(0,C39-1))*0+(0)*0+(0)*0))*0.125+IF(((1)*80+(MAX(0,C39-1))*200)&lt;=2000,10,IF(((1)*80+(MAX(0,C39-1))*200)&lt;=5000,15,IF(((1)*80+(MAX(0,C39-1))*200)&lt;=10000,60,110)))-10)*500,2)+ROUND((MAX(0,((1)*0.166864+(MAX(0,C39-1))*0.41716+(0)*1.0429+(0)*2.0858)+20*2*2*0.0035+30*(1/3600*0.128+5/3600*0.0106)-20)+IF(AND(((1)*55680+(MAX(0,C39-1))*139200+(0)*348000+(0)*696000)&lt;=1000000,((1)*1.536+(MAX(0,C39-1))*3.84+(0)*9.6+(0)*19.2)&lt;=1000),0,IF(((1)*55680+(MAX(0,C39-1))*139200+(0)*348000+(0)*696000)&lt;=10000000,20,IF(((1)*55680+(MAX(0,C39-1))*139200+(0)*348000+(0)*696000)&lt;=50000000,100,300)))+MAX(0,ROUNDUP(((1)*80+(MAX(0,C39-1))*200+(0)*500+(0)*1000)/5000,0)-1)*25+IF(((1)*80+(MAX(0,C39-1))*200+(0)*500+(0)*1000)&gt;5000,32-10,0))*500,2))</f>
+        <v>39661.418020833335</v>
       </c>
       <c r="F39" s="7">
         <f>D39+E39</f>
-        <v>167409.43</v>
+        <v>153908.9626875</v>
       </c>
     </row>
     <row r="40">
@@ -2966,15 +2974,15 @@
       </c>
       <c r="D40" s="10">
         <f>$D$22</f>
-        <v>91125.0</v>
+        <v>114247.54466666667</v>
       </c>
       <c r="E40" s="10">
-        <f>ROUND(C40*$D$27+(ROUND((((80*2+20)*0.16/1000+(80*2+20)*32/1000000*0.12)*500),2)+80*2*(4000*0.4+300*1.6)/1000000*500+MAX(0,C40-1)*(ROUND((((200*2+20)*0.16/1000+(200*2+20)*32/1000000*0.12)*500),2)+200*2*(4000*0.4+300*1.6)/1000000*500))+C40*$D$29+'Clientes e Ingresos'!D11*(8*5000)+(ROUND((MAX(0,((1)*1+(MAX(0,C40-1))*3+(0)*8+(0)*16)-100)*0.0213+MAX(0,((1)*1.056+(MAX(0,C40-1))*2.6399999999999997+(0)*6.6+(0)*13.2)-250)*0.09+(MAX(0,ROUNDUP((((1)*0.06+(MAX(0,C40-1))*0.15)+((0)*0.375+(0)*0.75)*0.05)*2,0)-8)+((1)*0+(MAX(0,C40-1))*0+(0)*0+(0)*0))*0.125+IF(((1)*80+(MAX(0,C40-1))*200)&lt;=2000,10,IF(((1)*80+(MAX(0,C40-1))*200)&lt;=5000,15,IF(((1)*80+(MAX(0,C40-1))*200)&lt;=10000,60,110)))-10)*500,2)+ROUND((MAX(0,((1)*0.166864+(MAX(0,C40-1))*0.41716+(0)*1.0429000000000002+(0)*2.0858000000000003)+20*2*2*0.0035+30*(1/3600*0.128+5/3600*0.0106)-20)+IF(AND(((1)*55680.0+(MAX(0,C40-1))*139200.0+(0)*348000.0+(0)*696000.0)&lt;=1000000,((1)*1.536+(MAX(0,C40-1))*3.84+(0)*9.6+(0)*19.2)&lt;=1000),0,IF(((1)*55680.0+(MAX(0,C40-1))*139200.0+(0)*348000.0+(0)*696000.0)&lt;=10000000,20,IF(((1)*55680.0+(MAX(0,C40-1))*139200.0+(0)*348000.0+(0)*696000.0)&lt;=50000000,100,300)))+MAX(0,ROUNDUP(((1)*80+(MAX(0,C40-1))*200+(0)*500+(0)*1000)/5000,0)-1)*25+IF(((1)*80+(MAX(0,C40-1))*200+(0)*500+(0)*1000)&gt;5000,32-10,0))*500,2)),2)</f>
-        <v>76284.43</v>
+        <f>C40*$D$27+(ROUND((((80*2+20)*0.16/1000+(80*2+20)*32/1000000*0.12)*500),2)+80*2*(4000*0.4+300*1.6)/1000000*500+MAX(0,C40-1)*(ROUND((((200*2+20)*0.16/1000+(200*2+20)*32/1000000*0.12)*500),2)+200*2*(4000*0.4+300*1.6)/1000000*500))+C40*$D$29+'Clientes e Ingresos'!D11*(8*(496838.17/30/8))+(ROUND((MAX(0,((1)*1+(MAX(0,C40-1))*3+(0)*8+(0)*16)-100)*0.0213+MAX(0,((1)*1.056+(MAX(0,C40-1))*2.63999999999999+(0)*6.6+(0)*13.2)-250)*0.09+(MAX(0,ROUNDUP((((1)*0.06+(MAX(0,C40-1))*0.15)+((0)*0.375+(0)*0.75)*0.05)*2,0)-8)+((1)*0+(MAX(0,C40-1))*0+(0)*0+(0)*0))*0.125+IF(((1)*80+(MAX(0,C40-1))*200)&lt;=2000,10,IF(((1)*80+(MAX(0,C40-1))*200)&lt;=5000,15,IF(((1)*80+(MAX(0,C40-1))*200)&lt;=10000,60,110)))-10)*500,2)+ROUND((MAX(0,((1)*0.166864+(MAX(0,C40-1))*0.41716+(0)*1.0429+(0)*2.0858)+20*2*2*0.0035+30*(1/3600*0.128+5/3600*0.0106)-20)+IF(AND(((1)*55680+(MAX(0,C40-1))*139200+(0)*348000+(0)*696000)&lt;=1000000,((1)*1.536+(MAX(0,C40-1))*3.84+(0)*9.6+(0)*19.2)&lt;=1000),0,IF(((1)*55680+(MAX(0,C40-1))*139200+(0)*348000+(0)*696000)&lt;=10000000,20,IF(((1)*55680+(MAX(0,C40-1))*139200+(0)*348000+(0)*696000)&lt;=50000000,100,300)))+MAX(0,ROUNDUP(((1)*80+(MAX(0,C40-1))*200+(0)*500+(0)*1000)/5000,0)-1)*25+IF(((1)*80+(MAX(0,C40-1))*200+(0)*500+(0)*1000)&gt;5000,32-10,0))*500,2))</f>
+        <v>39661.418020833335</v>
       </c>
       <c r="F40" s="10">
         <f>D40+E40</f>
-        <v>167409.43</v>
+        <v>153908.9626875</v>
       </c>
     </row>
     <row r="41">
@@ -2989,15 +2997,15 @@
       </c>
       <c r="D41" s="7">
         <f>$D$22</f>
-        <v>91125.0</v>
+        <v>114247.54466666667</v>
       </c>
       <c r="E41" s="7">
-        <f>ROUND(C41*$D$27+(ROUND((((80*2+20)*0.16/1000+(80*2+20)*32/1000000*0.12)*500),2)+80*2*(4000*0.4+300*1.6)/1000000*500+MAX(0,C41-1)*(ROUND((((200*2+20)*0.16/1000+(200*2+20)*32/1000000*0.12)*500),2)+200*2*(4000*0.4+300*1.6)/1000000*500))+C41*$D$29+'Clientes e Ingresos'!D12*(8*5000)+(ROUND((MAX(0,((1)*1+(MAX(0,C41-1))*3+(0)*8+(0)*16)-100)*0.0213+MAX(0,((1)*1.056+(MAX(0,C41-1))*2.6399999999999997+(0)*6.6+(0)*13.2)-250)*0.09+(MAX(0,ROUNDUP((((1)*0.06+(MAX(0,C41-1))*0.15)+((0)*0.375+(0)*0.75)*0.05)*2,0)-8)+((1)*0+(MAX(0,C41-1))*0+(0)*0+(0)*0))*0.125+IF(((1)*80+(MAX(0,C41-1))*200)&lt;=2000,10,IF(((1)*80+(MAX(0,C41-1))*200)&lt;=5000,15,IF(((1)*80+(MAX(0,C41-1))*200)&lt;=10000,60,110)))-10)*500,2)+ROUND((MAX(0,((1)*0.166864+(MAX(0,C41-1))*0.41716+(0)*1.0429000000000002+(0)*2.0858000000000003)+20*2*2*0.0035+30*(1/3600*0.128+5/3600*0.0106)-20)+IF(AND(((1)*55680.0+(MAX(0,C41-1))*139200.0+(0)*348000.0+(0)*696000.0)&lt;=1000000,((1)*1.536+(MAX(0,C41-1))*3.84+(0)*9.6+(0)*19.2)&lt;=1000),0,IF(((1)*55680.0+(MAX(0,C41-1))*139200.0+(0)*348000.0+(0)*696000.0)&lt;=10000000,20,IF(((1)*55680.0+(MAX(0,C41-1))*139200.0+(0)*348000.0+(0)*696000.0)&lt;=50000000,100,300)))+MAX(0,ROUNDUP(((1)*80+(MAX(0,C41-1))*200+(0)*500+(0)*1000)/5000,0)-1)*25+IF(((1)*80+(MAX(0,C41-1))*200+(0)*500+(0)*1000)&gt;5000,32-10,0))*500,2)),2)</f>
-        <v>79234.84</v>
+        <f>C41*$D$27+(ROUND((((80*2+20)*0.16/1000+(80*2+20)*32/1000000*0.12)*500),2)+80*2*(4000*0.4+300*1.6)/1000000*500+MAX(0,C41-1)*(ROUND((((200*2+20)*0.16/1000+(200*2+20)*32/1000000*0.12)*500),2)+200*2*(4000*0.4+300*1.6)/1000000*500))+C41*$D$29+'Clientes e Ingresos'!D12*(8*(496838.17/30/8))+(ROUND((MAX(0,((1)*1+(MAX(0,C41-1))*3+(0)*8+(0)*16)-100)*0.0213+MAX(0,((1)*1.056+(MAX(0,C41-1))*2.63999999999999+(0)*6.6+(0)*13.2)-250)*0.09+(MAX(0,ROUNDUP((((1)*0.06+(MAX(0,C41-1))*0.15)+((0)*0.375+(0)*0.75)*0.05)*2,0)-8)+((1)*0+(MAX(0,C41-1))*0+(0)*0+(0)*0))*0.125+IF(((1)*80+(MAX(0,C41-1))*200)&lt;=2000,10,IF(((1)*80+(MAX(0,C41-1))*200)&lt;=5000,15,IF(((1)*80+(MAX(0,C41-1))*200)&lt;=10000,60,110)))-10)*500,2)+ROUND((MAX(0,((1)*0.166864+(MAX(0,C41-1))*0.41716+(0)*1.0429+(0)*2.0858)+20*2*2*0.0035+30*(1/3600*0.128+5/3600*0.0106)-20)+IF(AND(((1)*55680+(MAX(0,C41-1))*139200+(0)*348000+(0)*696000)&lt;=1000000,((1)*1.536+(MAX(0,C41-1))*3.84+(0)*9.6+(0)*19.2)&lt;=1000),0,IF(((1)*55680+(MAX(0,C41-1))*139200+(0)*348000+(0)*696000)&lt;=10000000,20,IF(((1)*55680+(MAX(0,C41-1))*139200+(0)*348000+(0)*696000)&lt;=50000000,100,300)))+MAX(0,ROUNDUP(((1)*80+(MAX(0,C41-1))*200+(0)*500+(0)*1000)/5000,0)-1)*25+IF(((1)*80+(MAX(0,C41-1))*200+(0)*500+(0)*1000)&gt;5000,32-10,0))*500,2))</f>
+        <v>41146.90754166667</v>
       </c>
       <c r="F41" s="7">
         <f>D41+E41</f>
-        <v>170359.84</v>
+        <v>155394.45220833333</v>
       </c>
     </row>
     <row r="42">
@@ -3012,15 +3020,15 @@
       </c>
       <c r="D42" s="10">
         <f>$D$22</f>
-        <v>91125.0</v>
+        <v>114247.54466666667</v>
       </c>
       <c r="E42" s="10">
-        <f>ROUND(C42*$D$27+(ROUND((((80*2+20)*0.16/1000+(80*2+20)*32/1000000*0.12)*500),2)+80*2*(4000*0.4+300*1.6)/1000000*500+MAX(0,C42-1)*(ROUND((((200*2+20)*0.16/1000+(200*2+20)*32/1000000*0.12)*500),2)+200*2*(4000*0.4+300*1.6)/1000000*500))+C42*$D$29+'Clientes e Ingresos'!D13*(8*5000)+(ROUND((MAX(0,((1)*1+(MAX(0,C42-1))*3+(0)*8+(0)*16)-100)*0.0213+MAX(0,((1)*1.056+(MAX(0,C42-1))*2.6399999999999997+(0)*6.6+(0)*13.2)-250)*0.09+(MAX(0,ROUNDUP((((1)*0.06+(MAX(0,C42-1))*0.15)+((0)*0.375+(0)*0.75)*0.05)*2,0)-8)+((1)*0+(MAX(0,C42-1))*0+(0)*0+(0)*0))*0.125+IF(((1)*80+(MAX(0,C42-1))*200)&lt;=2000,10,IF(((1)*80+(MAX(0,C42-1))*200)&lt;=5000,15,IF(((1)*80+(MAX(0,C42-1))*200)&lt;=10000,60,110)))-10)*500,2)+ROUND((MAX(0,((1)*0.166864+(MAX(0,C42-1))*0.41716+(0)*1.0429000000000002+(0)*2.0858000000000003)+20*2*2*0.0035+30*(1/3600*0.128+5/3600*0.0106)-20)+IF(AND(((1)*55680.0+(MAX(0,C42-1))*139200.0+(0)*348000.0+(0)*696000.0)&lt;=1000000,((1)*1.536+(MAX(0,C42-1))*3.84+(0)*9.6+(0)*19.2)&lt;=1000),0,IF(((1)*55680.0+(MAX(0,C42-1))*139200.0+(0)*348000.0+(0)*696000.0)&lt;=10000000,20,IF(((1)*55680.0+(MAX(0,C42-1))*139200.0+(0)*348000.0+(0)*696000.0)&lt;=50000000,100,300)))+MAX(0,ROUNDUP(((1)*80+(MAX(0,C42-1))*200+(0)*500+(0)*1000)/5000,0)-1)*25+IF(((1)*80+(MAX(0,C42-1))*200+(0)*500+(0)*1000)&gt;5000,32-10,0))*500,2)),2)</f>
-        <v>84685.25</v>
+        <f>C42*$D$27+(ROUND((((80*2+20)*0.16/1000+(80*2+20)*32/1000000*0.12)*500),2)+80*2*(4000*0.4+300*1.6)/1000000*500+MAX(0,C42-1)*(ROUND((((200*2+20)*0.16/1000+(200*2+20)*32/1000000*0.12)*500),2)+200*2*(4000*0.4+300*1.6)/1000000*500))+C42*$D$29+'Clientes e Ingresos'!D13*(8*(496838.17/30/8))+(ROUND((MAX(0,((1)*1+(MAX(0,C42-1))*3+(0)*8+(0)*16)-100)*0.0213+MAX(0,((1)*1.056+(MAX(0,C42-1))*2.63999999999999+(0)*6.6+(0)*13.2)-250)*0.09+(MAX(0,ROUNDUP((((1)*0.06+(MAX(0,C42-1))*0.15)+((0)*0.375+(0)*0.75)*0.05)*2,0)-8)+((1)*0+(MAX(0,C42-1))*0+(0)*0+(0)*0))*0.125+IF(((1)*80+(MAX(0,C42-1))*200)&lt;=2000,10,IF(((1)*80+(MAX(0,C42-1))*200)&lt;=5000,15,IF(((1)*80+(MAX(0,C42-1))*200)&lt;=10000,60,110)))-10)*500,2)+ROUND((MAX(0,((1)*0.166864+(MAX(0,C42-1))*0.41716+(0)*1.0429+(0)*2.0858)+20*2*2*0.0035+30*(1/3600*0.128+5/3600*0.0106)-20)+IF(AND(((1)*55680+(MAX(0,C42-1))*139200+(0)*348000+(0)*696000)&lt;=1000000,((1)*1.536+(MAX(0,C42-1))*3.84+(0)*9.6+(0)*19.2)&lt;=1000),0,IF(((1)*55680+(MAX(0,C42-1))*139200+(0)*348000+(0)*696000)&lt;=10000000,20,IF(((1)*55680+(MAX(0,C42-1))*139200+(0)*348000+(0)*696000)&lt;=50000000,100,300)))+MAX(0,ROUNDUP(((1)*80+(MAX(0,C42-1))*200+(0)*500+(0)*1000)/5000,0)-1)*25+IF(((1)*80+(MAX(0,C42-1))*200+(0)*500+(0)*1000)&gt;5000,32-10,0))*500,2))</f>
+        <v>45132.3970625</v>
       </c>
       <c r="F42" s="10">
         <f>D42+E42</f>
-        <v>175810.25</v>
+        <v>159379.94172916666</v>
       </c>
     </row>
     <row r="43">
@@ -3035,15 +3043,15 @@
       </c>
       <c r="D43" s="7">
         <f>$D$22</f>
-        <v>91125.0</v>
+        <v>114247.54466666667</v>
       </c>
       <c r="E43" s="7">
-        <f>ROUND(C43*$D$27+(ROUND((((80*2+20)*0.16/1000+(80*2+20)*32/1000000*0.12)*500),2)+80*2*(4000*0.4+300*1.6)/1000000*500+MAX(0,C43-1)*(ROUND((((200*2+20)*0.16/1000+(200*2+20)*32/1000000*0.12)*500),2)+200*2*(4000*0.4+300*1.6)/1000000*500))+C43*$D$29+'Clientes e Ingresos'!D14*(8*5000)+(ROUND((MAX(0,((1)*1+(MAX(0,C43-1))*3+(0)*8+(0)*16)-100)*0.0213+MAX(0,((1)*1.056+(MAX(0,C43-1))*2.6399999999999997+(0)*6.6+(0)*13.2)-250)*0.09+(MAX(0,ROUNDUP((((1)*0.06+(MAX(0,C43-1))*0.15)+((0)*0.375+(0)*0.75)*0.05)*2,0)-8)+((1)*0+(MAX(0,C43-1))*0+(0)*0+(0)*0))*0.125+IF(((1)*80+(MAX(0,C43-1))*200)&lt;=2000,10,IF(((1)*80+(MAX(0,C43-1))*200)&lt;=5000,15,IF(((1)*80+(MAX(0,C43-1))*200)&lt;=10000,60,110)))-10)*500,2)+ROUND((MAX(0,((1)*0.166864+(MAX(0,C43-1))*0.41716+(0)*1.0429000000000002+(0)*2.0858000000000003)+20*2*2*0.0035+30*(1/3600*0.128+5/3600*0.0106)-20)+IF(AND(((1)*55680.0+(MAX(0,C43-1))*139200.0+(0)*348000.0+(0)*696000.0)&lt;=1000000,((1)*1.536+(MAX(0,C43-1))*3.84+(0)*9.6+(0)*19.2)&lt;=1000),0,IF(((1)*55680.0+(MAX(0,C43-1))*139200.0+(0)*348000.0+(0)*696000.0)&lt;=10000000,20,IF(((1)*55680.0+(MAX(0,C43-1))*139200.0+(0)*348000.0+(0)*696000.0)&lt;=50000000,100,300)))+MAX(0,ROUNDUP(((1)*80+(MAX(0,C43-1))*200+(0)*500+(0)*1000)/5000,0)-1)*25+IF(((1)*80+(MAX(0,C43-1))*200+(0)*500+(0)*1000)&gt;5000,32-10,0))*500,2)),2)</f>
-        <v>87635.66</v>
+        <f>C43*$D$27+(ROUND((((80*2+20)*0.16/1000+(80*2+20)*32/1000000*0.12)*500),2)+80*2*(4000*0.4+300*1.6)/1000000*500+MAX(0,C43-1)*(ROUND((((200*2+20)*0.16/1000+(200*2+20)*32/1000000*0.12)*500),2)+200*2*(4000*0.4+300*1.6)/1000000*500))+C43*$D$29+'Clientes e Ingresos'!D14*(8*(496838.17/30/8))+(ROUND((MAX(0,((1)*1+(MAX(0,C43-1))*3+(0)*8+(0)*16)-100)*0.0213+MAX(0,((1)*1.056+(MAX(0,C43-1))*2.63999999999999+(0)*6.6+(0)*13.2)-250)*0.09+(MAX(0,ROUNDUP((((1)*0.06+(MAX(0,C43-1))*0.15)+((0)*0.375+(0)*0.75)*0.05)*2,0)-8)+((1)*0+(MAX(0,C43-1))*0+(0)*0+(0)*0))*0.125+IF(((1)*80+(MAX(0,C43-1))*200)&lt;=2000,10,IF(((1)*80+(MAX(0,C43-1))*200)&lt;=5000,15,IF(((1)*80+(MAX(0,C43-1))*200)&lt;=10000,60,110)))-10)*500,2)+ROUND((MAX(0,((1)*0.166864+(MAX(0,C43-1))*0.41716+(0)*1.0429+(0)*2.0858)+20*2*2*0.0035+30*(1/3600*0.128+5/3600*0.0106)-20)+IF(AND(((1)*55680+(MAX(0,C43-1))*139200+(0)*348000+(0)*696000)&lt;=1000000,((1)*1.536+(MAX(0,C43-1))*3.84+(0)*9.6+(0)*19.2)&lt;=1000),0,IF(((1)*55680+(MAX(0,C43-1))*139200+(0)*348000+(0)*696000)&lt;=10000000,20,IF(((1)*55680+(MAX(0,C43-1))*139200+(0)*348000+(0)*696000)&lt;=50000000,100,300)))+MAX(0,ROUNDUP(((1)*80+(MAX(0,C43-1))*200+(0)*500+(0)*1000)/5000,0)-1)*25+IF(((1)*80+(MAX(0,C43-1))*200+(0)*500+(0)*1000)&gt;5000,32-10,0))*500,2))</f>
+        <v>46617.88658333333</v>
       </c>
       <c r="F43" s="7">
         <f>D43+E43</f>
-        <v>178760.66</v>
+        <v>160865.43125</v>
       </c>
     </row>
     <row r="44">
@@ -3058,15 +3066,15 @@
       </c>
       <c r="D44" s="10">
         <f>$D$22</f>
-        <v>91125.0</v>
+        <v>114247.54466666667</v>
       </c>
       <c r="E44" s="10">
-        <f>ROUND(C44*$D$27+(ROUND((((80*2+20)*0.16/1000+(80*2+20)*32/1000000*0.12)*500),2)+80*2*(4000*0.4+300*1.6)/1000000*500+MAX(0,C44-1)*(ROUND((((200*2+20)*0.16/1000+(200*2+20)*32/1000000*0.12)*500),2)+200*2*(4000*0.4+300*1.6)/1000000*500))+C44*$D$29+'Clientes e Ingresos'!D15*(8*5000)+(ROUND((MAX(0,((1)*1+(MAX(0,C44-1))*3+(0)*8+(0)*16)-100)*0.0213+MAX(0,((1)*1.056+(MAX(0,C44-1))*2.6399999999999997+(0)*6.6+(0)*13.2)-250)*0.09+(MAX(0,ROUNDUP((((1)*0.06+(MAX(0,C44-1))*0.15)+((0)*0.375+(0)*0.75)*0.05)*2,0)-8)+((1)*0+(MAX(0,C44-1))*0+(0)*0+(0)*0))*0.125+IF(((1)*80+(MAX(0,C44-1))*200)&lt;=2000,10,IF(((1)*80+(MAX(0,C44-1))*200)&lt;=5000,15,IF(((1)*80+(MAX(0,C44-1))*200)&lt;=10000,60,110)))-10)*500,2)+ROUND((MAX(0,((1)*0.166864+(MAX(0,C44-1))*0.41716+(0)*1.0429000000000002+(0)*2.0858000000000003)+20*2*2*0.0035+30*(1/3600*0.128+5/3600*0.0106)-20)+IF(AND(((1)*55680.0+(MAX(0,C44-1))*139200.0+(0)*348000.0+(0)*696000.0)&lt;=1000000,((1)*1.536+(MAX(0,C44-1))*3.84+(0)*9.6+(0)*19.2)&lt;=1000),0,IF(((1)*55680.0+(MAX(0,C44-1))*139200.0+(0)*348000.0+(0)*696000.0)&lt;=10000000,20,IF(((1)*55680.0+(MAX(0,C44-1))*139200.0+(0)*348000.0+(0)*696000.0)&lt;=50000000,100,300)))+MAX(0,ROUNDUP(((1)*80+(MAX(0,C44-1))*200+(0)*500+(0)*1000)/5000,0)-1)*25+IF(((1)*80+(MAX(0,C44-1))*200+(0)*500+(0)*1000)&gt;5000,32-10,0))*500,2)),2)</f>
-        <v>87635.66</v>
+        <f>C44*$D$27+(ROUND((((80*2+20)*0.16/1000+(80*2+20)*32/1000000*0.12)*500),2)+80*2*(4000*0.4+300*1.6)/1000000*500+MAX(0,C44-1)*(ROUND((((200*2+20)*0.16/1000+(200*2+20)*32/1000000*0.12)*500),2)+200*2*(4000*0.4+300*1.6)/1000000*500))+C44*$D$29+'Clientes e Ingresos'!D15*(8*(496838.17/30/8))+(ROUND((MAX(0,((1)*1+(MAX(0,C44-1))*3+(0)*8+(0)*16)-100)*0.0213+MAX(0,((1)*1.056+(MAX(0,C44-1))*2.63999999999999+(0)*6.6+(0)*13.2)-250)*0.09+(MAX(0,ROUNDUP((((1)*0.06+(MAX(0,C44-1))*0.15)+((0)*0.375+(0)*0.75)*0.05)*2,0)-8)+((1)*0+(MAX(0,C44-1))*0+(0)*0+(0)*0))*0.125+IF(((1)*80+(MAX(0,C44-1))*200)&lt;=2000,10,IF(((1)*80+(MAX(0,C44-1))*200)&lt;=5000,15,IF(((1)*80+(MAX(0,C44-1))*200)&lt;=10000,60,110)))-10)*500,2)+ROUND((MAX(0,((1)*0.166864+(MAX(0,C44-1))*0.41716+(0)*1.0429+(0)*2.0858)+20*2*2*0.0035+30*(1/3600*0.128+5/3600*0.0106)-20)+IF(AND(((1)*55680+(MAX(0,C44-1))*139200+(0)*348000+(0)*696000)&lt;=1000000,((1)*1.536+(MAX(0,C44-1))*3.84+(0)*9.6+(0)*19.2)&lt;=1000),0,IF(((1)*55680+(MAX(0,C44-1))*139200+(0)*348000+(0)*696000)&lt;=10000000,20,IF(((1)*55680+(MAX(0,C44-1))*139200+(0)*348000+(0)*696000)&lt;=50000000,100,300)))+MAX(0,ROUNDUP(((1)*80+(MAX(0,C44-1))*200+(0)*500+(0)*1000)/5000,0)-1)*25+IF(((1)*80+(MAX(0,C44-1))*200+(0)*500+(0)*1000)&gt;5000,32-10,0))*500,2))</f>
+        <v>46617.88658333333</v>
       </c>
       <c r="F44" s="10">
         <f>D44+E44</f>
-        <v>178760.66</v>
+        <v>160865.43125</v>
       </c>
     </row>
     <row r="45">
@@ -3081,15 +3089,15 @@
       </c>
       <c r="D45" s="7">
         <f>$D$22</f>
-        <v>91125.0</v>
+        <v>114247.54466666667</v>
       </c>
       <c r="E45" s="7">
-        <f>ROUND(C45*$D$27+(ROUND((((80*2+20)*0.16/1000+(80*2+20)*32/1000000*0.12)*500),2)+80*2*(4000*0.4+300*1.6)/1000000*500+MAX(0,C45-1)*(ROUND((((200*2+20)*0.16/1000+(200*2+20)*32/1000000*0.12)*500),2)+200*2*(4000*0.4+300*1.6)/1000000*500))+C45*$D$29+'Clientes e Ingresos'!D16*(8*5000)+(ROUND((MAX(0,((1)*1+(MAX(0,C45-1))*3+(0)*8+(0)*16)-100)*0.0213+MAX(0,((1)*1.056+(MAX(0,C45-1))*2.6399999999999997+(0)*6.6+(0)*13.2)-250)*0.09+(MAX(0,ROUNDUP((((1)*0.06+(MAX(0,C45-1))*0.15)+((0)*0.375+(0)*0.75)*0.05)*2,0)-8)+((1)*0+(MAX(0,C45-1))*0+(0)*0+(0)*0))*0.125+IF(((1)*80+(MAX(0,C45-1))*200)&lt;=2000,10,IF(((1)*80+(MAX(0,C45-1))*200)&lt;=5000,15,IF(((1)*80+(MAX(0,C45-1))*200)&lt;=10000,60,110)))-10)*500,2)+ROUND((MAX(0,((1)*0.166864+(MAX(0,C45-1))*0.41716+(0)*1.0429000000000002+(0)*2.0858000000000003)+20*2*2*0.0035+30*(1/3600*0.128+5/3600*0.0106)-20)+IF(AND(((1)*55680.0+(MAX(0,C45-1))*139200.0+(0)*348000.0+(0)*696000.0)&lt;=1000000,((1)*1.536+(MAX(0,C45-1))*3.84+(0)*9.6+(0)*19.2)&lt;=1000),0,IF(((1)*55680.0+(MAX(0,C45-1))*139200.0+(0)*348000.0+(0)*696000.0)&lt;=10000000,20,IF(((1)*55680.0+(MAX(0,C45-1))*139200.0+(0)*348000.0+(0)*696000.0)&lt;=50000000,100,300)))+MAX(0,ROUNDUP(((1)*80+(MAX(0,C45-1))*200+(0)*500+(0)*1000)/5000,0)-1)*25+IF(((1)*80+(MAX(0,C45-1))*200+(0)*500+(0)*1000)&gt;5000,32-10,0))*500,2)),2)</f>
-        <v>90586.07</v>
+        <f>C45*$D$27+(ROUND((((80*2+20)*0.16/1000+(80*2+20)*32/1000000*0.12)*500),2)+80*2*(4000*0.4+300*1.6)/1000000*500+MAX(0,C45-1)*(ROUND((((200*2+20)*0.16/1000+(200*2+20)*32/1000000*0.12)*500),2)+200*2*(4000*0.4+300*1.6)/1000000*500))+C45*$D$29+'Clientes e Ingresos'!D16*(8*(496838.17/30/8))+(ROUND((MAX(0,((1)*1+(MAX(0,C45-1))*3+(0)*8+(0)*16)-100)*0.0213+MAX(0,((1)*1.056+(MAX(0,C45-1))*2.63999999999999+(0)*6.6+(0)*13.2)-250)*0.09+(MAX(0,ROUNDUP((((1)*0.06+(MAX(0,C45-1))*0.15)+((0)*0.375+(0)*0.75)*0.05)*2,0)-8)+((1)*0+(MAX(0,C45-1))*0+(0)*0+(0)*0))*0.125+IF(((1)*80+(MAX(0,C45-1))*200)&lt;=2000,10,IF(((1)*80+(MAX(0,C45-1))*200)&lt;=5000,15,IF(((1)*80+(MAX(0,C45-1))*200)&lt;=10000,60,110)))-10)*500,2)+ROUND((MAX(0,((1)*0.166864+(MAX(0,C45-1))*0.41716+(0)*1.0429+(0)*2.0858)+20*2*2*0.0035+30*(1/3600*0.128+5/3600*0.0106)-20)+IF(AND(((1)*55680+(MAX(0,C45-1))*139200+(0)*348000+(0)*696000)&lt;=1000000,((1)*1.536+(MAX(0,C45-1))*3.84+(0)*9.6+(0)*19.2)&lt;=1000),0,IF(((1)*55680+(MAX(0,C45-1))*139200+(0)*348000+(0)*696000)&lt;=10000000,20,IF(((1)*55680+(MAX(0,C45-1))*139200+(0)*348000+(0)*696000)&lt;=50000000,100,300)))+MAX(0,ROUNDUP(((1)*80+(MAX(0,C45-1))*200+(0)*500+(0)*1000)/5000,0)-1)*25+IF(((1)*80+(MAX(0,C45-1))*200+(0)*500+(0)*1000)&gt;5000,32-10,0))*500,2))</f>
+        <v>48103.376104166666</v>
       </c>
       <c r="F45" s="7">
         <f>D45+E45</f>
-        <v>181711.07</v>
+        <v>162350.92077083333</v>
       </c>
     </row>
     <row r="46">
@@ -3104,15 +3112,15 @@
       </c>
       <c r="D46" s="10">
         <f>$D$22</f>
-        <v>91125.0</v>
+        <v>114247.54466666667</v>
       </c>
       <c r="E46" s="10">
-        <f>ROUND(C46*$D$27+(ROUND((((80*2+20)*0.16/1000+(80*2+20)*32/1000000*0.12)*500),2)+80*2*(4000*0.4+300*1.6)/1000000*500+MAX(0,C46-1)*(ROUND((((200*2+20)*0.16/1000+(200*2+20)*32/1000000*0.12)*500),2)+200*2*(4000*0.4+300*1.6)/1000000*500))+C46*$D$29+'Clientes e Ingresos'!D17*(8*5000)+(ROUND((MAX(0,((1)*1+(MAX(0,C46-1))*3+(0)*8+(0)*16)-100)*0.0213+MAX(0,((1)*1.056+(MAX(0,C46-1))*2.6399999999999997+(0)*6.6+(0)*13.2)-250)*0.09+(MAX(0,ROUNDUP((((1)*0.06+(MAX(0,C46-1))*0.15)+((0)*0.375+(0)*0.75)*0.05)*2,0)-8)+((1)*0+(MAX(0,C46-1))*0+(0)*0+(0)*0))*0.125+IF(((1)*80+(MAX(0,C46-1))*200)&lt;=2000,10,IF(((1)*80+(MAX(0,C46-1))*200)&lt;=5000,15,IF(((1)*80+(MAX(0,C46-1))*200)&lt;=10000,60,110)))-10)*500,2)+ROUND((MAX(0,((1)*0.166864+(MAX(0,C46-1))*0.41716+(0)*1.0429000000000002+(0)*2.0858000000000003)+20*2*2*0.0035+30*(1/3600*0.128+5/3600*0.0106)-20)+IF(AND(((1)*55680.0+(MAX(0,C46-1))*139200.0+(0)*348000.0+(0)*696000.0)&lt;=1000000,((1)*1.536+(MAX(0,C46-1))*3.84+(0)*9.6+(0)*19.2)&lt;=1000),0,IF(((1)*55680.0+(MAX(0,C46-1))*139200.0+(0)*348000.0+(0)*696000.0)&lt;=10000000,20,IF(((1)*55680.0+(MAX(0,C46-1))*139200.0+(0)*348000.0+(0)*696000.0)&lt;=50000000,100,300)))+MAX(0,ROUNDUP(((1)*80+(MAX(0,C46-1))*200+(0)*500+(0)*1000)/5000,0)-1)*25+IF(((1)*80+(MAX(0,C46-1))*200+(0)*500+(0)*1000)&gt;5000,32-10,0))*500,2)),2)</f>
-        <v>93536.48</v>
+        <f>C46*$D$27+(ROUND((((80*2+20)*0.16/1000+(80*2+20)*32/1000000*0.12)*500),2)+80*2*(4000*0.4+300*1.6)/1000000*500+MAX(0,C46-1)*(ROUND((((200*2+20)*0.16/1000+(200*2+20)*32/1000000*0.12)*500),2)+200*2*(4000*0.4+300*1.6)/1000000*500))+C46*$D$29+'Clientes e Ingresos'!D17*(8*(496838.17/30/8))+(ROUND((MAX(0,((1)*1+(MAX(0,C46-1))*3+(0)*8+(0)*16)-100)*0.0213+MAX(0,((1)*1.056+(MAX(0,C46-1))*2.63999999999999+(0)*6.6+(0)*13.2)-250)*0.09+(MAX(0,ROUNDUP((((1)*0.06+(MAX(0,C46-1))*0.15)+((0)*0.375+(0)*0.75)*0.05)*2,0)-8)+((1)*0+(MAX(0,C46-1))*0+(0)*0+(0)*0))*0.125+IF(((1)*80+(MAX(0,C46-1))*200)&lt;=2000,10,IF(((1)*80+(MAX(0,C46-1))*200)&lt;=5000,15,IF(((1)*80+(MAX(0,C46-1))*200)&lt;=10000,60,110)))-10)*500,2)+ROUND((MAX(0,((1)*0.166864+(MAX(0,C46-1))*0.41716+(0)*1.0429+(0)*2.0858)+20*2*2*0.0035+30*(1/3600*0.128+5/3600*0.0106)-20)+IF(AND(((1)*55680+(MAX(0,C46-1))*139200+(0)*348000+(0)*696000)&lt;=1000000,((1)*1.536+(MAX(0,C46-1))*3.84+(0)*9.6+(0)*19.2)&lt;=1000),0,IF(((1)*55680+(MAX(0,C46-1))*139200+(0)*348000+(0)*696000)&lt;=10000000,20,IF(((1)*55680+(MAX(0,C46-1))*139200+(0)*348000+(0)*696000)&lt;=50000000,100,300)))+MAX(0,ROUNDUP(((1)*80+(MAX(0,C46-1))*200+(0)*500+(0)*1000)/5000,0)-1)*25+IF(((1)*80+(MAX(0,C46-1))*200+(0)*500+(0)*1000)&gt;5000,32-10,0))*500,2))</f>
+        <v>49588.865625000006</v>
       </c>
       <c r="F46" s="10">
         <f>D46+E46</f>
-        <v>184661.47999999998</v>
+        <v>163836.4102916667</v>
       </c>
     </row>
     <row r="47">
@@ -3124,15 +3132,15 @@
       <c r="C47" s="19" t="n"/>
       <c r="D47" s="15">
         <f>SUM(D35:D46)</f>
-        <v>1093500.0</v>
+        <v>1448654.3530000004</v>
       </c>
       <c r="E47" s="15">
         <f>SUM(E35:E46)</f>
-        <v>1081516.44</v>
+        <v>536566.02175</v>
       </c>
       <c r="F47" s="15">
         <f>SUM(F35:F46)</f>
-        <v>2175016.44</v>
+        <v>1985220.3747499997</v>
       </c>
     </row>
   </sheetData>
@@ -3150,16 +3158,16 @@
   <dimension ref="B2:H32"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="25" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
-    <col width="22" customWidth="1" min="6" max="7"/>
-    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" style="51" min="1" max="1"/>
+    <col width="30" customWidth="1" style="51" min="2" max="2"/>
+    <col width="25" customWidth="1" style="51" min="3" max="3"/>
+    <col width="22" customWidth="1" style="51" min="4" max="4"/>
+    <col width="20" customWidth="1" style="51" min="5" max="5"/>
+    <col width="22" customWidth="1" style="51" min="6" max="7"/>
+    <col width="16" customWidth="1" style="51" min="8" max="8"/>
   </cols>
   <sheetData>
-    <row r="2" ht="21" customHeight="1">
+    <row r="2" ht="21" customHeight="1" s="51">
       <c r="B2" s="1" t="inlineStr">
         <is>
           <t>ANÁLISIS DE PUNTO DE EQUILIBRIO</t>
@@ -3173,7 +3181,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="17.4" customHeight="1">
+    <row r="5" ht="17.4" customHeight="1" s="51">
       <c r="B5" s="3" t="inlineStr">
         <is>
           <t>VARIABLES DE ENTRADA</t>
@@ -3181,54 +3189,54 @@
       </c>
     </row>
     <row r="6">
-      <c r="B6" s="49" t="inlineStr">
+      <c r="B6" s="59" t="inlineStr">
         <is>
           <t>Precio medio de la mezcla inicial</t>
         </is>
       </c>
-      <c r="C6" s="53" t="n"/>
+      <c r="C6" s="46" t="n"/>
       <c r="D6" s="20">
         <f>'Clientes e Ingresos'!G6</f>
         <v>23000.0</v>
       </c>
     </row>
     <row r="7">
-      <c r="B7" s="49" t="inlineStr">
+      <c r="B7" s="59" t="inlineStr">
         <is>
           <t>Costo Variable por Gimnasio (CVU)</t>
         </is>
       </c>
-      <c r="C7" s="53" t="n"/>
+      <c r="C7" s="46" t="n"/>
       <c r="D7" s="20">
         <f>'Egresos e Inversión'!D30</f>
-        <v>2896.558</v>
+        <v>1431.6375208333334</v>
       </c>
     </row>
     <row r="8">
-      <c r="B8" s="49" t="inlineStr">
+      <c r="B8" s="59" t="inlineStr">
         <is>
           <t>Margen de Contribución Unitario (MC = P - CVU)</t>
         </is>
       </c>
-      <c r="C8" s="53" t="n"/>
+      <c r="C8" s="46" t="n"/>
       <c r="D8" s="20">
         <f>D6-D7</f>
-        <v>20103.442</v>
+        <v>21568.362479166666</v>
       </c>
     </row>
     <row r="9">
-      <c r="B9" s="49" t="inlineStr">
+      <c r="B9" s="59" t="inlineStr">
         <is>
           <t>Costos Fijos Mensuales Base (CF)</t>
         </is>
       </c>
-      <c r="C9" s="53" t="n"/>
+      <c r="C9" s="46" t="n"/>
       <c r="D9" s="20">
         <f>'Egresos e Inversión'!D22</f>
-        <v>91125.0</v>
-      </c>
-    </row>
-    <row r="11" ht="17.4" customHeight="1">
+        <v>114247.54466666667</v>
+      </c>
+    </row>
+    <row r="11" ht="17.4" customHeight="1" s="51">
       <c r="B11" s="3" t="inlineStr">
         <is>
           <t>RESULTADO DEL PUNTO DE EQUILIBRIO</t>
@@ -3236,27 +3244,27 @@
       </c>
     </row>
     <row r="12">
-      <c r="B12" s="49" t="inlineStr">
+      <c r="B12" s="59" t="inlineStr">
         <is>
           <t>Umbral teórico (sin salto de nube)</t>
         </is>
       </c>
-      <c r="C12" s="53" t="n"/>
+      <c r="C12" s="46" t="n"/>
       <c r="D12" s="21">
-        <f>(D9+2681.15-2950.41-15000+25000)/(25000-2950.41)</f>
-        <v>4.574041512790033</v>
+        <f>(D9+('Egresos e Inversión'!D27+181.15)-('Egresos e Inversión'!D27+450.41)-15000+25000)/(25000-('Egresos e Inversión'!D27+450.41))</f>
+        <v>5.2724161439171215</v>
       </c>
     </row>
     <row r="13">
-      <c r="B13" s="48" t="inlineStr">
+      <c r="B13" s="58" t="inlineStr">
         <is>
           <t>Gimnasios Requeridos (Redondeado)</t>
         </is>
       </c>
-      <c r="C13" s="53" t="n"/>
+      <c r="C13" s="46" t="n"/>
       <c r="D13" s="22">
         <f>IF(MIN(IF(G18&gt;=0,B18,999),IF(G19&gt;=0,B19,999),IF(G20&gt;=0,B20,999),IF(G21&gt;=0,B21,999),IF(G22&gt;=0,B22,999),IF(G23&gt;=0,B23,999),IF(G24&gt;=0,B24,999),IF(G25&gt;=0,B25,999),IF(G26&gt;=0,B26,999),IF(G27&gt;=0,B27,999),IF(G28&gt;=0,B28,999),IF(G29&gt;=0,B29,999),IF(G30&gt;=0,B30,999),IF(G31&gt;=0,B31,999),IF(G32&gt;=0,B32,999))=999,"Fuera de tabla",MIN(IF(G18&gt;=0,B18,999),IF(G19&gt;=0,B19,999),IF(G20&gt;=0,B20,999),IF(G21&gt;=0,B21,999),IF(G22&gt;=0,B22,999),IF(G23&gt;=0,B23,999),IF(G24&gt;=0,B24,999),IF(G25&gt;=0,B25,999),IF(G26&gt;=0,B26,999),IF(G27&gt;=0,B27,999),IF(G28&gt;=0,B28,999),IF(G29&gt;=0,B29,999),IF(G30&gt;=0,B30,999),IF(G31&gt;=0,B31,999),IF(G32&gt;=0,B32,999)))</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -3264,19 +3272,19 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="23.4" customHeight="1">
-      <c r="B14" s="48" t="inlineStr">
+    <row r="14" ht="23.4" customHeight="1" s="51">
+      <c r="B14" s="58" t="inlineStr">
         <is>
           <t>Facturación Mínima Mensual (₡)</t>
         </is>
       </c>
-      <c r="C14" s="53" t="n"/>
+      <c r="C14" s="46" t="n"/>
       <c r="D14" s="23">
         <f>IF(ISNUMBER(D13),15000+MAX(0,D13-1)*25000,"Fuera de tabla")</f>
-        <v>115000.0</v>
-      </c>
-    </row>
-    <row r="16" ht="17.4" customHeight="1">
+        <v>140000.0</v>
+      </c>
+    </row>
+    <row r="16" ht="17.4" customHeight="1" s="51">
       <c r="B16" s="3" t="inlineStr">
         <is>
           <t>TABLA DE SENSIBILIDAD Y RESULTADO OPERATIVO SEGÚN VOLUMEN</t>
@@ -3329,20 +3337,20 @@
         <v>15000.0</v>
       </c>
       <c r="D18" s="10">
-        <f>ROUND(B18*'Egresos e Inversión'!$D$27+(ROUND((((80*2+20)*0.16/1000+(80*2+20)*32/1000000*0.12)*500),2)+80*2*(4000*0.4+300*1.6)/1000000*500+MAX(0,B18-1)*(ROUND((((200*2+20)*0.16/1000+(200*2+20)*32/1000000*0.12)*500),2)+200*2*(4000*0.4+300*1.6)/1000000*500))+B18*'Egresos e Inversión'!$D$29+(ROUND((MAX(0,((1)*1+(MAX(0,B18-1))*3+(0)*8+(0)*16)-100)*0.0213+MAX(0,((1)*1.056+(MAX(0,B18-1))*2.6399999999999997+(0)*6.6+(0)*13.2)-250)*0.09+(MAX(0,ROUNDUP((((1)*0.06+(MAX(0,B18-1))*0.15)+((0)*0.375+(0)*0.75)*0.05)*2,0)-8)+((1)*0+(MAX(0,B18-1))*0+(0)*0+(0)*0))*0.125+IF(((1)*80+(MAX(0,B18-1))*200)&lt;=2000,10,IF(((1)*80+(MAX(0,B18-1))*200)&lt;=5000,15,IF(((1)*80+(MAX(0,B18-1))*200)&lt;=10000,60,110)))-10)*500,2)+ROUND((MAX(0,((1)*0.166864+(MAX(0,B18-1))*0.41716+(0)*1.0429000000000002+(0)*2.0858000000000003)+20*2*2*0.0035+30*(1/3600*0.128+5/3600*0.0106)-20)+IF(AND(((1)*55680.0+(MAX(0,B18-1))*139200.0+(0)*348000.0+(0)*696000.0)&lt;=1000000,((1)*1.536+(MAX(0,B18-1))*3.84+(0)*9.6+(0)*19.2)&lt;=1000),0,IF(((1)*55680.0+(MAX(0,B18-1))*139200.0+(0)*348000.0+(0)*696000.0)&lt;=10000000,20,IF(((1)*55680.0+(MAX(0,B18-1))*139200.0+(0)*348000.0+(0)*696000.0)&lt;=50000000,100,300)))+MAX(0,ROUNDUP(((1)*80+(MAX(0,B18-1))*200+(0)*500+(0)*1000)/5000,0)-1)*25+IF(((1)*80+(MAX(0,B18-1))*200+(0)*500+(0)*1000)&gt;5000,32-10,0))*500,2)),2)</f>
-        <v>2681.15</v>
+        <f>ROUND(B18*'Egresos e Inversión'!$D$27+(ROUND((((80*2+20)*0.16/1000+(80*2+20)*32/1000000*0.12)*500),2)+80*2*(4000*0.4+300*1.6)/1000000*500+MAX(0,B18-1)*(ROUND((((200*2+20)*0.16/1000+(200*2+20)*32/1000000*0.12)*500),2)+200*2*(4000*0.4+300*1.6)/1000000*500))+B18*'Egresos e Inversión'!$D$29+(ROUND((MAX(0,((1)*1+(MAX(0,B18-1))*3+(0)*8+(0)*16)-100)*0.0213+MAX(0,((1)*1.056+(MAX(0,B18-1))*2.63999999999999+(0)*6.6+(0)*13.2)-250)*0.09+(MAX(0,ROUNDUP((((1)*0.06+(MAX(0,B18-1))*0.15)+((0)*0.375+(0)*0.75)*0.05)*2,0)-8)+((1)*0+(MAX(0,B18-1))*0+(0)*0+(0)*0))*0.125+IF(((1)*80+(MAX(0,B18-1))*200)&lt;=2000,10,IF(((1)*80+(MAX(0,B18-1))*200)&lt;=5000,15,IF(((1)*80+(MAX(0,B18-1))*200)&lt;=10000,60,110)))-10)*500,2)+ROUND((MAX(0,((1)*0.166864+(MAX(0,B18-1))*0.41716+(0)*1.0429+(0)*2.0858)+20*2*2*0.0035+30*(1/3600*0.128+5/3600*0.0106)-20)+IF(AND(((1)*55680+(MAX(0,B18-1))*139200+(0)*348000+(0)*696000)&lt;=1000000,((1)*1.536+(MAX(0,B18-1))*3.84+(0)*9.6+(0)*19.2)&lt;=1000),0,IF(((1)*55680+(MAX(0,B18-1))*139200+(0)*348000+(0)*696000)&lt;=10000000,20,IF(((1)*55680+(MAX(0,B18-1))*139200+(0)*348000+(0)*696000)&lt;=50000000,100,300)))+MAX(0,ROUNDUP(((1)*80+(MAX(0,B18-1))*200+(0)*500+(0)*1000)/5000,0)-1)*25+IF(((1)*80+(MAX(0,B18-1))*200+(0)*500+(0)*1000)&gt;5000,32-10,0))*500,2)),2)</f>
+        <v>1216.23</v>
       </c>
       <c r="E18" s="10">
         <f>$D$9</f>
-        <v>91125.0</v>
+        <v>114247.54466666667</v>
       </c>
       <c r="F18" s="10">
         <f>D18+E18</f>
-        <v>93806.15</v>
+        <v>115463.77466666666</v>
       </c>
       <c r="G18" s="10">
         <f>C18-F18</f>
-        <v>-78806.15</v>
+        <v>-100463.77466666666</v>
       </c>
       <c r="H18" s="8" t="str">
         <f>IF(G18&lt;0,"Pérdida",IF(G18=0,"Equilibrio","Ganancia"))</f>
@@ -3358,20 +3366,20 @@
         <v>40000.0</v>
       </c>
       <c r="D19" s="7">
-        <f>ROUND(B19*'Egresos e Inversión'!$D$27+(ROUND((((80*2+20)*0.16/1000+(80*2+20)*32/1000000*0.12)*500),2)+80*2*(4000*0.4+300*1.6)/1000000*500+MAX(0,B19-1)*(ROUND((((200*2+20)*0.16/1000+(200*2+20)*32/1000000*0.12)*500),2)+200*2*(4000*0.4+300*1.6)/1000000*500))+B19*'Egresos e Inversión'!$D$29+(ROUND((MAX(0,((1)*1+(MAX(0,B19-1))*3+(0)*8+(0)*16)-100)*0.0213+MAX(0,((1)*1.056+(MAX(0,B19-1))*2.6399999999999997+(0)*6.6+(0)*13.2)-250)*0.09+(MAX(0,ROUNDUP((((1)*0.06+(MAX(0,B19-1))*0.15)+((0)*0.375+(0)*0.75)*0.05)*2,0)-8)+((1)*0+(MAX(0,B19-1))*0+(0)*0+(0)*0))*0.125+IF(((1)*80+(MAX(0,B19-1))*200)&lt;=2000,10,IF(((1)*80+(MAX(0,B19-1))*200)&lt;=5000,15,IF(((1)*80+(MAX(0,B19-1))*200)&lt;=10000,60,110)))-10)*500,2)+ROUND((MAX(0,((1)*0.166864+(MAX(0,B19-1))*0.41716+(0)*1.0429000000000002+(0)*2.0858000000000003)+20*2*2*0.0035+30*(1/3600*0.128+5/3600*0.0106)-20)+IF(AND(((1)*55680.0+(MAX(0,B19-1))*139200.0+(0)*348000.0+(0)*696000.0)&lt;=1000000,((1)*1.536+(MAX(0,B19-1))*3.84+(0)*9.6+(0)*19.2)&lt;=1000),0,IF(((1)*55680.0+(MAX(0,B19-1))*139200.0+(0)*348000.0+(0)*696000.0)&lt;=10000000,20,IF(((1)*55680.0+(MAX(0,B19-1))*139200.0+(0)*348000.0+(0)*696000.0)&lt;=50000000,100,300)))+MAX(0,ROUNDUP(((1)*80+(MAX(0,B19-1))*200+(0)*500+(0)*1000)/5000,0)-1)*25+IF(((1)*80+(MAX(0,B19-1))*200+(0)*500+(0)*1000)&gt;5000,32-10,0))*500,2)),2)</f>
-        <v>5631.56</v>
+        <f>ROUND(B19*'Egresos e Inversión'!$D$27+(ROUND((((80*2+20)*0.16/1000+(80*2+20)*32/1000000*0.12)*500),2)+80*2*(4000*0.4+300*1.6)/1000000*500+MAX(0,B19-1)*(ROUND((((200*2+20)*0.16/1000+(200*2+20)*32/1000000*0.12)*500),2)+200*2*(4000*0.4+300*1.6)/1000000*500))+B19*'Egresos e Inversión'!$D$29+(ROUND((MAX(0,((1)*1+(MAX(0,B19-1))*3+(0)*8+(0)*16)-100)*0.0213+MAX(0,((1)*1.056+(MAX(0,B19-1))*2.63999999999999+(0)*6.6+(0)*13.2)-250)*0.09+(MAX(0,ROUNDUP((((1)*0.06+(MAX(0,B19-1))*0.15)+((0)*0.375+(0)*0.75)*0.05)*2,0)-8)+((1)*0+(MAX(0,B19-1))*0+(0)*0+(0)*0))*0.125+IF(((1)*80+(MAX(0,B19-1))*200)&lt;=2000,10,IF(((1)*80+(MAX(0,B19-1))*200)&lt;=5000,15,IF(((1)*80+(MAX(0,B19-1))*200)&lt;=10000,60,110)))-10)*500,2)+ROUND((MAX(0,((1)*0.166864+(MAX(0,B19-1))*0.41716+(0)*1.0429+(0)*2.0858)+20*2*2*0.0035+30*(1/3600*0.128+5/3600*0.0106)-20)+IF(AND(((1)*55680+(MAX(0,B19-1))*139200+(0)*348000+(0)*696000)&lt;=1000000,((1)*1.536+(MAX(0,B19-1))*3.84+(0)*9.6+(0)*19.2)&lt;=1000),0,IF(((1)*55680+(MAX(0,B19-1))*139200+(0)*348000+(0)*696000)&lt;=10000000,20,IF(((1)*55680+(MAX(0,B19-1))*139200+(0)*348000+(0)*696000)&lt;=50000000,100,300)))+MAX(0,ROUNDUP(((1)*80+(MAX(0,B19-1))*200+(0)*500+(0)*1000)/5000,0)-1)*25+IF(((1)*80+(MAX(0,B19-1))*200+(0)*500+(0)*1000)&gt;5000,32-10,0))*500,2)),2)</f>
+        <v>2701.72</v>
       </c>
       <c r="E19" s="7">
         <f>$D$9</f>
-        <v>91125.0</v>
+        <v>114247.54466666667</v>
       </c>
       <c r="F19" s="7">
         <f>D19+E19</f>
-        <v>96756.56</v>
+        <v>116949.26466666667</v>
       </c>
       <c r="G19" s="7">
         <f>C19-F19</f>
-        <v>-56756.56</v>
+        <v>-76949.26466666667</v>
       </c>
       <c r="H19" s="5" t="str">
         <f>IF(G19&lt;0,"Pérdida",IF(G19=0,"Equilibrio","Ganancia"))</f>
@@ -3387,20 +3395,20 @@
         <v>65000.0</v>
       </c>
       <c r="D20" s="10">
-        <f>ROUND(B20*'Egresos e Inversión'!$D$27+(ROUND((((80*2+20)*0.16/1000+(80*2+20)*32/1000000*0.12)*500),2)+80*2*(4000*0.4+300*1.6)/1000000*500+MAX(0,B20-1)*(ROUND((((200*2+20)*0.16/1000+(200*2+20)*32/1000000*0.12)*500),2)+200*2*(4000*0.4+300*1.6)/1000000*500))+B20*'Egresos e Inversión'!$D$29+(ROUND((MAX(0,((1)*1+(MAX(0,B20-1))*3+(0)*8+(0)*16)-100)*0.0213+MAX(0,((1)*1.056+(MAX(0,B20-1))*2.6399999999999997+(0)*6.6+(0)*13.2)-250)*0.09+(MAX(0,ROUNDUP((((1)*0.06+(MAX(0,B20-1))*0.15)+((0)*0.375+(0)*0.75)*0.05)*2,0)-8)+((1)*0+(MAX(0,B20-1))*0+(0)*0+(0)*0))*0.125+IF(((1)*80+(MAX(0,B20-1))*200)&lt;=2000,10,IF(((1)*80+(MAX(0,B20-1))*200)&lt;=5000,15,IF(((1)*80+(MAX(0,B20-1))*200)&lt;=10000,60,110)))-10)*500,2)+ROUND((MAX(0,((1)*0.166864+(MAX(0,B20-1))*0.41716+(0)*1.0429000000000002+(0)*2.0858000000000003)+20*2*2*0.0035+30*(1/3600*0.128+5/3600*0.0106)-20)+IF(AND(((1)*55680.0+(MAX(0,B20-1))*139200.0+(0)*348000.0+(0)*696000.0)&lt;=1000000,((1)*1.536+(MAX(0,B20-1))*3.84+(0)*9.6+(0)*19.2)&lt;=1000),0,IF(((1)*55680.0+(MAX(0,B20-1))*139200.0+(0)*348000.0+(0)*696000.0)&lt;=10000000,20,IF(((1)*55680.0+(MAX(0,B20-1))*139200.0+(0)*348000.0+(0)*696000.0)&lt;=50000000,100,300)))+MAX(0,ROUNDUP(((1)*80+(MAX(0,B20-1))*200+(0)*500+(0)*1000)/5000,0)-1)*25+IF(((1)*80+(MAX(0,B20-1))*200+(0)*500+(0)*1000)&gt;5000,32-10,0))*500,2)),2)</f>
-        <v>8581.97</v>
+        <f>ROUND(B20*'Egresos e Inversión'!$D$27+(ROUND((((80*2+20)*0.16/1000+(80*2+20)*32/1000000*0.12)*500),2)+80*2*(4000*0.4+300*1.6)/1000000*500+MAX(0,B20-1)*(ROUND((((200*2+20)*0.16/1000+(200*2+20)*32/1000000*0.12)*500),2)+200*2*(4000*0.4+300*1.6)/1000000*500))+B20*'Egresos e Inversión'!$D$29+(ROUND((MAX(0,((1)*1+(MAX(0,B20-1))*3+(0)*8+(0)*16)-100)*0.0213+MAX(0,((1)*1.056+(MAX(0,B20-1))*2.63999999999999+(0)*6.6+(0)*13.2)-250)*0.09+(MAX(0,ROUNDUP((((1)*0.06+(MAX(0,B20-1))*0.15)+((0)*0.375+(0)*0.75)*0.05)*2,0)-8)+((1)*0+(MAX(0,B20-1))*0+(0)*0+(0)*0))*0.125+IF(((1)*80+(MAX(0,B20-1))*200)&lt;=2000,10,IF(((1)*80+(MAX(0,B20-1))*200)&lt;=5000,15,IF(((1)*80+(MAX(0,B20-1))*200)&lt;=10000,60,110)))-10)*500,2)+ROUND((MAX(0,((1)*0.166864+(MAX(0,B20-1))*0.41716+(0)*1.0429+(0)*2.0858)+20*2*2*0.0035+30*(1/3600*0.128+5/3600*0.0106)-20)+IF(AND(((1)*55680+(MAX(0,B20-1))*139200+(0)*348000+(0)*696000)&lt;=1000000,((1)*1.536+(MAX(0,B20-1))*3.84+(0)*9.6+(0)*19.2)&lt;=1000),0,IF(((1)*55680+(MAX(0,B20-1))*139200+(0)*348000+(0)*696000)&lt;=10000000,20,IF(((1)*55680+(MAX(0,B20-1))*139200+(0)*348000+(0)*696000)&lt;=50000000,100,300)))+MAX(0,ROUNDUP(((1)*80+(MAX(0,B20-1))*200+(0)*500+(0)*1000)/5000,0)-1)*25+IF(((1)*80+(MAX(0,B20-1))*200+(0)*500+(0)*1000)&gt;5000,32-10,0))*500,2)),2)</f>
+        <v>4187.21</v>
       </c>
       <c r="E20" s="10">
         <f>$D$9</f>
-        <v>91125.0</v>
+        <v>114247.54466666667</v>
       </c>
       <c r="F20" s="10">
         <f>D20+E20</f>
-        <v>99706.97</v>
+        <v>118434.75466666667</v>
       </c>
       <c r="G20" s="10">
         <f>C20-F20</f>
-        <v>-34706.97</v>
+        <v>-53434.754666666675</v>
       </c>
       <c r="H20" s="8" t="str">
         <f>IF(G20&lt;0,"Pérdida",IF(G20=0,"Equilibrio","Ganancia"))</f>
@@ -3416,20 +3424,20 @@
         <v>90000.0</v>
       </c>
       <c r="D21" s="7">
-        <f>ROUND(B21*'Egresos e Inversión'!$D$27+(ROUND((((80*2+20)*0.16/1000+(80*2+20)*32/1000000*0.12)*500),2)+80*2*(4000*0.4+300*1.6)/1000000*500+MAX(0,B21-1)*(ROUND((((200*2+20)*0.16/1000+(200*2+20)*32/1000000*0.12)*500),2)+200*2*(4000*0.4+300*1.6)/1000000*500))+B21*'Egresos e Inversión'!$D$29+(ROUND((MAX(0,((1)*1+(MAX(0,B21-1))*3+(0)*8+(0)*16)-100)*0.0213+MAX(0,((1)*1.056+(MAX(0,B21-1))*2.6399999999999997+(0)*6.6+(0)*13.2)-250)*0.09+(MAX(0,ROUNDUP((((1)*0.06+(MAX(0,B21-1))*0.15)+((0)*0.375+(0)*0.75)*0.05)*2,0)-8)+((1)*0+(MAX(0,B21-1))*0+(0)*0+(0)*0))*0.125+IF(((1)*80+(MAX(0,B21-1))*200)&lt;=2000,10,IF(((1)*80+(MAX(0,B21-1))*200)&lt;=5000,15,IF(((1)*80+(MAX(0,B21-1))*200)&lt;=10000,60,110)))-10)*500,2)+ROUND((MAX(0,((1)*0.166864+(MAX(0,B21-1))*0.41716+(0)*1.0429000000000002+(0)*2.0858000000000003)+20*2*2*0.0035+30*(1/3600*0.128+5/3600*0.0106)-20)+IF(AND(((1)*55680.0+(MAX(0,B21-1))*139200.0+(0)*348000.0+(0)*696000.0)&lt;=1000000,((1)*1.536+(MAX(0,B21-1))*3.84+(0)*9.6+(0)*19.2)&lt;=1000),0,IF(((1)*55680.0+(MAX(0,B21-1))*139200.0+(0)*348000.0+(0)*696000.0)&lt;=10000000,20,IF(((1)*55680.0+(MAX(0,B21-1))*139200.0+(0)*348000.0+(0)*696000.0)&lt;=50000000,100,300)))+MAX(0,ROUNDUP(((1)*80+(MAX(0,B21-1))*200+(0)*500+(0)*1000)/5000,0)-1)*25+IF(((1)*80+(MAX(0,B21-1))*200+(0)*500+(0)*1000)&gt;5000,32-10,0))*500,2)),2)</f>
-        <v>11532.38</v>
+        <f>ROUND(B21*'Egresos e Inversión'!$D$27+(ROUND((((80*2+20)*0.16/1000+(80*2+20)*32/1000000*0.12)*500),2)+80*2*(4000*0.4+300*1.6)/1000000*500+MAX(0,B21-1)*(ROUND((((200*2+20)*0.16/1000+(200*2+20)*32/1000000*0.12)*500),2)+200*2*(4000*0.4+300*1.6)/1000000*500))+B21*'Egresos e Inversión'!$D$29+(ROUND((MAX(0,((1)*1+(MAX(0,B21-1))*3+(0)*8+(0)*16)-100)*0.0213+MAX(0,((1)*1.056+(MAX(0,B21-1))*2.63999999999999+(0)*6.6+(0)*13.2)-250)*0.09+(MAX(0,ROUNDUP((((1)*0.06+(MAX(0,B21-1))*0.15)+((0)*0.375+(0)*0.75)*0.05)*2,0)-8)+((1)*0+(MAX(0,B21-1))*0+(0)*0+(0)*0))*0.125+IF(((1)*80+(MAX(0,B21-1))*200)&lt;=2000,10,IF(((1)*80+(MAX(0,B21-1))*200)&lt;=5000,15,IF(((1)*80+(MAX(0,B21-1))*200)&lt;=10000,60,110)))-10)*500,2)+ROUND((MAX(0,((1)*0.166864+(MAX(0,B21-1))*0.41716+(0)*1.0429+(0)*2.0858)+20*2*2*0.0035+30*(1/3600*0.128+5/3600*0.0106)-20)+IF(AND(((1)*55680+(MAX(0,B21-1))*139200+(0)*348000+(0)*696000)&lt;=1000000,((1)*1.536+(MAX(0,B21-1))*3.84+(0)*9.6+(0)*19.2)&lt;=1000),0,IF(((1)*55680+(MAX(0,B21-1))*139200+(0)*348000+(0)*696000)&lt;=10000000,20,IF(((1)*55680+(MAX(0,B21-1))*139200+(0)*348000+(0)*696000)&lt;=50000000,100,300)))+MAX(0,ROUNDUP(((1)*80+(MAX(0,B21-1))*200+(0)*500+(0)*1000)/5000,0)-1)*25+IF(((1)*80+(MAX(0,B21-1))*200+(0)*500+(0)*1000)&gt;5000,32-10,0))*500,2)),2)</f>
+        <v>5672.7</v>
       </c>
       <c r="E21" s="7">
         <f>$D$9</f>
-        <v>91125.0</v>
+        <v>114247.54466666667</v>
       </c>
       <c r="F21" s="7">
         <f>D21+E21</f>
-        <v>102657.38</v>
+        <v>119920.24466666667</v>
       </c>
       <c r="G21" s="7">
         <f>C21-F21</f>
-        <v>-12657.380000000005</v>
+        <v>-29920.244666666666</v>
       </c>
       <c r="H21" s="5" t="str">
         <f>IF(G21&lt;0,"Pérdida",IF(G21=0,"Equilibrio","Ganancia"))</f>
@@ -3445,24 +3453,24 @@
         <v>115000.0</v>
       </c>
       <c r="D22" s="25">
-        <f>ROUND(B22*'Egresos e Inversión'!$D$27+(ROUND((((80*2+20)*0.16/1000+(80*2+20)*32/1000000*0.12)*500),2)+80*2*(4000*0.4+300*1.6)/1000000*500+MAX(0,B22-1)*(ROUND((((200*2+20)*0.16/1000+(200*2+20)*32/1000000*0.12)*500),2)+200*2*(4000*0.4+300*1.6)/1000000*500))+B22*'Egresos e Inversión'!$D$29+(ROUND((MAX(0,((1)*1+(MAX(0,B22-1))*3+(0)*8+(0)*16)-100)*0.0213+MAX(0,((1)*1.056+(MAX(0,B22-1))*2.6399999999999997+(0)*6.6+(0)*13.2)-250)*0.09+(MAX(0,ROUNDUP((((1)*0.06+(MAX(0,B22-1))*0.15)+((0)*0.375+(0)*0.75)*0.05)*2,0)-8)+((1)*0+(MAX(0,B22-1))*0+(0)*0+(0)*0))*0.125+IF(((1)*80+(MAX(0,B22-1))*200)&lt;=2000,10,IF(((1)*80+(MAX(0,B22-1))*200)&lt;=5000,15,IF(((1)*80+(MAX(0,B22-1))*200)&lt;=10000,60,110)))-10)*500,2)+ROUND((MAX(0,((1)*0.166864+(MAX(0,B22-1))*0.41716+(0)*1.0429000000000002+(0)*2.0858000000000003)+20*2*2*0.0035+30*(1/3600*0.128+5/3600*0.0106)-20)+IF(AND(((1)*55680.0+(MAX(0,B22-1))*139200.0+(0)*348000.0+(0)*696000.0)&lt;=1000000,((1)*1.536+(MAX(0,B22-1))*3.84+(0)*9.6+(0)*19.2)&lt;=1000),0,IF(((1)*55680.0+(MAX(0,B22-1))*139200.0+(0)*348000.0+(0)*696000.0)&lt;=10000000,20,IF(((1)*55680.0+(MAX(0,B22-1))*139200.0+(0)*348000.0+(0)*696000.0)&lt;=50000000,100,300)))+MAX(0,ROUNDUP(((1)*80+(MAX(0,B22-1))*200+(0)*500+(0)*1000)/5000,0)-1)*25+IF(((1)*80+(MAX(0,B22-1))*200+(0)*500+(0)*1000)&gt;5000,32-10,0))*500,2)),2)</f>
-        <v>14482.79</v>
+        <f>ROUND(B22*'Egresos e Inversión'!$D$27+(ROUND((((80*2+20)*0.16/1000+(80*2+20)*32/1000000*0.12)*500),2)+80*2*(4000*0.4+300*1.6)/1000000*500+MAX(0,B22-1)*(ROUND((((200*2+20)*0.16/1000+(200*2+20)*32/1000000*0.12)*500),2)+200*2*(4000*0.4+300*1.6)/1000000*500))+B22*'Egresos e Inversión'!$D$29+(ROUND((MAX(0,((1)*1+(MAX(0,B22-1))*3+(0)*8+(0)*16)-100)*0.0213+MAX(0,((1)*1.056+(MAX(0,B22-1))*2.63999999999999+(0)*6.6+(0)*13.2)-250)*0.09+(MAX(0,ROUNDUP((((1)*0.06+(MAX(0,B22-1))*0.15)+((0)*0.375+(0)*0.75)*0.05)*2,0)-8)+((1)*0+(MAX(0,B22-1))*0+(0)*0+(0)*0))*0.125+IF(((1)*80+(MAX(0,B22-1))*200)&lt;=2000,10,IF(((1)*80+(MAX(0,B22-1))*200)&lt;=5000,15,IF(((1)*80+(MAX(0,B22-1))*200)&lt;=10000,60,110)))-10)*500,2)+ROUND((MAX(0,((1)*0.166864+(MAX(0,B22-1))*0.41716+(0)*1.0429+(0)*2.0858)+20*2*2*0.0035+30*(1/3600*0.128+5/3600*0.0106)-20)+IF(AND(((1)*55680+(MAX(0,B22-1))*139200+(0)*348000+(0)*696000)&lt;=1000000,((1)*1.536+(MAX(0,B22-1))*3.84+(0)*9.6+(0)*19.2)&lt;=1000),0,IF(((1)*55680+(MAX(0,B22-1))*139200+(0)*348000+(0)*696000)&lt;=10000000,20,IF(((1)*55680+(MAX(0,B22-1))*139200+(0)*348000+(0)*696000)&lt;=50000000,100,300)))+MAX(0,ROUNDUP(((1)*80+(MAX(0,B22-1))*200+(0)*500+(0)*1000)/5000,0)-1)*25+IF(((1)*80+(MAX(0,B22-1))*200+(0)*500+(0)*1000)&gt;5000,32-10,0))*500,2)),2)</f>
+        <v>7158.19</v>
       </c>
       <c r="E22" s="25">
         <f>$D$9</f>
-        <v>91125.0</v>
+        <v>114247.54466666667</v>
       </c>
       <c r="F22" s="25">
         <f>D22+E22</f>
-        <v>105607.79000000001</v>
+        <v>121405.73466666667</v>
       </c>
       <c r="G22" s="25">
         <f>C22-F22</f>
-        <v>9392.209999999992</v>
+        <v>-6405.734666666671</v>
       </c>
       <c r="H22" s="26" t="str">
         <f>IF(G22&lt;0,"Pérdida",IF(G22=0,"Equilibrio","Ganancia"))</f>
-        <v>Ganancia</v>
+        <v>Pérdida</v>
       </c>
     </row>
     <row r="23">
@@ -3474,20 +3482,20 @@
         <v>140000.0</v>
       </c>
       <c r="D23" s="7">
-        <f>ROUND(B23*'Egresos e Inversión'!$D$27+(ROUND((((80*2+20)*0.16/1000+(80*2+20)*32/1000000*0.12)*500),2)+80*2*(4000*0.4+300*1.6)/1000000*500+MAX(0,B23-1)*(ROUND((((200*2+20)*0.16/1000+(200*2+20)*32/1000000*0.12)*500),2)+200*2*(4000*0.4+300*1.6)/1000000*500))+B23*'Egresos e Inversión'!$D$29+(ROUND((MAX(0,((1)*1+(MAX(0,B23-1))*3+(0)*8+(0)*16)-100)*0.0213+MAX(0,((1)*1.056+(MAX(0,B23-1))*2.6399999999999997+(0)*6.6+(0)*13.2)-250)*0.09+(MAX(0,ROUNDUP((((1)*0.06+(MAX(0,B23-1))*0.15)+((0)*0.375+(0)*0.75)*0.05)*2,0)-8)+((1)*0+(MAX(0,B23-1))*0+(0)*0+(0)*0))*0.125+IF(((1)*80+(MAX(0,B23-1))*200)&lt;=2000,10,IF(((1)*80+(MAX(0,B23-1))*200)&lt;=5000,15,IF(((1)*80+(MAX(0,B23-1))*200)&lt;=10000,60,110)))-10)*500,2)+ROUND((MAX(0,((1)*0.166864+(MAX(0,B23-1))*0.41716+(0)*1.0429000000000002+(0)*2.0858000000000003)+20*2*2*0.0035+30*(1/3600*0.128+5/3600*0.0106)-20)+IF(AND(((1)*55680.0+(MAX(0,B23-1))*139200.0+(0)*348000.0+(0)*696000.0)&lt;=1000000,((1)*1.536+(MAX(0,B23-1))*3.84+(0)*9.6+(0)*19.2)&lt;=1000),0,IF(((1)*55680.0+(MAX(0,B23-1))*139200.0+(0)*348000.0+(0)*696000.0)&lt;=10000000,20,IF(((1)*55680.0+(MAX(0,B23-1))*139200.0+(0)*348000.0+(0)*696000.0)&lt;=50000000,100,300)))+MAX(0,ROUNDUP(((1)*80+(MAX(0,B23-1))*200+(0)*500+(0)*1000)/5000,0)-1)*25+IF(((1)*80+(MAX(0,B23-1))*200+(0)*500+(0)*1000)&gt;5000,32-10,0))*500,2)),2)</f>
-        <v>17433.2</v>
+        <f>ROUND(B23*'Egresos e Inversión'!$D$27+(ROUND((((80*2+20)*0.16/1000+(80*2+20)*32/1000000*0.12)*500),2)+80*2*(4000*0.4+300*1.6)/1000000*500+MAX(0,B23-1)*(ROUND((((200*2+20)*0.16/1000+(200*2+20)*32/1000000*0.12)*500),2)+200*2*(4000*0.4+300*1.6)/1000000*500))+B23*'Egresos e Inversión'!$D$29+(ROUND((MAX(0,((1)*1+(MAX(0,B23-1))*3+(0)*8+(0)*16)-100)*0.0213+MAX(0,((1)*1.056+(MAX(0,B23-1))*2.63999999999999+(0)*6.6+(0)*13.2)-250)*0.09+(MAX(0,ROUNDUP((((1)*0.06+(MAX(0,B23-1))*0.15)+((0)*0.375+(0)*0.75)*0.05)*2,0)-8)+((1)*0+(MAX(0,B23-1))*0+(0)*0+(0)*0))*0.125+IF(((1)*80+(MAX(0,B23-1))*200)&lt;=2000,10,IF(((1)*80+(MAX(0,B23-1))*200)&lt;=5000,15,IF(((1)*80+(MAX(0,B23-1))*200)&lt;=10000,60,110)))-10)*500,2)+ROUND((MAX(0,((1)*0.166864+(MAX(0,B23-1))*0.41716+(0)*1.0429+(0)*2.0858)+20*2*2*0.0035+30*(1/3600*0.128+5/3600*0.0106)-20)+IF(AND(((1)*55680+(MAX(0,B23-1))*139200+(0)*348000+(0)*696000)&lt;=1000000,((1)*1.536+(MAX(0,B23-1))*3.84+(0)*9.6+(0)*19.2)&lt;=1000),0,IF(((1)*55680+(MAX(0,B23-1))*139200+(0)*348000+(0)*696000)&lt;=10000000,20,IF(((1)*55680+(MAX(0,B23-1))*139200+(0)*348000+(0)*696000)&lt;=50000000,100,300)))+MAX(0,ROUNDUP(((1)*80+(MAX(0,B23-1))*200+(0)*500+(0)*1000)/5000,0)-1)*25+IF(((1)*80+(MAX(0,B23-1))*200+(0)*500+(0)*1000)&gt;5000,32-10,0))*500,2)),2)</f>
+        <v>8643.68</v>
       </c>
       <c r="E23" s="7">
         <f>$D$9</f>
-        <v>91125.0</v>
+        <v>114247.54466666667</v>
       </c>
       <c r="F23" s="7">
         <f>D23+E23</f>
-        <v>108558.2</v>
+        <v>122891.22466666668</v>
       </c>
       <c r="G23" s="7">
         <f>C23-F23</f>
-        <v>31441.800000000003</v>
+        <v>17108.775333333324</v>
       </c>
       <c r="H23" s="5" t="str">
         <f>IF(G23&lt;0,"Pérdida",IF(G23=0,"Equilibrio","Ganancia"))</f>
@@ -3503,20 +3511,20 @@
         <v>165000.0</v>
       </c>
       <c r="D24" s="10">
-        <f>ROUND(B24*'Egresos e Inversión'!$D$27+(ROUND((((80*2+20)*0.16/1000+(80*2+20)*32/1000000*0.12)*500),2)+80*2*(4000*0.4+300*1.6)/1000000*500+MAX(0,B24-1)*(ROUND((((200*2+20)*0.16/1000+(200*2+20)*32/1000000*0.12)*500),2)+200*2*(4000*0.4+300*1.6)/1000000*500))+B24*'Egresos e Inversión'!$D$29+(ROUND((MAX(0,((1)*1+(MAX(0,B24-1))*3+(0)*8+(0)*16)-100)*0.0213+MAX(0,((1)*1.056+(MAX(0,B24-1))*2.6399999999999997+(0)*6.6+(0)*13.2)-250)*0.09+(MAX(0,ROUNDUP((((1)*0.06+(MAX(0,B24-1))*0.15)+((0)*0.375+(0)*0.75)*0.05)*2,0)-8)+((1)*0+(MAX(0,B24-1))*0+(0)*0+(0)*0))*0.125+IF(((1)*80+(MAX(0,B24-1))*200)&lt;=2000,10,IF(((1)*80+(MAX(0,B24-1))*200)&lt;=5000,15,IF(((1)*80+(MAX(0,B24-1))*200)&lt;=10000,60,110)))-10)*500,2)+ROUND((MAX(0,((1)*0.166864+(MAX(0,B24-1))*0.41716+(0)*1.0429000000000002+(0)*2.0858000000000003)+20*2*2*0.0035+30*(1/3600*0.128+5/3600*0.0106)-20)+IF(AND(((1)*55680.0+(MAX(0,B24-1))*139200.0+(0)*348000.0+(0)*696000.0)&lt;=1000000,((1)*1.536+(MAX(0,B24-1))*3.84+(0)*9.6+(0)*19.2)&lt;=1000),0,IF(((1)*55680.0+(MAX(0,B24-1))*139200.0+(0)*348000.0+(0)*696000.0)&lt;=10000000,20,IF(((1)*55680.0+(MAX(0,B24-1))*139200.0+(0)*348000.0+(0)*696000.0)&lt;=50000000,100,300)))+MAX(0,ROUNDUP(((1)*80+(MAX(0,B24-1))*200+(0)*500+(0)*1000)/5000,0)-1)*25+IF(((1)*80+(MAX(0,B24-1))*200+(0)*500+(0)*1000)&gt;5000,32-10,0))*500,2)),2)</f>
-        <v>20383.61</v>
+        <f>ROUND(B24*'Egresos e Inversión'!$D$27+(ROUND((((80*2+20)*0.16/1000+(80*2+20)*32/1000000*0.12)*500),2)+80*2*(4000*0.4+300*1.6)/1000000*500+MAX(0,B24-1)*(ROUND((((200*2+20)*0.16/1000+(200*2+20)*32/1000000*0.12)*500),2)+200*2*(4000*0.4+300*1.6)/1000000*500))+B24*'Egresos e Inversión'!$D$29+(ROUND((MAX(0,((1)*1+(MAX(0,B24-1))*3+(0)*8+(0)*16)-100)*0.0213+MAX(0,((1)*1.056+(MAX(0,B24-1))*2.63999999999999+(0)*6.6+(0)*13.2)-250)*0.09+(MAX(0,ROUNDUP((((1)*0.06+(MAX(0,B24-1))*0.15)+((0)*0.375+(0)*0.75)*0.05)*2,0)-8)+((1)*0+(MAX(0,B24-1))*0+(0)*0+(0)*0))*0.125+IF(((1)*80+(MAX(0,B24-1))*200)&lt;=2000,10,IF(((1)*80+(MAX(0,B24-1))*200)&lt;=5000,15,IF(((1)*80+(MAX(0,B24-1))*200)&lt;=10000,60,110)))-10)*500,2)+ROUND((MAX(0,((1)*0.166864+(MAX(0,B24-1))*0.41716+(0)*1.0429+(0)*2.0858)+20*2*2*0.0035+30*(1/3600*0.128+5/3600*0.0106)-20)+IF(AND(((1)*55680+(MAX(0,B24-1))*139200+(0)*348000+(0)*696000)&lt;=1000000,((1)*1.536+(MAX(0,B24-1))*3.84+(0)*9.6+(0)*19.2)&lt;=1000),0,IF(((1)*55680+(MAX(0,B24-1))*139200+(0)*348000+(0)*696000)&lt;=10000000,20,IF(((1)*55680+(MAX(0,B24-1))*139200+(0)*348000+(0)*696000)&lt;=50000000,100,300)))+MAX(0,ROUNDUP(((1)*80+(MAX(0,B24-1))*200+(0)*500+(0)*1000)/5000,0)-1)*25+IF(((1)*80+(MAX(0,B24-1))*200+(0)*500+(0)*1000)&gt;5000,32-10,0))*500,2)),2)</f>
+        <v>10129.17</v>
       </c>
       <c r="E24" s="10">
         <f>$D$9</f>
-        <v>91125.0</v>
+        <v>114247.54466666667</v>
       </c>
       <c r="F24" s="10">
         <f>D24+E24</f>
-        <v>111508.61</v>
+        <v>124376.71466666667</v>
       </c>
       <c r="G24" s="10">
         <f>C24-F24</f>
-        <v>53491.39</v>
+        <v>40623.28533333333</v>
       </c>
       <c r="H24" s="8" t="str">
         <f>IF(G24&lt;0,"Pérdida",IF(G24=0,"Equilibrio","Ganancia"))</f>
@@ -3532,20 +3540,20 @@
         <v>190000.0</v>
       </c>
       <c r="D25" s="7">
-        <f>ROUND(B25*'Egresos e Inversión'!$D$27+(ROUND((((80*2+20)*0.16/1000+(80*2+20)*32/1000000*0.12)*500),2)+80*2*(4000*0.4+300*1.6)/1000000*500+MAX(0,B25-1)*(ROUND((((200*2+20)*0.16/1000+(200*2+20)*32/1000000*0.12)*500),2)+200*2*(4000*0.4+300*1.6)/1000000*500))+B25*'Egresos e Inversión'!$D$29+(ROUND((MAX(0,((1)*1+(MAX(0,B25-1))*3+(0)*8+(0)*16)-100)*0.0213+MAX(0,((1)*1.056+(MAX(0,B25-1))*2.6399999999999997+(0)*6.6+(0)*13.2)-250)*0.09+(MAX(0,ROUNDUP((((1)*0.06+(MAX(0,B25-1))*0.15)+((0)*0.375+(0)*0.75)*0.05)*2,0)-8)+((1)*0+(MAX(0,B25-1))*0+(0)*0+(0)*0))*0.125+IF(((1)*80+(MAX(0,B25-1))*200)&lt;=2000,10,IF(((1)*80+(MAX(0,B25-1))*200)&lt;=5000,15,IF(((1)*80+(MAX(0,B25-1))*200)&lt;=10000,60,110)))-10)*500,2)+ROUND((MAX(0,((1)*0.166864+(MAX(0,B25-1))*0.41716+(0)*1.0429000000000002+(0)*2.0858000000000003)+20*2*2*0.0035+30*(1/3600*0.128+5/3600*0.0106)-20)+IF(AND(((1)*55680.0+(MAX(0,B25-1))*139200.0+(0)*348000.0+(0)*696000.0)&lt;=1000000,((1)*1.536+(MAX(0,B25-1))*3.84+(0)*9.6+(0)*19.2)&lt;=1000),0,IF(((1)*55680.0+(MAX(0,B25-1))*139200.0+(0)*348000.0+(0)*696000.0)&lt;=10000000,20,IF(((1)*55680.0+(MAX(0,B25-1))*139200.0+(0)*348000.0+(0)*696000.0)&lt;=50000000,100,300)))+MAX(0,ROUNDUP(((1)*80+(MAX(0,B25-1))*200+(0)*500+(0)*1000)/5000,0)-1)*25+IF(((1)*80+(MAX(0,B25-1))*200+(0)*500+(0)*1000)&gt;5000,32-10,0))*500,2)),2)</f>
-        <v>33334.02</v>
+        <f>ROUND(B25*'Egresos e Inversión'!$D$27+(ROUND((((80*2+20)*0.16/1000+(80*2+20)*32/1000000*0.12)*500),2)+80*2*(4000*0.4+300*1.6)/1000000*500+MAX(0,B25-1)*(ROUND((((200*2+20)*0.16/1000+(200*2+20)*32/1000000*0.12)*500),2)+200*2*(4000*0.4+300*1.6)/1000000*500))+B25*'Egresos e Inversión'!$D$29+(ROUND((MAX(0,((1)*1+(MAX(0,B25-1))*3+(0)*8+(0)*16)-100)*0.0213+MAX(0,((1)*1.056+(MAX(0,B25-1))*2.63999999999999+(0)*6.6+(0)*13.2)-250)*0.09+(MAX(0,ROUNDUP((((1)*0.06+(MAX(0,B25-1))*0.15)+((0)*0.375+(0)*0.75)*0.05)*2,0)-8)+((1)*0+(MAX(0,B25-1))*0+(0)*0+(0)*0))*0.125+IF(((1)*80+(MAX(0,B25-1))*200)&lt;=2000,10,IF(((1)*80+(MAX(0,B25-1))*200)&lt;=5000,15,IF(((1)*80+(MAX(0,B25-1))*200)&lt;=10000,60,110)))-10)*500,2)+ROUND((MAX(0,((1)*0.166864+(MAX(0,B25-1))*0.41716+(0)*1.0429+(0)*2.0858)+20*2*2*0.0035+30*(1/3600*0.128+5/3600*0.0106)-20)+IF(AND(((1)*55680+(MAX(0,B25-1))*139200+(0)*348000+(0)*696000)&lt;=1000000,((1)*1.536+(MAX(0,B25-1))*3.84+(0)*9.6+(0)*19.2)&lt;=1000),0,IF(((1)*55680+(MAX(0,B25-1))*139200+(0)*348000+(0)*696000)&lt;=10000000,20,IF(((1)*55680+(MAX(0,B25-1))*139200+(0)*348000+(0)*696000)&lt;=50000000,100,300)))+MAX(0,ROUNDUP(((1)*80+(MAX(0,B25-1))*200+(0)*500+(0)*1000)/5000,0)-1)*25+IF(((1)*80+(MAX(0,B25-1))*200+(0)*500+(0)*1000)&gt;5000,32-10,0))*500,2)),2)</f>
+        <v>21614.66</v>
       </c>
       <c r="E25" s="7">
         <f>$D$9</f>
-        <v>91125.0</v>
+        <v>114247.54466666667</v>
       </c>
       <c r="F25" s="7">
         <f>D25+E25</f>
-        <v>124459.01999999999</v>
+        <v>135862.20466666666</v>
       </c>
       <c r="G25" s="7">
         <f>C25-F25</f>
-        <v>65540.98000000001</v>
+        <v>54137.79533333334</v>
       </c>
       <c r="H25" s="5" t="str">
         <f>IF(G25&lt;0,"Pérdida",IF(G25=0,"Equilibrio","Ganancia"))</f>
@@ -3561,20 +3569,20 @@
         <v>215000.0</v>
       </c>
       <c r="D26" s="10">
-        <f>ROUND(B26*'Egresos e Inversión'!$D$27+(ROUND((((80*2+20)*0.16/1000+(80*2+20)*32/1000000*0.12)*500),2)+80*2*(4000*0.4+300*1.6)/1000000*500+MAX(0,B26-1)*(ROUND((((200*2+20)*0.16/1000+(200*2+20)*32/1000000*0.12)*500),2)+200*2*(4000*0.4+300*1.6)/1000000*500))+B26*'Egresos e Inversión'!$D$29+(ROUND((MAX(0,((1)*1+(MAX(0,B26-1))*3+(0)*8+(0)*16)-100)*0.0213+MAX(0,((1)*1.056+(MAX(0,B26-1))*2.6399999999999997+(0)*6.6+(0)*13.2)-250)*0.09+(MAX(0,ROUNDUP((((1)*0.06+(MAX(0,B26-1))*0.15)+((0)*0.375+(0)*0.75)*0.05)*2,0)-8)+((1)*0+(MAX(0,B26-1))*0+(0)*0+(0)*0))*0.125+IF(((1)*80+(MAX(0,B26-1))*200)&lt;=2000,10,IF(((1)*80+(MAX(0,B26-1))*200)&lt;=5000,15,IF(((1)*80+(MAX(0,B26-1))*200)&lt;=10000,60,110)))-10)*500,2)+ROUND((MAX(0,((1)*0.166864+(MAX(0,B26-1))*0.41716+(0)*1.0429000000000002+(0)*2.0858000000000003)+20*2*2*0.0035+30*(1/3600*0.128+5/3600*0.0106)-20)+IF(AND(((1)*55680.0+(MAX(0,B26-1))*139200.0+(0)*348000.0+(0)*696000.0)&lt;=1000000,((1)*1.536+(MAX(0,B26-1))*3.84+(0)*9.6+(0)*19.2)&lt;=1000),0,IF(((1)*55680.0+(MAX(0,B26-1))*139200.0+(0)*348000.0+(0)*696000.0)&lt;=10000000,20,IF(((1)*55680.0+(MAX(0,B26-1))*139200.0+(0)*348000.0+(0)*696000.0)&lt;=50000000,100,300)))+MAX(0,ROUNDUP(((1)*80+(MAX(0,B26-1))*200+(0)*500+(0)*1000)/5000,0)-1)*25+IF(((1)*80+(MAX(0,B26-1))*200+(0)*500+(0)*1000)&gt;5000,32-10,0))*500,2)),2)</f>
-        <v>36284.43</v>
+        <f>ROUND(B26*'Egresos e Inversión'!$D$27+(ROUND((((80*2+20)*0.16/1000+(80*2+20)*32/1000000*0.12)*500),2)+80*2*(4000*0.4+300*1.6)/1000000*500+MAX(0,B26-1)*(ROUND((((200*2+20)*0.16/1000+(200*2+20)*32/1000000*0.12)*500),2)+200*2*(4000*0.4+300*1.6)/1000000*500))+B26*'Egresos e Inversión'!$D$29+(ROUND((MAX(0,((1)*1+(MAX(0,B26-1))*3+(0)*8+(0)*16)-100)*0.0213+MAX(0,((1)*1.056+(MAX(0,B26-1))*2.63999999999999+(0)*6.6+(0)*13.2)-250)*0.09+(MAX(0,ROUNDUP((((1)*0.06+(MAX(0,B26-1))*0.15)+((0)*0.375+(0)*0.75)*0.05)*2,0)-8)+((1)*0+(MAX(0,B26-1))*0+(0)*0+(0)*0))*0.125+IF(((1)*80+(MAX(0,B26-1))*200)&lt;=2000,10,IF(((1)*80+(MAX(0,B26-1))*200)&lt;=5000,15,IF(((1)*80+(MAX(0,B26-1))*200)&lt;=10000,60,110)))-10)*500,2)+ROUND((MAX(0,((1)*0.166864+(MAX(0,B26-1))*0.41716+(0)*1.0429+(0)*2.0858)+20*2*2*0.0035+30*(1/3600*0.128+5/3600*0.0106)-20)+IF(AND(((1)*55680+(MAX(0,B26-1))*139200+(0)*348000+(0)*696000)&lt;=1000000,((1)*1.536+(MAX(0,B26-1))*3.84+(0)*9.6+(0)*19.2)&lt;=1000),0,IF(((1)*55680+(MAX(0,B26-1))*139200+(0)*348000+(0)*696000)&lt;=10000000,20,IF(((1)*55680+(MAX(0,B26-1))*139200+(0)*348000+(0)*696000)&lt;=50000000,100,300)))+MAX(0,ROUNDUP(((1)*80+(MAX(0,B26-1))*200+(0)*500+(0)*1000)/5000,0)-1)*25+IF(((1)*80+(MAX(0,B26-1))*200+(0)*500+(0)*1000)&gt;5000,32-10,0))*500,2)),2)</f>
+        <v>23100.15</v>
       </c>
       <c r="E26" s="10">
         <f>$D$9</f>
-        <v>91125.0</v>
+        <v>114247.54466666667</v>
       </c>
       <c r="F26" s="10">
         <f>D26+E26</f>
-        <v>127409.43</v>
+        <v>137347.69466666668</v>
       </c>
       <c r="G26" s="10">
         <f>C26-F26</f>
-        <v>87590.57</v>
+        <v>77652.30533333332</v>
       </c>
       <c r="H26" s="8" t="str">
         <f>IF(G26&lt;0,"Pérdida",IF(G26=0,"Equilibrio","Ganancia"))</f>
@@ -3590,20 +3598,20 @@
         <v>240000.0</v>
       </c>
       <c r="D27" s="7">
-        <f>ROUND(B27*'Egresos e Inversión'!$D$27+(ROUND((((80*2+20)*0.16/1000+(80*2+20)*32/1000000*0.12)*500),2)+80*2*(4000*0.4+300*1.6)/1000000*500+MAX(0,B27-1)*(ROUND((((200*2+20)*0.16/1000+(200*2+20)*32/1000000*0.12)*500),2)+200*2*(4000*0.4+300*1.6)/1000000*500))+B27*'Egresos e Inversión'!$D$29+(ROUND((MAX(0,((1)*1+(MAX(0,B27-1))*3+(0)*8+(0)*16)-100)*0.0213+MAX(0,((1)*1.056+(MAX(0,B27-1))*2.6399999999999997+(0)*6.6+(0)*13.2)-250)*0.09+(MAX(0,ROUNDUP((((1)*0.06+(MAX(0,B27-1))*0.15)+((0)*0.375+(0)*0.75)*0.05)*2,0)-8)+((1)*0+(MAX(0,B27-1))*0+(0)*0+(0)*0))*0.125+IF(((1)*80+(MAX(0,B27-1))*200)&lt;=2000,10,IF(((1)*80+(MAX(0,B27-1))*200)&lt;=5000,15,IF(((1)*80+(MAX(0,B27-1))*200)&lt;=10000,60,110)))-10)*500,2)+ROUND((MAX(0,((1)*0.166864+(MAX(0,B27-1))*0.41716+(0)*1.0429000000000002+(0)*2.0858000000000003)+20*2*2*0.0035+30*(1/3600*0.128+5/3600*0.0106)-20)+IF(AND(((1)*55680.0+(MAX(0,B27-1))*139200.0+(0)*348000.0+(0)*696000.0)&lt;=1000000,((1)*1.536+(MAX(0,B27-1))*3.84+(0)*9.6+(0)*19.2)&lt;=1000),0,IF(((1)*55680.0+(MAX(0,B27-1))*139200.0+(0)*348000.0+(0)*696000.0)&lt;=10000000,20,IF(((1)*55680.0+(MAX(0,B27-1))*139200.0+(0)*348000.0+(0)*696000.0)&lt;=50000000,100,300)))+MAX(0,ROUNDUP(((1)*80+(MAX(0,B27-1))*200+(0)*500+(0)*1000)/5000,0)-1)*25+IF(((1)*80+(MAX(0,B27-1))*200+(0)*500+(0)*1000)&gt;5000,32-10,0))*500,2)),2)</f>
-        <v>39234.84</v>
+        <f>ROUND(B27*'Egresos e Inversión'!$D$27+(ROUND((((80*2+20)*0.16/1000+(80*2+20)*32/1000000*0.12)*500),2)+80*2*(4000*0.4+300*1.6)/1000000*500+MAX(0,B27-1)*(ROUND((((200*2+20)*0.16/1000+(200*2+20)*32/1000000*0.12)*500),2)+200*2*(4000*0.4+300*1.6)/1000000*500))+B27*'Egresos e Inversión'!$D$29+(ROUND((MAX(0,((1)*1+(MAX(0,B27-1))*3+(0)*8+(0)*16)-100)*0.0213+MAX(0,((1)*1.056+(MAX(0,B27-1))*2.63999999999999+(0)*6.6+(0)*13.2)-250)*0.09+(MAX(0,ROUNDUP((((1)*0.06+(MAX(0,B27-1))*0.15)+((0)*0.375+(0)*0.75)*0.05)*2,0)-8)+((1)*0+(MAX(0,B27-1))*0+(0)*0+(0)*0))*0.125+IF(((1)*80+(MAX(0,B27-1))*200)&lt;=2000,10,IF(((1)*80+(MAX(0,B27-1))*200)&lt;=5000,15,IF(((1)*80+(MAX(0,B27-1))*200)&lt;=10000,60,110)))-10)*500,2)+ROUND((MAX(0,((1)*0.166864+(MAX(0,B27-1))*0.41716+(0)*1.0429+(0)*2.0858)+20*2*2*0.0035+30*(1/3600*0.128+5/3600*0.0106)-20)+IF(AND(((1)*55680+(MAX(0,B27-1))*139200+(0)*348000+(0)*696000)&lt;=1000000,((1)*1.536+(MAX(0,B27-1))*3.84+(0)*9.6+(0)*19.2)&lt;=1000),0,IF(((1)*55680+(MAX(0,B27-1))*139200+(0)*348000+(0)*696000)&lt;=10000000,20,IF(((1)*55680+(MAX(0,B27-1))*139200+(0)*348000+(0)*696000)&lt;=50000000,100,300)))+MAX(0,ROUNDUP(((1)*80+(MAX(0,B27-1))*200+(0)*500+(0)*1000)/5000,0)-1)*25+IF(((1)*80+(MAX(0,B27-1))*200+(0)*500+(0)*1000)&gt;5000,32-10,0))*500,2)),2)</f>
+        <v>24585.64</v>
       </c>
       <c r="E27" s="7">
         <f>$D$9</f>
-        <v>91125.0</v>
+        <v>114247.54466666667</v>
       </c>
       <c r="F27" s="7">
         <f>D27+E27</f>
-        <v>130359.84</v>
+        <v>138833.18466666667</v>
       </c>
       <c r="G27" s="7">
         <f>C27-F27</f>
-        <v>109640.16</v>
+        <v>101166.81533333333</v>
       </c>
       <c r="H27" s="5" t="str">
         <f>IF(G27&lt;0,"Pérdida",IF(G27=0,"Equilibrio","Ganancia"))</f>
@@ -3619,20 +3627,20 @@
         <v>265000.0</v>
       </c>
       <c r="D28" s="10">
-        <f>ROUND(B28*'Egresos e Inversión'!$D$27+(ROUND((((80*2+20)*0.16/1000+(80*2+20)*32/1000000*0.12)*500),2)+80*2*(4000*0.4+300*1.6)/1000000*500+MAX(0,B28-1)*(ROUND((((200*2+20)*0.16/1000+(200*2+20)*32/1000000*0.12)*500),2)+200*2*(4000*0.4+300*1.6)/1000000*500))+B28*'Egresos e Inversión'!$D$29+(ROUND((MAX(0,((1)*1+(MAX(0,B28-1))*3+(0)*8+(0)*16)-100)*0.0213+MAX(0,((1)*1.056+(MAX(0,B28-1))*2.6399999999999997+(0)*6.6+(0)*13.2)-250)*0.09+(MAX(0,ROUNDUP((((1)*0.06+(MAX(0,B28-1))*0.15)+((0)*0.375+(0)*0.75)*0.05)*2,0)-8)+((1)*0+(MAX(0,B28-1))*0+(0)*0+(0)*0))*0.125+IF(((1)*80+(MAX(0,B28-1))*200)&lt;=2000,10,IF(((1)*80+(MAX(0,B28-1))*200)&lt;=5000,15,IF(((1)*80+(MAX(0,B28-1))*200)&lt;=10000,60,110)))-10)*500,2)+ROUND((MAX(0,((1)*0.166864+(MAX(0,B28-1))*0.41716+(0)*1.0429000000000002+(0)*2.0858000000000003)+20*2*2*0.0035+30*(1/3600*0.128+5/3600*0.0106)-20)+IF(AND(((1)*55680.0+(MAX(0,B28-1))*139200.0+(0)*348000.0+(0)*696000.0)&lt;=1000000,((1)*1.536+(MAX(0,B28-1))*3.84+(0)*9.6+(0)*19.2)&lt;=1000),0,IF(((1)*55680.0+(MAX(0,B28-1))*139200.0+(0)*348000.0+(0)*696000.0)&lt;=10000000,20,IF(((1)*55680.0+(MAX(0,B28-1))*139200.0+(0)*348000.0+(0)*696000.0)&lt;=50000000,100,300)))+MAX(0,ROUNDUP(((1)*80+(MAX(0,B28-1))*200+(0)*500+(0)*1000)/5000,0)-1)*25+IF(((1)*80+(MAX(0,B28-1))*200+(0)*500+(0)*1000)&gt;5000,32-10,0))*500,2)),2)</f>
-        <v>44685.25</v>
+        <f>ROUND(B28*'Egresos e Inversión'!$D$27+(ROUND((((80*2+20)*0.16/1000+(80*2+20)*32/1000000*0.12)*500),2)+80*2*(4000*0.4+300*1.6)/1000000*500+MAX(0,B28-1)*(ROUND((((200*2+20)*0.16/1000+(200*2+20)*32/1000000*0.12)*500),2)+200*2*(4000*0.4+300*1.6)/1000000*500))+B28*'Egresos e Inversión'!$D$29+(ROUND((MAX(0,((1)*1+(MAX(0,B28-1))*3+(0)*8+(0)*16)-100)*0.0213+MAX(0,((1)*1.056+(MAX(0,B28-1))*2.63999999999999+(0)*6.6+(0)*13.2)-250)*0.09+(MAX(0,ROUNDUP((((1)*0.06+(MAX(0,B28-1))*0.15)+((0)*0.375+(0)*0.75)*0.05)*2,0)-8)+((1)*0+(MAX(0,B28-1))*0+(0)*0+(0)*0))*0.125+IF(((1)*80+(MAX(0,B28-1))*200)&lt;=2000,10,IF(((1)*80+(MAX(0,B28-1))*200)&lt;=5000,15,IF(((1)*80+(MAX(0,B28-1))*200)&lt;=10000,60,110)))-10)*500,2)+ROUND((MAX(0,((1)*0.166864+(MAX(0,B28-1))*0.41716+(0)*1.0429+(0)*2.0858)+20*2*2*0.0035+30*(1/3600*0.128+5/3600*0.0106)-20)+IF(AND(((1)*55680+(MAX(0,B28-1))*139200+(0)*348000+(0)*696000)&lt;=1000000,((1)*1.536+(MAX(0,B28-1))*3.84+(0)*9.6+(0)*19.2)&lt;=1000),0,IF(((1)*55680+(MAX(0,B28-1))*139200+(0)*348000+(0)*696000)&lt;=10000000,20,IF(((1)*55680+(MAX(0,B28-1))*139200+(0)*348000+(0)*696000)&lt;=50000000,100,300)))+MAX(0,ROUNDUP(((1)*80+(MAX(0,B28-1))*200+(0)*500+(0)*1000)/5000,0)-1)*25+IF(((1)*80+(MAX(0,B28-1))*200+(0)*500+(0)*1000)&gt;5000,32-10,0))*500,2)),2)</f>
+        <v>28571.12</v>
       </c>
       <c r="E28" s="10">
         <f>$D$9</f>
-        <v>91125.0</v>
+        <v>114247.54466666667</v>
       </c>
       <c r="F28" s="10">
         <f>D28+E28</f>
-        <v>135810.25</v>
+        <v>142818.66466666668</v>
       </c>
       <c r="G28" s="10">
         <f>C28-F28</f>
-        <v>129189.75</v>
+        <v>122181.33533333332</v>
       </c>
       <c r="H28" s="8" t="str">
         <f>IF(G28&lt;0,"Pérdida",IF(G28=0,"Equilibrio","Ganancia"))</f>
@@ -3648,20 +3656,20 @@
         <v>290000.0</v>
       </c>
       <c r="D29" s="7">
-        <f>ROUND(B29*'Egresos e Inversión'!$D$27+(ROUND((((80*2+20)*0.16/1000+(80*2+20)*32/1000000*0.12)*500),2)+80*2*(4000*0.4+300*1.6)/1000000*500+MAX(0,B29-1)*(ROUND((((200*2+20)*0.16/1000+(200*2+20)*32/1000000*0.12)*500),2)+200*2*(4000*0.4+300*1.6)/1000000*500))+B29*'Egresos e Inversión'!$D$29+(ROUND((MAX(0,((1)*1+(MAX(0,B29-1))*3+(0)*8+(0)*16)-100)*0.0213+MAX(0,((1)*1.056+(MAX(0,B29-1))*2.6399999999999997+(0)*6.6+(0)*13.2)-250)*0.09+(MAX(0,ROUNDUP((((1)*0.06+(MAX(0,B29-1))*0.15)+((0)*0.375+(0)*0.75)*0.05)*2,0)-8)+((1)*0+(MAX(0,B29-1))*0+(0)*0+(0)*0))*0.125+IF(((1)*80+(MAX(0,B29-1))*200)&lt;=2000,10,IF(((1)*80+(MAX(0,B29-1))*200)&lt;=5000,15,IF(((1)*80+(MAX(0,B29-1))*200)&lt;=10000,60,110)))-10)*500,2)+ROUND((MAX(0,((1)*0.166864+(MAX(0,B29-1))*0.41716+(0)*1.0429000000000002+(0)*2.0858000000000003)+20*2*2*0.0035+30*(1/3600*0.128+5/3600*0.0106)-20)+IF(AND(((1)*55680.0+(MAX(0,B29-1))*139200.0+(0)*348000.0+(0)*696000.0)&lt;=1000000,((1)*1.536+(MAX(0,B29-1))*3.84+(0)*9.6+(0)*19.2)&lt;=1000),0,IF(((1)*55680.0+(MAX(0,B29-1))*139200.0+(0)*348000.0+(0)*696000.0)&lt;=10000000,20,IF(((1)*55680.0+(MAX(0,B29-1))*139200.0+(0)*348000.0+(0)*696000.0)&lt;=50000000,100,300)))+MAX(0,ROUNDUP(((1)*80+(MAX(0,B29-1))*200+(0)*500+(0)*1000)/5000,0)-1)*25+IF(((1)*80+(MAX(0,B29-1))*200+(0)*500+(0)*1000)&gt;5000,32-10,0))*500,2)),2)</f>
-        <v>47635.66</v>
+        <f>ROUND(B29*'Egresos e Inversión'!$D$27+(ROUND((((80*2+20)*0.16/1000+(80*2+20)*32/1000000*0.12)*500),2)+80*2*(4000*0.4+300*1.6)/1000000*500+MAX(0,B29-1)*(ROUND((((200*2+20)*0.16/1000+(200*2+20)*32/1000000*0.12)*500),2)+200*2*(4000*0.4+300*1.6)/1000000*500))+B29*'Egresos e Inversión'!$D$29+(ROUND((MAX(0,((1)*1+(MAX(0,B29-1))*3+(0)*8+(0)*16)-100)*0.0213+MAX(0,((1)*1.056+(MAX(0,B29-1))*2.63999999999999+(0)*6.6+(0)*13.2)-250)*0.09+(MAX(0,ROUNDUP((((1)*0.06+(MAX(0,B29-1))*0.15)+((0)*0.375+(0)*0.75)*0.05)*2,0)-8)+((1)*0+(MAX(0,B29-1))*0+(0)*0+(0)*0))*0.125+IF(((1)*80+(MAX(0,B29-1))*200)&lt;=2000,10,IF(((1)*80+(MAX(0,B29-1))*200)&lt;=5000,15,IF(((1)*80+(MAX(0,B29-1))*200)&lt;=10000,60,110)))-10)*500,2)+ROUND((MAX(0,((1)*0.166864+(MAX(0,B29-1))*0.41716+(0)*1.0429+(0)*2.0858)+20*2*2*0.0035+30*(1/3600*0.128+5/3600*0.0106)-20)+IF(AND(((1)*55680+(MAX(0,B29-1))*139200+(0)*348000+(0)*696000)&lt;=1000000,((1)*1.536+(MAX(0,B29-1))*3.84+(0)*9.6+(0)*19.2)&lt;=1000),0,IF(((1)*55680+(MAX(0,B29-1))*139200+(0)*348000+(0)*696000)&lt;=10000000,20,IF(((1)*55680+(MAX(0,B29-1))*139200+(0)*348000+(0)*696000)&lt;=50000000,100,300)))+MAX(0,ROUNDUP(((1)*80+(MAX(0,B29-1))*200+(0)*500+(0)*1000)/5000,0)-1)*25+IF(((1)*80+(MAX(0,B29-1))*200+(0)*500+(0)*1000)&gt;5000,32-10,0))*500,2)),2)</f>
+        <v>30056.61</v>
       </c>
       <c r="E29" s="7">
         <f>$D$9</f>
-        <v>91125.0</v>
+        <v>114247.54466666667</v>
       </c>
       <c r="F29" s="7">
         <f>D29+E29</f>
-        <v>138760.66</v>
+        <v>144304.15466666667</v>
       </c>
       <c r="G29" s="7">
         <f>C29-F29</f>
-        <v>151239.34</v>
+        <v>145695.84533333333</v>
       </c>
       <c r="H29" s="5" t="str">
         <f>IF(G29&lt;0,"Pérdida",IF(G29=0,"Equilibrio","Ganancia"))</f>
@@ -3677,20 +3685,20 @@
         <v>315000.0</v>
       </c>
       <c r="D30" s="10">
-        <f>ROUND(B30*'Egresos e Inversión'!$D$27+(ROUND((((80*2+20)*0.16/1000+(80*2+20)*32/1000000*0.12)*500),2)+80*2*(4000*0.4+300*1.6)/1000000*500+MAX(0,B30-1)*(ROUND((((200*2+20)*0.16/1000+(200*2+20)*32/1000000*0.12)*500),2)+200*2*(4000*0.4+300*1.6)/1000000*500))+B30*'Egresos e Inversión'!$D$29+(ROUND((MAX(0,((1)*1+(MAX(0,B30-1))*3+(0)*8+(0)*16)-100)*0.0213+MAX(0,((1)*1.056+(MAX(0,B30-1))*2.6399999999999997+(0)*6.6+(0)*13.2)-250)*0.09+(MAX(0,ROUNDUP((((1)*0.06+(MAX(0,B30-1))*0.15)+((0)*0.375+(0)*0.75)*0.05)*2,0)-8)+((1)*0+(MAX(0,B30-1))*0+(0)*0+(0)*0))*0.125+IF(((1)*80+(MAX(0,B30-1))*200)&lt;=2000,10,IF(((1)*80+(MAX(0,B30-1))*200)&lt;=5000,15,IF(((1)*80+(MAX(0,B30-1))*200)&lt;=10000,60,110)))-10)*500,2)+ROUND((MAX(0,((1)*0.166864+(MAX(0,B30-1))*0.41716+(0)*1.0429000000000002+(0)*2.0858000000000003)+20*2*2*0.0035+30*(1/3600*0.128+5/3600*0.0106)-20)+IF(AND(((1)*55680.0+(MAX(0,B30-1))*139200.0+(0)*348000.0+(0)*696000.0)&lt;=1000000,((1)*1.536+(MAX(0,B30-1))*3.84+(0)*9.6+(0)*19.2)&lt;=1000),0,IF(((1)*55680.0+(MAX(0,B30-1))*139200.0+(0)*348000.0+(0)*696000.0)&lt;=10000000,20,IF(((1)*55680.0+(MAX(0,B30-1))*139200.0+(0)*348000.0+(0)*696000.0)&lt;=50000000,100,300)))+MAX(0,ROUNDUP(((1)*80+(MAX(0,B30-1))*200+(0)*500+(0)*1000)/5000,0)-1)*25+IF(((1)*80+(MAX(0,B30-1))*200+(0)*500+(0)*1000)&gt;5000,32-10,0))*500,2)),2)</f>
-        <v>50586.07</v>
+        <f>ROUND(B30*'Egresos e Inversión'!$D$27+(ROUND((((80*2+20)*0.16/1000+(80*2+20)*32/1000000*0.12)*500),2)+80*2*(4000*0.4+300*1.6)/1000000*500+MAX(0,B30-1)*(ROUND((((200*2+20)*0.16/1000+(200*2+20)*32/1000000*0.12)*500),2)+200*2*(4000*0.4+300*1.6)/1000000*500))+B30*'Egresos e Inversión'!$D$29+(ROUND((MAX(0,((1)*1+(MAX(0,B30-1))*3+(0)*8+(0)*16)-100)*0.0213+MAX(0,((1)*1.056+(MAX(0,B30-1))*2.63999999999999+(0)*6.6+(0)*13.2)-250)*0.09+(MAX(0,ROUNDUP((((1)*0.06+(MAX(0,B30-1))*0.15)+((0)*0.375+(0)*0.75)*0.05)*2,0)-8)+((1)*0+(MAX(0,B30-1))*0+(0)*0+(0)*0))*0.125+IF(((1)*80+(MAX(0,B30-1))*200)&lt;=2000,10,IF(((1)*80+(MAX(0,B30-1))*200)&lt;=5000,15,IF(((1)*80+(MAX(0,B30-1))*200)&lt;=10000,60,110)))-10)*500,2)+ROUND((MAX(0,((1)*0.166864+(MAX(0,B30-1))*0.41716+(0)*1.0429+(0)*2.0858)+20*2*2*0.0035+30*(1/3600*0.128+5/3600*0.0106)-20)+IF(AND(((1)*55680+(MAX(0,B30-1))*139200+(0)*348000+(0)*696000)&lt;=1000000,((1)*1.536+(MAX(0,B30-1))*3.84+(0)*9.6+(0)*19.2)&lt;=1000),0,IF(((1)*55680+(MAX(0,B30-1))*139200+(0)*348000+(0)*696000)&lt;=10000000,20,IF(((1)*55680+(MAX(0,B30-1))*139200+(0)*348000+(0)*696000)&lt;=50000000,100,300)))+MAX(0,ROUNDUP(((1)*80+(MAX(0,B30-1))*200+(0)*500+(0)*1000)/5000,0)-1)*25+IF(((1)*80+(MAX(0,B30-1))*200+(0)*500+(0)*1000)&gt;5000,32-10,0))*500,2)),2)</f>
+        <v>31542.1</v>
       </c>
       <c r="E30" s="10">
         <f>$D$9</f>
-        <v>91125.0</v>
+        <v>114247.54466666667</v>
       </c>
       <c r="F30" s="10">
         <f>D30+E30</f>
-        <v>141711.07</v>
+        <v>145789.64466666666</v>
       </c>
       <c r="G30" s="10">
         <f>C30-F30</f>
-        <v>173288.93</v>
+        <v>169210.35533333334</v>
       </c>
       <c r="H30" s="8" t="str">
         <f>IF(G30&lt;0,"Pérdida",IF(G30=0,"Equilibrio","Ganancia"))</f>
@@ -3706,20 +3714,20 @@
         <v>340000.0</v>
       </c>
       <c r="D31" s="7">
-        <f>ROUND(B31*'Egresos e Inversión'!$D$27+(ROUND((((80*2+20)*0.16/1000+(80*2+20)*32/1000000*0.12)*500),2)+80*2*(4000*0.4+300*1.6)/1000000*500+MAX(0,B31-1)*(ROUND((((200*2+20)*0.16/1000+(200*2+20)*32/1000000*0.12)*500),2)+200*2*(4000*0.4+300*1.6)/1000000*500))+B31*'Egresos e Inversión'!$D$29+(ROUND((MAX(0,((1)*1+(MAX(0,B31-1))*3+(0)*8+(0)*16)-100)*0.0213+MAX(0,((1)*1.056+(MAX(0,B31-1))*2.6399999999999997+(0)*6.6+(0)*13.2)-250)*0.09+(MAX(0,ROUNDUP((((1)*0.06+(MAX(0,B31-1))*0.15)+((0)*0.375+(0)*0.75)*0.05)*2,0)-8)+((1)*0+(MAX(0,B31-1))*0+(0)*0+(0)*0))*0.125+IF(((1)*80+(MAX(0,B31-1))*200)&lt;=2000,10,IF(((1)*80+(MAX(0,B31-1))*200)&lt;=5000,15,IF(((1)*80+(MAX(0,B31-1))*200)&lt;=10000,60,110)))-10)*500,2)+ROUND((MAX(0,((1)*0.166864+(MAX(0,B31-1))*0.41716+(0)*1.0429000000000002+(0)*2.0858000000000003)+20*2*2*0.0035+30*(1/3600*0.128+5/3600*0.0106)-20)+IF(AND(((1)*55680.0+(MAX(0,B31-1))*139200.0+(0)*348000.0+(0)*696000.0)&lt;=1000000,((1)*1.536+(MAX(0,B31-1))*3.84+(0)*9.6+(0)*19.2)&lt;=1000),0,IF(((1)*55680.0+(MAX(0,B31-1))*139200.0+(0)*348000.0+(0)*696000.0)&lt;=10000000,20,IF(((1)*55680.0+(MAX(0,B31-1))*139200.0+(0)*348000.0+(0)*696000.0)&lt;=50000000,100,300)))+MAX(0,ROUNDUP(((1)*80+(MAX(0,B31-1))*200+(0)*500+(0)*1000)/5000,0)-1)*25+IF(((1)*80+(MAX(0,B31-1))*200+(0)*500+(0)*1000)&gt;5000,32-10,0))*500,2)),2)</f>
-        <v>53536.48</v>
+        <f>ROUND(B31*'Egresos e Inversión'!$D$27+(ROUND((((80*2+20)*0.16/1000+(80*2+20)*32/1000000*0.12)*500),2)+80*2*(4000*0.4+300*1.6)/1000000*500+MAX(0,B31-1)*(ROUND((((200*2+20)*0.16/1000+(200*2+20)*32/1000000*0.12)*500),2)+200*2*(4000*0.4+300*1.6)/1000000*500))+B31*'Egresos e Inversión'!$D$29+(ROUND((MAX(0,((1)*1+(MAX(0,B31-1))*3+(0)*8+(0)*16)-100)*0.0213+MAX(0,((1)*1.056+(MAX(0,B31-1))*2.63999999999999+(0)*6.6+(0)*13.2)-250)*0.09+(MAX(0,ROUNDUP((((1)*0.06+(MAX(0,B31-1))*0.15)+((0)*0.375+(0)*0.75)*0.05)*2,0)-8)+((1)*0+(MAX(0,B31-1))*0+(0)*0+(0)*0))*0.125+IF(((1)*80+(MAX(0,B31-1))*200)&lt;=2000,10,IF(((1)*80+(MAX(0,B31-1))*200)&lt;=5000,15,IF(((1)*80+(MAX(0,B31-1))*200)&lt;=10000,60,110)))-10)*500,2)+ROUND((MAX(0,((1)*0.166864+(MAX(0,B31-1))*0.41716+(0)*1.0429+(0)*2.0858)+20*2*2*0.0035+30*(1/3600*0.128+5/3600*0.0106)-20)+IF(AND(((1)*55680+(MAX(0,B31-1))*139200+(0)*348000+(0)*696000)&lt;=1000000,((1)*1.536+(MAX(0,B31-1))*3.84+(0)*9.6+(0)*19.2)&lt;=1000),0,IF(((1)*55680+(MAX(0,B31-1))*139200+(0)*348000+(0)*696000)&lt;=10000000,20,IF(((1)*55680+(MAX(0,B31-1))*139200+(0)*348000+(0)*696000)&lt;=50000000,100,300)))+MAX(0,ROUNDUP(((1)*80+(MAX(0,B31-1))*200+(0)*500+(0)*1000)/5000,0)-1)*25+IF(((1)*80+(MAX(0,B31-1))*200+(0)*500+(0)*1000)&gt;5000,32-10,0))*500,2)),2)</f>
+        <v>33027.59</v>
       </c>
       <c r="E31" s="7">
         <f>$D$9</f>
-        <v>91125.0</v>
+        <v>114247.54466666667</v>
       </c>
       <c r="F31" s="7">
         <f>D31+E31</f>
-        <v>144661.48</v>
+        <v>147275.13466666668</v>
       </c>
       <c r="G31" s="7">
         <f>C31-F31</f>
-        <v>195338.52</v>
+        <v>192724.86533333332</v>
       </c>
       <c r="H31" s="5" t="str">
         <f>IF(G31&lt;0,"Pérdida",IF(G31=0,"Equilibrio","Ganancia"))</f>
@@ -3735,20 +3743,20 @@
         <v>365000.0</v>
       </c>
       <c r="D32" s="10">
-        <f>ROUND(B32*'Egresos e Inversión'!$D$27+(ROUND((((80*2+20)*0.16/1000+(80*2+20)*32/1000000*0.12)*500),2)+80*2*(4000*0.4+300*1.6)/1000000*500+MAX(0,B32-1)*(ROUND((((200*2+20)*0.16/1000+(200*2+20)*32/1000000*0.12)*500),2)+200*2*(4000*0.4+300*1.6)/1000000*500))+B32*'Egresos e Inversión'!$D$29+(ROUND((MAX(0,((1)*1+(MAX(0,B32-1))*3+(0)*8+(0)*16)-100)*0.0213+MAX(0,((1)*1.056+(MAX(0,B32-1))*2.6399999999999997+(0)*6.6+(0)*13.2)-250)*0.09+(MAX(0,ROUNDUP((((1)*0.06+(MAX(0,B32-1))*0.15)+((0)*0.375+(0)*0.75)*0.05)*2,0)-8)+((1)*0+(MAX(0,B32-1))*0+(0)*0+(0)*0))*0.125+IF(((1)*80+(MAX(0,B32-1))*200)&lt;=2000,10,IF(((1)*80+(MAX(0,B32-1))*200)&lt;=5000,15,IF(((1)*80+(MAX(0,B32-1))*200)&lt;=10000,60,110)))-10)*500,2)+ROUND((MAX(0,((1)*0.166864+(MAX(0,B32-1))*0.41716+(0)*1.0429000000000002+(0)*2.0858000000000003)+20*2*2*0.0035+30*(1/3600*0.128+5/3600*0.0106)-20)+IF(AND(((1)*55680.0+(MAX(0,B32-1))*139200.0+(0)*348000.0+(0)*696000.0)&lt;=1000000,((1)*1.536+(MAX(0,B32-1))*3.84+(0)*9.6+(0)*19.2)&lt;=1000),0,IF(((1)*55680.0+(MAX(0,B32-1))*139200.0+(0)*348000.0+(0)*696000.0)&lt;=10000000,20,IF(((1)*55680.0+(MAX(0,B32-1))*139200.0+(0)*348000.0+(0)*696000.0)&lt;=50000000,100,300)))+MAX(0,ROUNDUP(((1)*80+(MAX(0,B32-1))*200+(0)*500+(0)*1000)/5000,0)-1)*25+IF(((1)*80+(MAX(0,B32-1))*200+(0)*500+(0)*1000)&gt;5000,32-10,0))*500,2)),2)</f>
-        <v>56486.89</v>
+        <f>ROUND(B32*'Egresos e Inversión'!$D$27+(ROUND((((80*2+20)*0.16/1000+(80*2+20)*32/1000000*0.12)*500),2)+80*2*(4000*0.4+300*1.6)/1000000*500+MAX(0,B32-1)*(ROUND((((200*2+20)*0.16/1000+(200*2+20)*32/1000000*0.12)*500),2)+200*2*(4000*0.4+300*1.6)/1000000*500))+B32*'Egresos e Inversión'!$D$29+(ROUND((MAX(0,((1)*1+(MAX(0,B32-1))*3+(0)*8+(0)*16)-100)*0.0213+MAX(0,((1)*1.056+(MAX(0,B32-1))*2.63999999999999+(0)*6.6+(0)*13.2)-250)*0.09+(MAX(0,ROUNDUP((((1)*0.06+(MAX(0,B32-1))*0.15)+((0)*0.375+(0)*0.75)*0.05)*2,0)-8)+((1)*0+(MAX(0,B32-1))*0+(0)*0+(0)*0))*0.125+IF(((1)*80+(MAX(0,B32-1))*200)&lt;=2000,10,IF(((1)*80+(MAX(0,B32-1))*200)&lt;=5000,15,IF(((1)*80+(MAX(0,B32-1))*200)&lt;=10000,60,110)))-10)*500,2)+ROUND((MAX(0,((1)*0.166864+(MAX(0,B32-1))*0.41716+(0)*1.0429+(0)*2.0858)+20*2*2*0.0035+30*(1/3600*0.128+5/3600*0.0106)-20)+IF(AND(((1)*55680+(MAX(0,B32-1))*139200+(0)*348000+(0)*696000)&lt;=1000000,((1)*1.536+(MAX(0,B32-1))*3.84+(0)*9.6+(0)*19.2)&lt;=1000),0,IF(((1)*55680+(MAX(0,B32-1))*139200+(0)*348000+(0)*696000)&lt;=10000000,20,IF(((1)*55680+(MAX(0,B32-1))*139200+(0)*348000+(0)*696000)&lt;=50000000,100,300)))+MAX(0,ROUNDUP(((1)*80+(MAX(0,B32-1))*200+(0)*500+(0)*1000)/5000,0)-1)*25+IF(((1)*80+(MAX(0,B32-1))*200+(0)*500+(0)*1000)&gt;5000,32-10,0))*500,2)),2)</f>
+        <v>34513.08</v>
       </c>
       <c r="E32" s="10">
         <f>$D$9</f>
-        <v>91125.0</v>
+        <v>114247.54466666667</v>
       </c>
       <c r="F32" s="10">
         <f>D32+E32</f>
-        <v>147611.89</v>
+        <v>148760.62466666667</v>
       </c>
       <c r="G32" s="10">
         <f>C32-F32</f>
-        <v>217388.11</v>
+        <v>216239.37533333333</v>
       </c>
       <c r="H32" s="8" t="str">
         <f>IF(G32&lt;0,"Pérdida",IF(G32=0,"Equilibrio","Ganancia"))</f>
@@ -3779,15 +3787,15 @@
   <dimension ref="B2:O41"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="38" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="4"/>
-    <col width="30.33203125" customWidth="1" min="5" max="5"/>
-    <col width="25.6640625" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="15"/>
+    <col width="12" customWidth="1" style="51" min="1" max="1"/>
+    <col width="38" customWidth="1" style="51" min="2" max="2"/>
+    <col width="18" customWidth="1" style="51" min="3" max="4"/>
+    <col width="30.33203125" customWidth="1" style="51" min="5" max="5"/>
+    <col width="25.6640625" customWidth="1" style="51" min="6" max="6"/>
+    <col width="18" customWidth="1" style="51" min="7" max="15"/>
   </cols>
   <sheetData>
-    <row r="2" ht="21" customHeight="1">
+    <row r="2" ht="21" customHeight="1" s="51">
       <c r="B2" s="1" t="inlineStr">
         <is>
           <t>ESTADOS FINANCIEROS PROYECTADOS (AÑO 1)</t>
@@ -3797,14 +3805,14 @@
     <row r="3">
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Proyección económica antes de impuestos: todo el trabajo se supone pagado; no es un estado fiscal.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="17.4" customHeight="1">
+          <t>Flujo: solo efectivo. Resultado: incluye trabajo aportado. Renta 0 bajo formalización MYPE; no es beneficio confirmado.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="17.4" customHeight="1" s="51">
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>1. FLUJO PROYECTADO (TRABAJO TÉCNICO PAGADO)</t>
+          <t>1. FLUJO DE EFECTIVO (TRABAJO PROPIO SIN PAGO)</t>
         </is>
       </c>
     </row>
@@ -3901,7 +3909,7 @@
       <c r="O7" s="28" t="n"/>
     </row>
     <row r="8">
-      <c r="B8" s="50" t="inlineStr">
+      <c r="B8" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">  Ingresos por Suscripciones (MRR)</t>
         </is>
@@ -3960,14 +3968,14 @@
       </c>
     </row>
     <row r="9">
-      <c r="B9" s="50" t="inlineStr">
+      <c r="B9" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">  Aporte de Capital Inicial / Socio</t>
         </is>
       </c>
       <c r="C9" s="7">
-        <f>MAX(0,(SUM($C$15:C15)-SUM($C$8:C8)),(SUM($C$15:D15)-SUM($C$8:D8)),(SUM($C$15:E15)-SUM($C$8:E8)),(SUM($C$15:F15)-SUM($C$8:F8)),(SUM($C$15:G15)-SUM($C$8:G8)),(SUM($C$15:H15)-SUM($C$8:H8)),(SUM($C$15:I15)-SUM($C$8:I8)),(SUM($C$15:J15)-SUM($C$8:J8)),(SUM($C$15:K15)-SUM($C$8:K8)),(SUM($C$15:L15)-SUM($C$8:L8)),(SUM($C$15:M15)-SUM($C$8:M8)),(SUM($C$15:N15)-SUM($C$8:N8)))</f>
-        <v>679165.99</v>
+        <f>MAX(40000,(SUM($C$15:C15)-SUM($C$8:C8)),(SUM($C$15:D15)-SUM($C$8:D8)),(SUM($C$15:E15)-SUM($C$8:E8)),(SUM($C$15:F15)-SUM($C$8:F8)),(SUM($C$15:G15)-SUM($C$8:G8)),(SUM($C$15:H15)-SUM($C$8:H8)),(SUM($C$15:I15)-SUM($C$8:I8)),(SUM($C$15:J15)-SUM($C$8:J8)),(SUM($C$15:K15)-SUM($C$8:K8)),(SUM($C$15:L15)-SUM($C$8:L8)),(SUM($C$15:M15)-SUM($C$8:M8)),(SUM($C$15:N15)-SUM($C$8:N8)))</f>
+        <v>40000</v>
       </c>
       <c r="D9" s="7" t="n">
         <v>0</v>
@@ -4004,7 +4012,7 @@
       </c>
       <c r="O9" s="20">
         <f>SUM(C9:N9)</f>
-        <v>679165.99</v>
+        <v>40000.0</v>
       </c>
     </row>
     <row r="10">
@@ -4015,7 +4023,7 @@
       </c>
       <c r="C10" s="20">
         <f>SUM(C8:C9)</f>
-        <v>794165.99</v>
+        <v>155000.0</v>
       </c>
       <c r="D10" s="20">
         <f>SUM(D8:D9)</f>
@@ -4063,7 +4071,7 @@
       </c>
       <c r="O10" s="20">
         <f>SUM(C10:N10)</f>
-        <v>3459165.99</v>
+        <v>2820000.0</v>
       </c>
     </row>
     <row r="11">
@@ -4087,14 +4095,14 @@
       <c r="O11" s="28" t="n"/>
     </row>
     <row r="12">
-      <c r="B12" s="50" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Desarrollo inicial (gasto único)</t>
+      <c r="B12" s="29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Desarrollo: desembolso efectivo</t>
         </is>
       </c>
       <c r="C12" s="7">
-        <f>'Egresos e Inversión'!D12</f>
-        <v>480000.0</v>
+        <f>0</f>
+        <v>0</v>
       </c>
       <c r="D12" s="7" t="n">
         <v>0</v>
@@ -4131,125 +4139,125 @@
       </c>
       <c r="O12" s="20">
         <f>SUM(C12:N12)</f>
-        <v>480000.0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
-      <c r="B13" s="50" t="inlineStr">
+      <c r="B13" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">  Gastos Fijos Operativos (OPEX)</t>
         </is>
       </c>
       <c r="C13" s="7">
-        <f>'Egresos e Inversión'!D35</f>
-        <v>91125.0</v>
+        <f>'Egresos e Inversión'!D35-(4+36)*(496838.17/30/8)</f>
+        <v>109125.0</v>
       </c>
       <c r="D13" s="7">
-        <f>'Egresos e Inversión'!D36</f>
-        <v>91125.0</v>
+        <f>'Egresos e Inversión'!D36-(4+12)*(496838.17/30/8)</f>
+        <v>81125.0</v>
       </c>
       <c r="E13" s="7">
-        <f>'Egresos e Inversión'!D37</f>
-        <v>91125.0</v>
+        <f>'Egresos e Inversión'!D37-(4+12)*(496838.17/30/8)</f>
+        <v>81125.0</v>
       </c>
       <c r="F13" s="7">
-        <f>'Egresos e Inversión'!D38</f>
-        <v>91125.0</v>
+        <f>'Egresos e Inversión'!D38-(4+12)*(496838.17/30/8)</f>
+        <v>81125.0</v>
       </c>
       <c r="G13" s="7">
-        <f>'Egresos e Inversión'!D39</f>
-        <v>91125.0</v>
+        <f>'Egresos e Inversión'!D39-(4+12)*(496838.17/30/8)</f>
+        <v>81125.0</v>
       </c>
       <c r="H13" s="7">
-        <f>'Egresos e Inversión'!D40</f>
-        <v>91125.0</v>
+        <f>'Egresos e Inversión'!D40-(4+12)*(496838.17/30/8)</f>
+        <v>81125.0</v>
       </c>
       <c r="I13" s="7">
-        <f>'Egresos e Inversión'!D41</f>
-        <v>91125.0</v>
+        <f>'Egresos e Inversión'!D41-(4+12)*(496838.17/30/8)</f>
+        <v>81125.0</v>
       </c>
       <c r="J13" s="7">
-        <f>'Egresos e Inversión'!D42</f>
-        <v>91125.0</v>
+        <f>'Egresos e Inversión'!D42-(4+12)*(496838.17/30/8)</f>
+        <v>81125.0</v>
       </c>
       <c r="K13" s="7">
-        <f>'Egresos e Inversión'!D43</f>
-        <v>91125.0</v>
+        <f>'Egresos e Inversión'!D43-(4+12)*(496838.17/30/8)</f>
+        <v>81125.0</v>
       </c>
       <c r="L13" s="7">
-        <f>'Egresos e Inversión'!D44</f>
-        <v>91125.0</v>
+        <f>'Egresos e Inversión'!D44-(4+12)*(496838.17/30/8)</f>
+        <v>81125.0</v>
       </c>
       <c r="M13" s="7">
-        <f>'Egresos e Inversión'!D45</f>
-        <v>91125.0</v>
+        <f>'Egresos e Inversión'!D45-(4+12)*(496838.17/30/8)</f>
+        <v>81125.0</v>
       </c>
       <c r="N13" s="7">
-        <f>'Egresos e Inversión'!D46</f>
-        <v>91125.0</v>
+        <f>'Egresos e Inversión'!D46-(4+12)*(496838.17/30/8)</f>
+        <v>81125.0</v>
       </c>
       <c r="O13" s="20">
         <f>SUM(C13:N13)</f>
-        <v>1093500.0</v>
+        <v>1001500.0</v>
       </c>
     </row>
     <row r="14">
-      <c r="B14" s="50" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Variables, instalaciones y nube</t>
+      <c r="B14" s="29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Servicios y nube: pagos externos</t>
         </is>
       </c>
       <c r="C14" s="7">
-        <f>'Egresos e Inversión'!E35</f>
-        <v>214482.79</v>
+        <f>'Egresos e Inversión'!E35-('Clientes e Ingresos'!F6*0.5+'Clientes e Ingresos'!D6*8)*(496838.17/30/8)</f>
+        <v>1982.7899999999936</v>
       </c>
       <c r="D14" s="7">
-        <f>'Egresos e Inversión'!E36</f>
-        <v>57433.2</v>
+        <f>'Egresos e Inversión'!E36-('Clientes e Ingresos'!F7*0.5+'Clientes e Ingresos'!D7*8)*(496838.17/30/8)</f>
+        <v>2433.2000000000007</v>
       </c>
       <c r="E14" s="7">
-        <f>'Egresos e Inversión'!E37</f>
-        <v>60383.61</v>
+        <f>'Egresos e Inversión'!E37-('Clientes e Ingresos'!F8*0.5+'Clientes e Ingresos'!D8*8)*(496838.17/30/8)</f>
+        <v>2883.6100000000006</v>
       </c>
       <c r="F14" s="7">
-        <f>'Egresos e Inversión'!E38</f>
-        <v>73334.02</v>
+        <f>'Egresos e Inversión'!E38-('Clientes e Ingresos'!F9*0.5+'Clientes e Ingresos'!D9*8)*(496838.17/30/8)</f>
+        <v>13334.02</v>
       </c>
       <c r="G14" s="7">
-        <f>'Egresos e Inversión'!E39</f>
-        <v>76284.43</v>
+        <f>'Egresos e Inversión'!E39-('Clientes e Ingresos'!F10*0.5+'Clientes e Ingresos'!D10*8)*(496838.17/30/8)</f>
+        <v>13784.43</v>
       </c>
       <c r="H14" s="7">
-        <f>'Egresos e Inversión'!E40</f>
-        <v>76284.43</v>
+        <f>'Egresos e Inversión'!E40-('Clientes e Ingresos'!F11*0.5+'Clientes e Ingresos'!D11*8)*(496838.17/30/8)</f>
+        <v>13784.43</v>
       </c>
       <c r="I14" s="7">
-        <f>'Egresos e Inversión'!E41</f>
-        <v>79234.84</v>
+        <f>'Egresos e Inversión'!E41-('Clientes e Ingresos'!F12*0.5+'Clientes e Ingresos'!D12*8)*(496838.17/30/8)</f>
+        <v>14234.84</v>
       </c>
       <c r="J14" s="7">
-        <f>'Egresos e Inversión'!E42</f>
-        <v>84685.25</v>
+        <f>'Egresos e Inversión'!E42-('Clientes e Ingresos'!F13*0.5+'Clientes e Ingresos'!D13*8)*(496838.17/30/8)</f>
+        <v>17185.25</v>
       </c>
       <c r="K14" s="7">
-        <f>'Egresos e Inversión'!E43</f>
-        <v>87635.66</v>
+        <f>'Egresos e Inversión'!E43-('Clientes e Ingresos'!F14*0.5+'Clientes e Ingresos'!D14*8)*(496838.17/30/8)</f>
+        <v>17635.659999999996</v>
       </c>
       <c r="L14" s="7">
-        <f>'Egresos e Inversión'!E44</f>
-        <v>87635.66</v>
+        <f>'Egresos e Inversión'!E44-('Clientes e Ingresos'!F15*0.5+'Clientes e Ingresos'!D15*8)*(496838.17/30/8)</f>
+        <v>17635.659999999996</v>
       </c>
       <c r="M14" s="7">
-        <f>'Egresos e Inversión'!E45</f>
-        <v>90586.07</v>
+        <f>'Egresos e Inversión'!E45-('Clientes e Ingresos'!F16*0.5+'Clientes e Ingresos'!D16*8)*(496838.17/30/8)</f>
+        <v>18086.069999999996</v>
       </c>
       <c r="N14" s="7">
-        <f>'Egresos e Inversión'!E46</f>
-        <v>93536.48</v>
+        <f>'Egresos e Inversión'!E46-('Clientes e Ingresos'!F17*0.5+'Clientes e Ingresos'!D17*8)*(496838.17/30/8)</f>
+        <v>18536.480000000003</v>
       </c>
       <c r="O14" s="20">
         <f>SUM(C14:N14)</f>
-        <v>1081516.44</v>
+        <v>151516.44</v>
       </c>
     </row>
     <row r="15">
@@ -4260,55 +4268,55 @@
       </c>
       <c r="C15" s="20">
         <f>SUM(C12:C14)</f>
-        <v>785607.79</v>
+        <v>111107.79</v>
       </c>
       <c r="D15" s="20">
         <f>SUM(D12:D14)</f>
-        <v>148558.2</v>
+        <v>83558.2</v>
       </c>
       <c r="E15" s="20">
         <f>SUM(E12:E14)</f>
-        <v>151508.61</v>
+        <v>84008.61</v>
       </c>
       <c r="F15" s="20">
         <f>SUM(F12:F14)</f>
-        <v>164459.02000000002</v>
+        <v>94459.02</v>
       </c>
       <c r="G15" s="20">
         <f>SUM(G12:G14)</f>
-        <v>167409.43</v>
+        <v>94909.43</v>
       </c>
       <c r="H15" s="20">
         <f>SUM(H12:H14)</f>
-        <v>167409.43</v>
+        <v>94909.43</v>
       </c>
       <c r="I15" s="20">
         <f>SUM(I12:I14)</f>
-        <v>170359.84</v>
+        <v>95359.84</v>
       </c>
       <c r="J15" s="20">
         <f>SUM(J12:J14)</f>
-        <v>175810.25</v>
+        <v>98310.25</v>
       </c>
       <c r="K15" s="20">
         <f>SUM(K12:K14)</f>
-        <v>178760.66</v>
+        <v>98760.66</v>
       </c>
       <c r="L15" s="20">
         <f>SUM(L12:L14)</f>
-        <v>178760.66</v>
+        <v>98760.66</v>
       </c>
       <c r="M15" s="20">
         <f>SUM(M12:M14)</f>
-        <v>181711.07</v>
+        <v>99211.06999999999</v>
       </c>
       <c r="N15" s="20">
         <f>SUM(N12:N14)</f>
-        <v>184661.47999999998</v>
+        <v>99661.48000000001</v>
       </c>
       <c r="O15" s="20">
         <f>SUM(C15:N15)</f>
-        <v>2655016.44</v>
+        <v>1153016.44</v>
       </c>
     </row>
     <row r="16">
@@ -4319,55 +4327,55 @@
       </c>
       <c r="C16" s="20">
         <f>C10-C15</f>
-        <v>8558.199999999953</v>
+        <v>43892.21000000001</v>
       </c>
       <c r="D16" s="20">
         <f>D10-D15</f>
-        <v>-8558.200000000012</v>
+        <v>56441.8</v>
       </c>
       <c r="E16" s="20">
         <f>E10-E15</f>
-        <v>13491.390000000014</v>
+        <v>80991.39</v>
       </c>
       <c r="F16" s="20">
         <f>F10-F15</f>
-        <v>25540.97999999998</v>
+        <v>95540.98</v>
       </c>
       <c r="G16" s="20">
         <f>G10-G15</f>
-        <v>47590.57000000001</v>
+        <v>120090.57</v>
       </c>
       <c r="H16" s="20">
         <f>H10-H15</f>
-        <v>47590.57000000001</v>
+        <v>120090.57</v>
       </c>
       <c r="I16" s="20">
         <f>I10-I15</f>
-        <v>69640.16</v>
+        <v>144640.16</v>
       </c>
       <c r="J16" s="20">
         <f>J10-J15</f>
-        <v>89189.75</v>
+        <v>166689.75</v>
       </c>
       <c r="K16" s="20">
         <f>K10-K15</f>
-        <v>111239.34</v>
+        <v>191239.34</v>
       </c>
       <c r="L16" s="20">
         <f>L10-L15</f>
-        <v>111239.34</v>
+        <v>191239.34</v>
       </c>
       <c r="M16" s="20">
         <f>M10-M15</f>
-        <v>133288.93</v>
+        <v>215788.93</v>
       </c>
       <c r="N16" s="20">
         <f>N10-N15</f>
-        <v>155338.52000000002</v>
+        <v>240338.52</v>
       </c>
       <c r="O16" s="20">
         <f>SUM(C16:N16)</f>
-        <v>804149.5499999998</v>
+        <v>1666983.56</v>
       </c>
     </row>
     <row r="17">
@@ -4378,58 +4386,58 @@
       </c>
       <c r="C17" s="31">
         <f>C16</f>
-        <v>8558.199999999953</v>
+        <v>43892.21000000001</v>
       </c>
       <c r="D17" s="31">
         <f>C17+D16</f>
-        <v>-5.820766091346741e-11</v>
+        <v>100334.01000000001</v>
       </c>
       <c r="E17" s="31">
         <f>D17+E16</f>
-        <v>13491.389999999956</v>
+        <v>181325.40000000002</v>
       </c>
       <c r="F17" s="31">
         <f>E17+F16</f>
-        <v>39032.36999999994</v>
+        <v>276866.38</v>
       </c>
       <c r="G17" s="31">
         <f>F17+G16</f>
-        <v>86622.93999999994</v>
+        <v>396956.95</v>
       </c>
       <c r="H17" s="31">
         <f>G17+H16</f>
-        <v>134213.50999999995</v>
+        <v>517047.52</v>
       </c>
       <c r="I17" s="31">
         <f>H17+I16</f>
-        <v>203853.66999999995</v>
+        <v>661687.68</v>
       </c>
       <c r="J17" s="31">
         <f>I17+J16</f>
-        <v>293043.4199999999</v>
+        <v>828377.43</v>
       </c>
       <c r="K17" s="31">
         <f>J17+K16</f>
-        <v>404282.7599999999</v>
+        <v>1019616.77</v>
       </c>
       <c r="L17" s="31">
         <f>K17+L16</f>
-        <v>515522.09999999986</v>
+        <v>1210856.11</v>
       </c>
       <c r="M17" s="31">
         <f>L17+M16</f>
-        <v>648811.0299999998</v>
+        <v>1426645.04</v>
       </c>
       <c r="N17" s="31">
         <f>M17+N16</f>
-        <v>804149.5499999998</v>
+        <v>1666983.56</v>
       </c>
       <c r="O17" s="20">
         <f>N17</f>
-        <v>804149.5499999998</v>
-      </c>
-    </row>
-    <row r="20" ht="17.4" customHeight="1">
+        <v>1666983.56</v>
+      </c>
+    </row>
+    <row r="20" ht="17.4" customHeight="1" s="51">
       <c r="B20" s="3" t="inlineStr">
         <is>
           <t>2. ESTADO DE GANANCIAS Y PÉRDIDAS PROYECTADO (AÑO 1)</t>
@@ -4454,7 +4462,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="B22" s="49" t="inlineStr">
+      <c r="B22" s="59" t="inlineStr">
         <is>
           <t>Ingresos Operativos Totales (Ventas)</t>
         </is>
@@ -4475,11 +4483,11 @@
       </c>
       <c r="C23" s="10">
         <f>'Egresos e Inversión'!E47</f>
-        <v>1081516.44</v>
+        <v>536566.02175</v>
       </c>
       <c r="D23" s="34">
         <f>C23/C22</f>
-        <v>0.389034690647482</v>
+        <v>0.1930093603417266</v>
       </c>
     </row>
     <row r="24">
@@ -4490,41 +4498,41 @@
       </c>
       <c r="C24" s="25">
         <f>C22-C23</f>
-        <v>1698483.56</v>
+        <v>2243433.97825</v>
       </c>
       <c r="D24" s="35">
         <f>C24/C22</f>
-        <v>0.610965309352518</v>
+        <v>0.8069906396582734</v>
       </c>
     </row>
     <row r="25">
-      <c r="B25" s="52" t="inlineStr">
+      <c r="B25" s="44" t="inlineStr">
         <is>
           <t xml:space="preserve">(-) Gastos Operativos Fijos </t>
         </is>
       </c>
       <c r="C25" s="10">
         <f>'Egresos e Inversión'!D47</f>
-        <v>1093500.0</v>
+        <v>1448654.3530000004</v>
       </c>
       <c r="D25" s="34">
         <f>C25/C22</f>
-        <v>0.39334532374100717</v>
+        <v>0.5210986881294966</v>
       </c>
     </row>
     <row r="26">
-      <c r="B26" s="49" t="inlineStr">
+      <c r="B26" s="59" t="inlineStr">
         <is>
           <t>RESULTADO ANTES DEL DESARROLLO</t>
         </is>
       </c>
       <c r="C26" s="7">
         <f>C24-C25</f>
-        <v>604983.56</v>
+        <v>794779.6252499998</v>
       </c>
       <c r="D26" s="32">
         <f>C26/C22</f>
-        <v>0.2176199856115108</v>
+        <v>0.2858919515287769</v>
       </c>
     </row>
     <row r="27">
@@ -4535,11 +4543,11 @@
       </c>
       <c r="C27" s="10">
         <f>'Egresos e Inversión'!D12</f>
-        <v>480000.0</v>
+        <v>198735.26799999998</v>
       </c>
       <c r="D27" s="34">
         <f>C27/C22</f>
-        <v>0.17266187050359713</v>
+        <v>0.07148750647482013</v>
       </c>
     </row>
     <row r="28">
@@ -4550,54 +4558,52 @@
       </c>
       <c r="C28" s="25">
         <f>C26-C27</f>
-        <v>124983.56000000006</v>
+        <v>596044.3572499999</v>
       </c>
       <c r="D28" s="35">
         <f>C28/C22</f>
-        <v>0.04495811510791369</v>
+        <v>0.21440444505395678</v>
       </c>
     </row>
     <row r="29">
       <c r="B29" s="33" t="inlineStr">
         <is>
-          <t>Impuestos: fuera de este análisis</t>
-        </is>
-      </c>
-      <c r="C29" s="10" t="inlineStr">
-        <is>
-          <t>No calculado</t>
-        </is>
-      </c>
-      <c r="D29" s="34" t="inlineStr">
-        <is>
-          <t>No aplica</t>
-        </is>
+          <t>Renta: escenario MYPE formalizada</t>
+        </is>
+      </c>
+      <c r="C29" s="10">
+        <f>0</f>
+        <v>0</v>
+      </c>
+      <c r="D29" s="34">
+        <f>IFERROR(C29/C22,0)</f>
+        <v>0</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>No se presupone exoneración MYPE. Resultado y balance se muestran antes de impuestos; no constituyen determinación tributaria.</t>
+          <t>0% del impuesto determinado en años 1–3, condicionado a registros y requisitos. Pulso todavía sin registrar.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="B30" s="36" t="inlineStr">
         <is>
-          <t>RESULTADO ECONÓMICO ANTES DE IMPUESTOS</t>
+          <t>RESULTADO ECONÓMICO · ESCENARIO MYPE</t>
         </is>
       </c>
       <c r="C30" s="37">
-        <f>C28</f>
-        <v>124983.56000000006</v>
+        <f>C28-C29</f>
+        <v>596044.3572499999</v>
       </c>
       <c r="D30" s="38">
         <f>C30/C22</f>
-        <v>0.04495811510791369</v>
-      </c>
-    </row>
-    <row r="32" ht="17.4" customHeight="1">
+        <v>0.21440444505395678</v>
+      </c>
+    </row>
+    <row r="32" ht="17.4" customHeight="1" s="51">
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>3. BALANCE ECONÓMICO SIMPLIFICADO (ANTES DE IMPUESTOS)</t>
+          <t>3. BALANCE ECONÓMICO (APORTES DE EFECTIVO Y TRABAJO)</t>
         </is>
       </c>
     </row>
@@ -4638,16 +4644,16 @@
       <c r="F34" s="42" t="n"/>
     </row>
     <row r="35">
-      <c r="B35" s="49" t="inlineStr">
+      <c r="B35" s="59" t="inlineStr">
         <is>
           <t xml:space="preserve">  Efectivo y Bancos (Caja Final)</t>
         </is>
       </c>
       <c r="C35" s="7">
         <f>N17</f>
-        <v>804149.5499999998</v>
-      </c>
-      <c r="E35" s="49" t="inlineStr">
+        <v>1666983.56</v>
+      </c>
+      <c r="E35" s="59" t="inlineStr">
         <is>
           <t xml:space="preserve">  Deuda financiera modelada</t>
         </is>
@@ -4665,7 +4671,7 @@
       </c>
       <c r="C36" s="25">
         <f>C35</f>
-        <v>804149.5499999998</v>
+        <v>1666983.56</v>
       </c>
       <c r="E36" s="27" t="inlineStr">
         <is>
@@ -4692,7 +4698,7 @@
       <c r="F37" s="42" t="n"/>
     </row>
     <row r="38">
-      <c r="B38" s="49" t="inlineStr">
+      <c r="B38" s="59" t="inlineStr">
         <is>
           <t xml:space="preserve">  Desarrollo capitalizado (no aplicado)</t>
         </is>
@@ -4701,18 +4707,18 @@
         <f>0</f>
         <v>0</v>
       </c>
-      <c r="E38" s="49" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Capital Social Aportado</t>
+      <c r="E38" s="59" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Aportes de efectivo y trabajo</t>
         </is>
       </c>
       <c r="F38" s="7">
-        <f>C9</f>
-        <v>679165.99</v>
+        <f>C9+'Egresos e Inversión'!D12+'Egresos e Inversión'!D47+'Egresos e Inversión'!E47-O15</f>
+        <v>1070939.2027500002</v>
       </c>
     </row>
     <row r="39">
-      <c r="B39" s="49" t="inlineStr">
+      <c r="B39" s="59" t="inlineStr">
         <is>
           <t xml:space="preserve">  Amortización (no aplicada)</t>
         </is>
@@ -4721,14 +4727,14 @@
         <f>0</f>
         <v>0</v>
       </c>
-      <c r="E39" s="49" t="inlineStr">
+      <c r="E39" s="59" t="inlineStr">
         <is>
           <t xml:space="preserve">  Utilidades Acumuladas del Ejercicio</t>
         </is>
       </c>
       <c r="F39" s="7">
         <f>C30</f>
-        <v>124983.56000000006</v>
+        <v>596044.3572499999</v>
       </c>
     </row>
     <row r="40">
@@ -4748,7 +4754,7 @@
       </c>
       <c r="F40" s="25">
         <f>F38+F39</f>
-        <v>804149.55</v>
+        <v>1666983.56</v>
       </c>
     </row>
     <row r="41">
@@ -4759,7 +4765,7 @@
       </c>
       <c r="C41" s="37">
         <f>C36+C40</f>
-        <v>804149.5499999998</v>
+        <v>1666983.56</v>
       </c>
       <c r="E41" s="36" t="inlineStr">
         <is>
@@ -4768,10 +4774,13 @@
       </c>
       <c r="F41" s="37">
         <f>F36+F40</f>
-        <v>804149.55</v>
+        <v>1666983.56</v>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="E29" r:id="rId1"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <legacyDrawing r:id="anysvml"/>
 </worksheet>
